--- a/Data/2015_F013B4_CO_ISOS/2015_F013B4_CO_ISOS_SoilAnalysis.xlsx
+++ b/Data/2015_F013B4_CO_ISOS/2015_F013B4_CO_ISOS_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2015_F013B4_CO_ISOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4C633C-F0AD-491E-ABE8-E7E7EC1B1F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004A9958-4438-4D38-B75F-6B3FC9F38899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16320" yWindow="-28050" windowWidth="17910" windowHeight="25080" xr2:uid="{703BA8F2-5457-4E8B-97CE-55FD3F4AE98B}"/>
+    <workbookView xWindow="-1665" yWindow="-25680" windowWidth="27270" windowHeight="17295" xr2:uid="{703BA8F2-5457-4E8B-97CE-55FD3F4AE98B}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDJH" sheetId="4" r:id="rId1"/>
@@ -380,9 +380,6 @@
     <t>Plot</t>
   </si>
   <si>
-    <t>2013d260EM38</t>
-  </si>
-  <si>
     <t>2015d118EM38</t>
   </si>
   <si>
@@ -1179,6 +1176,9 @@
   </si>
   <si>
     <t>2016-p2006</t>
+  </si>
+  <si>
+    <t>2013d260EM38V</t>
   </si>
 </sst>
 </file>
@@ -1558,13 +1558,13 @@
         <v>101</v>
       </c>
       <c r="B1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E1" t="s">
         <v>112</v>
@@ -1575,7 +1575,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C2">
         <v>408983.429999999</v>
@@ -1592,7 +1592,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C3">
         <v>408983.89409999899</v>
@@ -1609,7 +1609,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C4">
         <v>408984.30259999901</v>
@@ -1626,7 +1626,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C5">
         <v>408984.79070000001</v>
@@ -1643,7 +1643,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C6">
         <v>408985.21360000002</v>
@@ -1660,7 +1660,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C7">
         <v>408985.649299999</v>
@@ -1677,7 +1677,7 @@
         <v>131</v>
       </c>
       <c r="B8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C8">
         <v>408992.87400000001</v>
@@ -1694,7 +1694,7 @@
         <v>132</v>
       </c>
       <c r="B9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C9">
         <v>408992.37520000001</v>
@@ -1711,7 +1711,7 @@
         <v>133</v>
       </c>
       <c r="B10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C10">
         <v>408991.93300000002</v>
@@ -1728,7 +1728,7 @@
         <v>134</v>
       </c>
       <c r="B11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C11">
         <v>408991.4412</v>
@@ -1745,7 +1745,7 @@
         <v>135</v>
       </c>
       <c r="B12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C12">
         <v>408990.94170000002</v>
@@ -1762,7 +1762,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C13">
         <v>408957.18540000002</v>
@@ -1779,7 +1779,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C14">
         <v>408956.76750000002</v>
@@ -1796,7 +1796,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C15">
         <v>408956.30570000003</v>
@@ -1813,7 +1813,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C16">
         <v>408955.91499999899</v>
@@ -1830,7 +1830,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C17">
         <v>408955.44280000002</v>
@@ -1847,7 +1847,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C18">
         <v>408955.01179999899</v>
@@ -1864,7 +1864,7 @@
         <v>136</v>
       </c>
       <c r="B19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C19">
         <v>408962.41840000002</v>
@@ -1881,7 +1881,7 @@
         <v>137</v>
       </c>
       <c r="B20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C20">
         <v>408961.93680000002</v>
@@ -1898,7 +1898,7 @@
         <v>138</v>
       </c>
       <c r="B21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C21">
         <v>408961.4645</v>
@@ -1915,7 +1915,7 @@
         <v>139</v>
       </c>
       <c r="B22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C22">
         <v>408960.96830000001</v>
@@ -1932,7 +1932,7 @@
         <v>140</v>
       </c>
       <c r="B23" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C23">
         <v>408960.493599999</v>
@@ -1949,7 +1949,7 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C24">
         <v>408926.557299999</v>
@@ -1966,7 +1966,7 @@
         <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C25">
         <v>408926.97979999898</v>
@@ -1983,7 +1983,7 @@
         <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C26">
         <v>408927.42930000002</v>
@@ -2000,7 +2000,7 @@
         <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C27">
         <v>408927.88109999901</v>
@@ -2017,7 +2017,7 @@
         <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C28">
         <v>408928.31640000001</v>
@@ -2034,7 +2034,7 @@
         <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C29">
         <v>408928.783999999</v>
@@ -2051,7 +2051,7 @@
         <v>141</v>
       </c>
       <c r="B30" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C30">
         <v>408936.025599999</v>
@@ -2068,7 +2068,7 @@
         <v>142</v>
       </c>
       <c r="B31" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C31">
         <v>408935.529199999</v>
@@ -2085,7 +2085,7 @@
         <v>143</v>
       </c>
       <c r="B32" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C32">
         <v>408935.03840000002</v>
@@ -2102,7 +2102,7 @@
         <v>144</v>
       </c>
       <c r="B33" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C33">
         <v>408934.55099999899</v>
@@ -2119,7 +2119,7 @@
         <v>145</v>
       </c>
       <c r="B34" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C34">
         <v>408934.06530000002</v>
@@ -2136,7 +2136,7 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C35">
         <v>408901.33329999901</v>
@@ -2153,7 +2153,7 @@
         <v>26</v>
       </c>
       <c r="B36" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C36">
         <v>408900.9032</v>
@@ -2170,7 +2170,7 @@
         <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C37">
         <v>408900.44150000002</v>
@@ -2187,7 +2187,7 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C38">
         <v>408899.99949999899</v>
@@ -2204,7 +2204,7 @@
         <v>29</v>
       </c>
       <c r="B39" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C39">
         <v>408899.580599999</v>
@@ -2221,7 +2221,7 @@
         <v>30</v>
       </c>
       <c r="B40" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C40">
         <v>408899.109999999</v>
@@ -2238,7 +2238,7 @@
         <v>146</v>
       </c>
       <c r="B41" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C41">
         <v>408906.29479999898</v>
@@ -2255,7 +2255,7 @@
         <v>147</v>
       </c>
       <c r="B42" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C42">
         <v>408905.79359999899</v>
@@ -2272,7 +2272,7 @@
         <v>148</v>
       </c>
       <c r="B43" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C43">
         <v>408905.32140000002</v>
@@ -2289,7 +2289,7 @@
         <v>149</v>
       </c>
       <c r="B44" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C44">
         <v>408904.8211</v>
@@ -2306,7 +2306,7 @@
         <v>150</v>
       </c>
       <c r="B45" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C45">
         <v>408904.35749999899</v>
@@ -2323,7 +2323,7 @@
         <v>31</v>
       </c>
       <c r="B46" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C46">
         <v>408870.67979999899</v>
@@ -2340,7 +2340,7 @@
         <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C47">
         <v>408871.13660000003</v>
@@ -2357,7 +2357,7 @@
         <v>33</v>
       </c>
       <c r="B48" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C48">
         <v>408871.57900000003</v>
@@ -2374,7 +2374,7 @@
         <v>34</v>
       </c>
       <c r="B49" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C49">
         <v>408872.00809999899</v>
@@ -2391,7 +2391,7 @@
         <v>35</v>
       </c>
       <c r="B50" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C50">
         <v>408872.451899999</v>
@@ -2408,7 +2408,7 @@
         <v>36</v>
       </c>
       <c r="B51" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C51">
         <v>408872.89059999899</v>
@@ -2425,7 +2425,7 @@
         <v>151</v>
       </c>
       <c r="B52" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C52">
         <v>408879.86940000003</v>
@@ -2442,7 +2442,7 @@
         <v>152</v>
       </c>
       <c r="B53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C53">
         <v>408879.400499999</v>
@@ -2459,7 +2459,7 @@
         <v>153</v>
       </c>
       <c r="B54" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C54">
         <v>408878.89939999901</v>
@@ -2476,7 +2476,7 @@
         <v>154</v>
       </c>
       <c r="B55" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C55">
         <v>408878.41070000001</v>
@@ -2493,7 +2493,7 @@
         <v>155</v>
       </c>
       <c r="B56" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C56">
         <v>408877.92340000003</v>
@@ -2510,7 +2510,7 @@
         <v>37</v>
       </c>
       <c r="B57" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C57">
         <v>408845.46089999902</v>
@@ -2527,7 +2527,7 @@
         <v>38</v>
       </c>
       <c r="B58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C58">
         <v>408845.02049999899</v>
@@ -2544,7 +2544,7 @@
         <v>39</v>
       </c>
       <c r="B59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C59">
         <v>408844.56319999899</v>
@@ -2561,7 +2561,7 @@
         <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C60">
         <v>408844.13500000001</v>
@@ -2578,7 +2578,7 @@
         <v>41</v>
       </c>
       <c r="B61" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C61">
         <v>408843.68329999998</v>
@@ -2595,7 +2595,7 @@
         <v>42</v>
       </c>
       <c r="B62" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C62">
         <v>408843.26179999899</v>
@@ -2612,7 +2612,7 @@
         <v>156</v>
       </c>
       <c r="B63" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C63">
         <v>408850.18070000003</v>
@@ -2629,7 +2629,7 @@
         <v>157</v>
       </c>
       <c r="B64" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C64">
         <v>408849.70020000002</v>
@@ -2646,7 +2646,7 @@
         <v>158</v>
       </c>
       <c r="B65" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C65">
         <v>408849.219199999</v>
@@ -2663,7 +2663,7 @@
         <v>159</v>
       </c>
       <c r="B66" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C66">
         <v>408848.73200000002</v>
@@ -2680,7 +2680,7 @@
         <v>160</v>
       </c>
       <c r="B67" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C67">
         <v>408848.231299999</v>
@@ -2697,7 +2697,7 @@
         <v>43</v>
       </c>
       <c r="B68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C68">
         <v>408814.80080000003</v>
@@ -2714,7 +2714,7 @@
         <v>44</v>
       </c>
       <c r="B69" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C69">
         <v>408815.248499999</v>
@@ -2731,7 +2731,7 @@
         <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C70">
         <v>408815.666399999</v>
@@ -2748,7 +2748,7 @@
         <v>46</v>
       </c>
       <c r="B71" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C71">
         <v>408816.12689999898</v>
@@ -2765,7 +2765,7 @@
         <v>47</v>
       </c>
       <c r="B72" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C72">
         <v>408816.55469999899</v>
@@ -2782,7 +2782,7 @@
         <v>48</v>
       </c>
       <c r="B73" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C73">
         <v>408817.00829999999</v>
@@ -2799,7 +2799,7 @@
         <v>161</v>
       </c>
       <c r="B74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C74">
         <v>408823.76260000002</v>
@@ -2816,7 +2816,7 @@
         <v>162</v>
       </c>
       <c r="B75" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C75">
         <v>408823.264399999</v>
@@ -2833,7 +2833,7 @@
         <v>163</v>
       </c>
       <c r="B76" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C76">
         <v>408822.77899999899</v>
@@ -2850,7 +2850,7 @@
         <v>164</v>
       </c>
       <c r="B77" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C77">
         <v>408822.312299999</v>
@@ -2867,7 +2867,7 @@
         <v>165</v>
       </c>
       <c r="B78" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C78">
         <v>408821.829399999</v>
@@ -2884,7 +2884,7 @@
         <v>49</v>
       </c>
       <c r="B79" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C79">
         <v>408788.581799999</v>
@@ -2901,7 +2901,7 @@
         <v>50</v>
       </c>
       <c r="B80" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C80">
         <v>408788.11670000001</v>
@@ -2918,7 +2918,7 @@
         <v>51</v>
       </c>
       <c r="B81" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C81">
         <v>408787.67560000002</v>
@@ -2935,7 +2935,7 @@
         <v>52</v>
       </c>
       <c r="B82" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C82">
         <v>408787.222799999</v>
@@ -2952,7 +2952,7 @@
         <v>53</v>
       </c>
       <c r="B83" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C83">
         <v>408786.80749999901</v>
@@ -2969,7 +2969,7 @@
         <v>54</v>
       </c>
       <c r="B84" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C84">
         <v>408786.36930000002</v>
@@ -2986,7 +2986,7 @@
         <v>166</v>
       </c>
       <c r="B85" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C85">
         <v>408793.35800000001</v>
@@ -3003,7 +3003,7 @@
         <v>167</v>
       </c>
       <c r="B86" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C86">
         <v>408792.866099999</v>
@@ -3020,7 +3020,7 @@
         <v>168</v>
       </c>
       <c r="B87" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C87">
         <v>408792.38530000002</v>
@@ -3037,7 +3037,7 @@
         <v>169</v>
       </c>
       <c r="B88" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C88">
         <v>408791.8947</v>
@@ -3054,7 +3054,7 @@
         <v>170</v>
       </c>
       <c r="B89" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C89">
         <v>408791.43050000002</v>
@@ -3071,7 +3071,7 @@
         <v>55</v>
       </c>
       <c r="B90" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C90">
         <v>408757.90980000002</v>
@@ -3088,7 +3088,7 @@
         <v>56</v>
       </c>
       <c r="B91" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C91">
         <v>408758.367499999</v>
@@ -3105,7 +3105,7 @@
         <v>57</v>
       </c>
       <c r="B92" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C92">
         <v>408758.807399999</v>
@@ -3122,7 +3122,7 @@
         <v>58</v>
       </c>
       <c r="B93" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C93">
         <v>408759.24219999899</v>
@@ -3139,7 +3139,7 @@
         <v>59</v>
       </c>
       <c r="B94" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C94">
         <v>408759.692099999</v>
@@ -3156,7 +3156,7 @@
         <v>60</v>
       </c>
       <c r="B95" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C95">
         <v>408760.11839999899</v>
@@ -3173,7 +3173,7 @@
         <v>171</v>
       </c>
       <c r="B96" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C96">
         <v>408766.92910000001</v>
@@ -3190,7 +3190,7 @@
         <v>172</v>
       </c>
       <c r="B97" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C97">
         <v>408766.46409999899</v>
@@ -3207,7 +3207,7 @@
         <v>173</v>
       </c>
       <c r="B98" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C98">
         <v>408765.99229999899</v>
@@ -3224,7 +3224,7 @@
         <v>174</v>
       </c>
       <c r="B99" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C99">
         <v>408765.47999999899</v>
@@ -3241,7 +3241,7 @@
         <v>175</v>
       </c>
       <c r="B100" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C100">
         <v>408765.01639999897</v>
@@ -3258,7 +3258,7 @@
         <v>61</v>
       </c>
       <c r="B101" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C101">
         <v>408674.80969999899</v>
@@ -3275,7 +3275,7 @@
         <v>62</v>
       </c>
       <c r="B102" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C102">
         <v>408674.3175</v>
@@ -3292,7 +3292,7 @@
         <v>63</v>
       </c>
       <c r="B103" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C103">
         <v>408673.885899999</v>
@@ -3309,7 +3309,7 @@
         <v>64</v>
       </c>
       <c r="B104" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C104">
         <v>408673.42570000002</v>
@@ -3326,7 +3326,7 @@
         <v>65</v>
       </c>
       <c r="B105" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C105">
         <v>408673.00859999901</v>
@@ -3343,7 +3343,7 @@
         <v>66</v>
       </c>
       <c r="B106" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C106">
         <v>408672.59139999899</v>
@@ -3360,7 +3360,7 @@
         <v>176</v>
       </c>
       <c r="B107" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C107">
         <v>408680.68900000001</v>
@@ -3377,7 +3377,7 @@
         <v>177</v>
       </c>
       <c r="B108" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C108">
         <v>408680.20289999899</v>
@@ -3394,7 +3394,7 @@
         <v>178</v>
       </c>
       <c r="B109" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C109">
         <v>408679.7047</v>
@@ -3411,7 +3411,7 @@
         <v>179</v>
       </c>
       <c r="B110" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C110">
         <v>408679.21340000001</v>
@@ -3428,7 +3428,7 @@
         <v>180</v>
       </c>
       <c r="B111" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C111">
         <v>408678.73639999999</v>
@@ -3455,13 +3455,13 @@
         <v>101</v>
       </c>
       <c r="B1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E1" t="s">
         <v>112</v>
@@ -3472,7 +3472,7 @@
         <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C2">
         <v>409000.4903</v>
@@ -3489,7 +3489,7 @@
         <v>71</v>
       </c>
       <c r="B3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C3">
         <v>408997.63040000002</v>
@@ -3506,7 +3506,7 @@
         <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C4">
         <v>408987.19380000001</v>
@@ -3523,7 +3523,7 @@
         <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C5">
         <v>408982.38959999901</v>
@@ -3540,7 +3540,7 @@
         <v>146</v>
       </c>
       <c r="B6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C6">
         <v>408985.71999999898</v>
@@ -3557,7 +3557,7 @@
         <v>147</v>
       </c>
       <c r="B7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C7">
         <v>408984.80999999901</v>
@@ -3574,7 +3574,7 @@
         <v>148</v>
       </c>
       <c r="B8" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C8">
         <v>408983.89</v>
@@ -3591,7 +3591,7 @@
         <v>149</v>
       </c>
       <c r="B9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C9">
         <v>409002.11999999901</v>
@@ -3608,7 +3608,7 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C10">
         <v>408957.29330000002</v>
@@ -3625,7 +3625,7 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C11">
         <v>408956.69130000001</v>
@@ -3642,7 +3642,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C12">
         <v>408956.084399999</v>
@@ -3659,7 +3659,7 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C13">
         <v>408955.49589999899</v>
@@ -3676,7 +3676,7 @@
         <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C14">
         <v>408973.7121</v>
@@ -3693,7 +3693,7 @@
         <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C15">
         <v>408968.074599999</v>
@@ -3710,7 +3710,7 @@
         <v>144</v>
       </c>
       <c r="B16" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C16">
         <v>408961.76</v>
@@ -3727,7 +3727,7 @@
         <v>145</v>
       </c>
       <c r="B17" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C17">
         <v>408963.02</v>
@@ -3744,7 +3744,7 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C18">
         <v>408943.05879999901</v>
@@ -3761,7 +3761,7 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C19">
         <v>408942.48519999901</v>
@@ -3778,7 +3778,7 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C20">
         <v>408941.846599999</v>
@@ -3795,7 +3795,7 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C21">
         <v>408941.274299999</v>
@@ -3812,7 +3812,7 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C22">
         <v>408928.85560000001</v>
@@ -3829,7 +3829,7 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C23">
         <v>408928.25300000003</v>
@@ -3846,7 +3846,7 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C24">
         <v>408927.64370000002</v>
@@ -3863,7 +3863,7 @@
         <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C25">
         <v>408927.035299999</v>
@@ -3880,7 +3880,7 @@
         <v>140</v>
       </c>
       <c r="B26" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C26">
         <v>408933.33</v>
@@ -3897,7 +3897,7 @@
         <v>141</v>
       </c>
       <c r="B27" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C27">
         <v>408934.59</v>
@@ -3914,7 +3914,7 @@
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C28">
         <v>408914.35340000002</v>
@@ -3931,7 +3931,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C29">
         <v>408913.7599</v>
@@ -3948,7 +3948,7 @@
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C30">
         <v>408913.14380000002</v>
@@ -3965,7 +3965,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C31">
         <v>408912.52870000002</v>
@@ -3982,7 +3982,7 @@
         <v>139</v>
       </c>
       <c r="B32" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C32">
         <v>408905.239999999</v>
@@ -3999,7 +3999,7 @@
         <v>153</v>
       </c>
       <c r="B33" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C33">
         <v>408900.20380000002</v>
@@ -4016,7 +4016,7 @@
         <v>154</v>
       </c>
       <c r="B34" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C34">
         <v>408899.61949999898</v>
@@ -4033,7 +4033,7 @@
         <v>155</v>
       </c>
       <c r="B35" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C35">
         <v>408899.00260000001</v>
@@ -4050,7 +4050,7 @@
         <v>156</v>
       </c>
       <c r="B36" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C36">
         <v>408898.37829999899</v>
@@ -4067,7 +4067,7 @@
         <v>135</v>
       </c>
       <c r="B37" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C37">
         <v>408877.859999999</v>
@@ -4084,7 +4084,7 @@
         <v>157</v>
       </c>
       <c r="B38" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C38">
         <v>408885.99040000001</v>
@@ -4101,7 +4101,7 @@
         <v>158</v>
       </c>
       <c r="B39" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C39">
         <v>408885.37439999898</v>
@@ -4118,7 +4118,7 @@
         <v>159</v>
       </c>
       <c r="B40" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C40">
         <v>408884.80279999902</v>
@@ -4135,7 +4135,7 @@
         <v>160</v>
       </c>
       <c r="B41" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C41">
         <v>408884.17149999901</v>
@@ -4152,7 +4152,7 @@
         <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C42">
         <v>408859.25290000002</v>
@@ -4169,7 +4169,7 @@
         <v>18</v>
       </c>
       <c r="B43" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C43">
         <v>408858.64659999899</v>
@@ -4186,7 +4186,7 @@
         <v>19</v>
       </c>
       <c r="B44" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C44">
         <v>408858.0344</v>
@@ -4203,7 +4203,7 @@
         <v>20</v>
       </c>
       <c r="B45" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C45">
         <v>408857.44079999899</v>
@@ -4220,7 +4220,7 @@
         <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C46">
         <v>408845.03460000001</v>
@@ -4237,7 +4237,7 @@
         <v>22</v>
       </c>
       <c r="B47" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C47">
         <v>408844.4375</v>
@@ -4254,7 +4254,7 @@
         <v>23</v>
       </c>
       <c r="B48" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C48">
         <v>408843.829399999</v>
@@ -4271,7 +4271,7 @@
         <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C49">
         <v>408843.20490000001</v>
@@ -4288,7 +4288,7 @@
         <v>132</v>
       </c>
       <c r="B50" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C50">
         <v>408849.489999999</v>
@@ -4305,7 +4305,7 @@
         <v>133</v>
       </c>
       <c r="B51" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C51">
         <v>408850.72999999899</v>
@@ -4322,7 +4322,7 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C52">
         <v>408830.81489999901</v>
@@ -4339,7 +4339,7 @@
         <v>26</v>
       </c>
       <c r="B53" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C53">
         <v>408830.206899999</v>
@@ -4356,7 +4356,7 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C54">
         <v>408829.59519999899</v>
@@ -4373,7 +4373,7 @@
         <v>28</v>
       </c>
       <c r="B55" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C55">
         <v>408828.99920000002</v>
@@ -4390,7 +4390,7 @@
         <v>29</v>
       </c>
       <c r="B56" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C56">
         <v>408816.59179999901</v>
@@ -4407,7 +4407,7 @@
         <v>30</v>
       </c>
       <c r="B57" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C57">
         <v>408815.986199999</v>
@@ -4424,7 +4424,7 @@
         <v>31</v>
       </c>
       <c r="B58" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C58">
         <v>408815.39</v>
@@ -4441,7 +4441,7 @@
         <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C59">
         <v>408814.777</v>
@@ -4458,7 +4458,7 @@
         <v>128</v>
       </c>
       <c r="B60" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C60">
         <v>408821.109999999</v>
@@ -4475,7 +4475,7 @@
         <v>129</v>
       </c>
       <c r="B61" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C61">
         <v>408822.35</v>
@@ -4492,7 +4492,7 @@
         <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C62">
         <v>408802.449499999</v>
@@ -4509,7 +4509,7 @@
         <v>34</v>
       </c>
       <c r="B63" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C63">
         <v>408801.83819999901</v>
@@ -4526,7 +4526,7 @@
         <v>35</v>
       </c>
       <c r="B64" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C64">
         <v>408801.21379999898</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="B65" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C65">
         <v>408800.62819999899</v>
@@ -4560,7 +4560,7 @@
         <v>37</v>
       </c>
       <c r="B66" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C66">
         <v>408788.22350000002</v>
@@ -4577,7 +4577,7 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C67">
         <v>408787.60700000002</v>
@@ -4594,7 +4594,7 @@
         <v>39</v>
       </c>
       <c r="B68" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C68">
         <v>408787.00040000002</v>
@@ -4611,7 +4611,7 @@
         <v>40</v>
       </c>
       <c r="B69" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C69">
         <v>408786.40159999899</v>
@@ -4628,7 +4628,7 @@
         <v>126</v>
       </c>
       <c r="B70" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C70">
         <v>408794.59</v>
@@ -4645,7 +4645,7 @@
         <v>127</v>
       </c>
       <c r="B71" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C71">
         <v>408793.34999999899</v>
@@ -4662,7 +4662,7 @@
         <v>41</v>
       </c>
       <c r="B72" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C72">
         <v>408773.99790000002</v>
@@ -4679,7 +4679,7 @@
         <v>42</v>
       </c>
       <c r="B73" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C73">
         <v>408773.39649999898</v>
@@ -4696,7 +4696,7 @@
         <v>43</v>
       </c>
       <c r="B74" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C74">
         <v>408772.784099999</v>
@@ -4713,7 +4713,7 @@
         <v>44</v>
       </c>
       <c r="B75" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C75">
         <v>408772.17050000001</v>
@@ -4730,7 +4730,7 @@
         <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C76">
         <v>408759.7758</v>
@@ -4747,7 +4747,7 @@
         <v>46</v>
       </c>
       <c r="B77" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C77">
         <v>408759.1692</v>
@@ -4764,7 +4764,7 @@
         <v>47</v>
       </c>
       <c r="B78" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C78">
         <v>408758.57179999899</v>
@@ -4781,7 +4781,7 @@
         <v>48</v>
       </c>
       <c r="B79" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C79">
         <v>408757.959299999</v>
@@ -4798,7 +4798,7 @@
         <v>123</v>
       </c>
       <c r="B80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C80">
         <v>408764.84999999899</v>
@@ -4815,7 +4815,7 @@
         <v>67</v>
       </c>
       <c r="B81" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C81">
         <v>408685.49530000001</v>
@@ -4832,7 +4832,7 @@
         <v>68</v>
       </c>
       <c r="B82" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C82">
         <v>408676.1875</v>
@@ -4849,7 +4849,7 @@
         <v>70</v>
       </c>
       <c r="B83" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C83">
         <v>408673.02689999901</v>
@@ -4866,7 +4866,7 @@
         <v>113</v>
       </c>
       <c r="B84" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C84">
         <v>408680.549999999</v>
@@ -4883,7 +4883,7 @@
         <v>114</v>
       </c>
       <c r="B85" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C85">
         <v>408679.679999999</v>
@@ -4900,7 +4900,7 @@
         <v>115</v>
       </c>
       <c r="B86" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C86">
         <v>408678.72999999899</v>
@@ -4930,211 +4930,211 @@
         <v>100</v>
       </c>
       <c r="C1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D1" t="s">
         <v>113</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>114</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>115</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>116</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>117</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>118</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>119</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>120</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>121</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>122</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>123</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>124</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>125</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>126</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>127</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>128</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>129</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>130</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>131</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>132</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>133</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>134</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>135</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>136</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>137</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>138</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>139</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>140</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>141</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>142</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>143</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>144</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>145</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>146</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>147</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>148</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>149</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>150</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>151</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>152</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>153</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>154</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>155</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>156</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>157</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>158</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>159</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>160</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>161</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>162</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>163</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>164</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>165</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>166</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>167</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>168</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>169</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>170</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>171</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>172</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>173</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>174</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>175</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>176</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>177</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>178</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>179</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>180</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
@@ -26226,211 +26226,211 @@
         <v>112</v>
       </c>
       <c r="C1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D1" t="s">
         <v>113</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>114</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>115</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>116</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>117</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>118</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>119</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>120</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>121</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>122</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>123</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>124</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>125</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>126</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>127</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>128</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>129</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>130</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>131</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>132</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>133</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>134</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>135</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>136</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>137</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>138</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>139</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>140</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>141</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>142</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>143</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>144</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>145</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>146</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>147</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>148</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>149</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>150</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>151</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>152</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>153</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>154</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>155</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>156</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>157</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>158</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>159</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>160</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>161</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>162</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>163</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>164</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>165</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>166</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>167</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>168</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>169</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>170</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>171</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>172</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>173</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>174</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>175</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>176</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>177</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>178</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>179</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>180</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">

--- a/Data/2015_F013B4_CO_ISOS/2015_F013B4_CO_ISOS_SoilAnalysis.xlsx
+++ b/Data/2015_F013B4_CO_ISOS/2015_F013B4_CO_ISOS_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2015_F013B4_CO_ISOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004A9958-4438-4D38-B75F-6B3FC9F38899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5A46FF-5482-4CA6-A7B8-768EF08A13DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1665" yWindow="-25680" windowWidth="27270" windowHeight="17295" xr2:uid="{703BA8F2-5457-4E8B-97CE-55FD3F4AE98B}"/>
+    <workbookView xWindow="-975" yWindow="-24765" windowWidth="17775" windowHeight="24285" xr2:uid="{703BA8F2-5457-4E8B-97CE-55FD3F4AE98B}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDJH" sheetId="4" r:id="rId1"/>
@@ -5202,58 +5202,58 @@
         <v>24.030116</v>
       </c>
       <c r="X2">
-        <v>9.7179000000000001E-2</v>
+        <v>0.15548699999999999</v>
       </c>
       <c r="Y2">
-        <v>0.107957</v>
+        <v>0.173682</v>
       </c>
       <c r="Z2">
-        <v>0.12321500000000001</v>
+        <v>0.19714400000000001</v>
       </c>
       <c r="AA2">
-        <v>0.108789</v>
+        <v>0.174063</v>
       </c>
       <c r="AB2">
-        <v>9.1558E-2</v>
+        <v>0.14649300000000001</v>
       </c>
       <c r="AC2">
-        <v>8.0760999999999999E-2</v>
+        <v>0.12921099999999999</v>
       </c>
       <c r="AD2">
-        <v>0.10753</v>
+        <v>0.17204700000000001</v>
       </c>
       <c r="AE2">
-        <v>0.11884</v>
+        <v>0.19014400000000001</v>
       </c>
       <c r="AF2">
-        <v>0.13208500000000001</v>
+        <v>0.211337</v>
       </c>
       <c r="AG2">
-        <v>0.12156</v>
+        <v>0.194497</v>
       </c>
       <c r="AH2">
-        <v>0.106224</v>
+        <v>0.169849</v>
       </c>
       <c r="AI2">
-        <v>9.1069999999999998E-2</v>
+        <v>0.14679600000000001</v>
       </c>
       <c r="AJ2">
-        <v>0.176341</v>
+        <v>0.28214600000000001</v>
       </c>
       <c r="AK2">
-        <v>0.184891</v>
+        <v>0.29582599999999998</v>
       </c>
       <c r="AL2">
-        <v>0.20402500000000001</v>
+        <v>0.319158</v>
       </c>
       <c r="AM2">
-        <v>0.19641</v>
+        <v>0.30916300000000002</v>
       </c>
       <c r="AN2">
-        <v>0.17178099999999999</v>
+        <v>0.27682499999999999</v>
       </c>
       <c r="AO2">
-        <v>0.161214</v>
+        <v>0.26582299999999998</v>
       </c>
       <c r="AP2">
         <v>57.980710999999999</v>
@@ -5411,58 +5411,58 @@
         <v>23.677059</v>
       </c>
       <c r="X3">
-        <v>9.9682000000000007E-2</v>
+        <v>0.15949099999999999</v>
       </c>
       <c r="Y3">
-        <v>0.111653</v>
+        <v>0.176816</v>
       </c>
       <c r="Z3">
-        <v>0.12137299999999999</v>
+        <v>0.19419700000000001</v>
       </c>
       <c r="AA3">
-        <v>0.109588</v>
+        <v>0.175341</v>
       </c>
       <c r="AB3">
-        <v>9.4585000000000002E-2</v>
+        <v>0.151337</v>
       </c>
       <c r="AC3">
-        <v>8.2350000000000007E-2</v>
+        <v>0.13175500000000001</v>
       </c>
       <c r="AD3">
-        <v>0.109114</v>
+        <v>0.17458199999999999</v>
       </c>
       <c r="AE3">
-        <v>0.119726</v>
+        <v>0.19156200000000001</v>
       </c>
       <c r="AF3">
-        <v>0.129384</v>
+        <v>0.207015</v>
       </c>
       <c r="AG3">
-        <v>0.120893</v>
+        <v>0.19342899999999999</v>
       </c>
       <c r="AH3">
-        <v>0.104573</v>
+        <v>0.16753000000000001</v>
       </c>
       <c r="AI3">
-        <v>9.0669E-2</v>
+        <v>0.14608099999999999</v>
       </c>
       <c r="AJ3">
-        <v>0.17612900000000001</v>
+        <v>0.28180699999999997</v>
       </c>
       <c r="AK3">
-        <v>0.18679499999999999</v>
+        <v>0.29887200000000003</v>
       </c>
       <c r="AL3">
-        <v>0.201318</v>
+        <v>0.31607200000000002</v>
       </c>
       <c r="AM3">
-        <v>0.19376199999999999</v>
+        <v>0.306365</v>
       </c>
       <c r="AN3">
-        <v>0.17105400000000001</v>
+        <v>0.27520699999999998</v>
       </c>
       <c r="AO3">
-        <v>0.15922800000000001</v>
+        <v>0.26347100000000001</v>
       </c>
       <c r="AP3">
         <v>58.133383000000002</v>
@@ -5620,58 +5620,58 @@
         <v>23.443877000000001</v>
       </c>
       <c r="X4">
-        <v>0.10230300000000001</v>
+        <v>0.163684</v>
       </c>
       <c r="Y4">
-        <v>0.113331</v>
+        <v>0.17796999999999999</v>
       </c>
       <c r="Z4">
-        <v>0.113481</v>
+        <v>0.18157000000000001</v>
       </c>
       <c r="AA4">
-        <v>0.10986</v>
+        <v>0.17577499999999999</v>
       </c>
       <c r="AB4">
-        <v>9.8752999999999994E-2</v>
+        <v>0.15800500000000001</v>
       </c>
       <c r="AC4">
-        <v>8.6348999999999995E-2</v>
+        <v>0.138157</v>
       </c>
       <c r="AD4">
-        <v>0.110958</v>
+        <v>0.177533</v>
       </c>
       <c r="AE4">
-        <v>0.11863799999999999</v>
+        <v>0.18981999999999999</v>
       </c>
       <c r="AF4">
-        <v>0.12091499999999999</v>
+        <v>0.193463</v>
       </c>
       <c r="AG4">
-        <v>0.118685</v>
+        <v>0.18989600000000001</v>
       </c>
       <c r="AH4">
-        <v>0.101912</v>
+        <v>0.16370100000000001</v>
       </c>
       <c r="AI4">
-        <v>9.0720999999999996E-2</v>
+        <v>0.14604600000000001</v>
       </c>
       <c r="AJ4">
-        <v>0.18001</v>
+        <v>0.28801700000000002</v>
       </c>
       <c r="AK4">
-        <v>0.186303</v>
+        <v>0.29808400000000002</v>
       </c>
       <c r="AL4">
-        <v>0.192303</v>
+        <v>0.30610300000000001</v>
       </c>
       <c r="AM4">
-        <v>0.18909000000000001</v>
+        <v>0.30118099999999998</v>
       </c>
       <c r="AN4">
-        <v>0.16830600000000001</v>
+        <v>0.27138800000000002</v>
       </c>
       <c r="AO4">
-        <v>0.15775600000000001</v>
+        <v>0.261818</v>
       </c>
       <c r="AP4">
         <v>57.843505999999998</v>
@@ -5829,58 +5829,58 @@
         <v>23.127585</v>
       </c>
       <c r="X5">
-        <v>0.105286</v>
+        <v>0.168459</v>
       </c>
       <c r="Y5">
-        <v>0.11178299999999999</v>
+        <v>0.17522199999999999</v>
       </c>
       <c r="Z5">
-        <v>0.110538</v>
+        <v>0.17685999999999999</v>
       </c>
       <c r="AA5">
-        <v>0.110842</v>
+        <v>0.17734800000000001</v>
       </c>
       <c r="AB5">
-        <v>9.8914000000000002E-2</v>
+        <v>0.15826299999999999</v>
       </c>
       <c r="AC5">
-        <v>8.8599999999999998E-2</v>
+        <v>0.141759</v>
       </c>
       <c r="AD5">
-        <v>0.114203</v>
+        <v>0.182725</v>
       </c>
       <c r="AE5">
-        <v>0.11508500000000001</v>
+        <v>0.18413599999999999</v>
       </c>
       <c r="AF5">
-        <v>0.11515400000000001</v>
+        <v>0.18424599999999999</v>
       </c>
       <c r="AG5">
-        <v>0.11677700000000001</v>
+        <v>0.18684400000000001</v>
       </c>
       <c r="AH5">
-        <v>9.9346000000000004E-2</v>
+        <v>0.159937</v>
       </c>
       <c r="AI5">
-        <v>9.1019000000000003E-2</v>
+        <v>0.14652000000000001</v>
       </c>
       <c r="AJ5">
-        <v>0.18563399999999999</v>
+        <v>0.297014</v>
       </c>
       <c r="AK5">
-        <v>0.184138</v>
+        <v>0.29461999999999999</v>
       </c>
       <c r="AL5">
-        <v>0.18923599999999999</v>
+        <v>0.30243500000000001</v>
       </c>
       <c r="AM5">
-        <v>0.189832</v>
+        <v>0.30128899999999997</v>
       </c>
       <c r="AN5">
-        <v>0.16725200000000001</v>
+        <v>0.26865499999999998</v>
       </c>
       <c r="AO5">
-        <v>0.15793699999999999</v>
+        <v>0.26227200000000001</v>
       </c>
       <c r="AP5">
         <v>56.988582000000001</v>
@@ -6038,58 +6038,58 @@
         <v>22.567706999999999</v>
       </c>
       <c r="X6">
-        <v>0.106226</v>
+        <v>0.169962</v>
       </c>
       <c r="Y6">
-        <v>0.10589700000000001</v>
+        <v>0.16847500000000001</v>
       </c>
       <c r="Z6">
-        <v>0.110975</v>
+        <v>0.17756</v>
       </c>
       <c r="AA6">
-        <v>0.10543</v>
+        <v>0.168688</v>
       </c>
       <c r="AB6">
-        <v>9.6976000000000007E-2</v>
+        <v>0.15516199999999999</v>
       </c>
       <c r="AC6">
-        <v>8.7159E-2</v>
+        <v>0.13945299999999999</v>
       </c>
       <c r="AD6">
-        <v>0.114608</v>
+        <v>0.18337300000000001</v>
       </c>
       <c r="AE6">
-        <v>0.109735</v>
+        <v>0.17557600000000001</v>
       </c>
       <c r="AF6">
-        <v>0.113512</v>
+        <v>0.18162</v>
       </c>
       <c r="AG6">
-        <v>0.11365699999999999</v>
+        <v>0.18185100000000001</v>
       </c>
       <c r="AH6">
-        <v>9.6609E-2</v>
+        <v>0.15591099999999999</v>
       </c>
       <c r="AI6">
-        <v>9.2184000000000002E-2</v>
+        <v>0.14838299999999999</v>
       </c>
       <c r="AJ6">
-        <v>0.18415500000000001</v>
+        <v>0.29464800000000002</v>
       </c>
       <c r="AK6">
-        <v>0.17882799999999999</v>
+        <v>0.28612599999999999</v>
       </c>
       <c r="AL6">
-        <v>0.19034999999999999</v>
+        <v>0.30296000000000001</v>
       </c>
       <c r="AM6">
-        <v>0.184087</v>
+        <v>0.29439100000000001</v>
       </c>
       <c r="AN6">
-        <v>0.164885</v>
+        <v>0.26454899999999998</v>
       </c>
       <c r="AO6">
-        <v>0.160551</v>
+        <v>0.26564900000000002</v>
       </c>
       <c r="AP6">
         <v>56.949894999999998</v>
@@ -6247,58 +6247,58 @@
         <v>22.265611</v>
       </c>
       <c r="X7">
-        <v>0.104703</v>
+        <v>0.16752500000000001</v>
       </c>
       <c r="Y7">
-        <v>9.6038999999999999E-2</v>
+        <v>0.16062100000000001</v>
       </c>
       <c r="Z7">
-        <v>0.10893600000000001</v>
+        <v>0.17429800000000001</v>
       </c>
       <c r="AA7">
-        <v>0.100134</v>
+        <v>0.160214</v>
       </c>
       <c r="AB7">
-        <v>9.2622999999999997E-2</v>
+        <v>0.14819599999999999</v>
       </c>
       <c r="AC7">
-        <v>8.5777999999999993E-2</v>
+        <v>0.137241</v>
       </c>
       <c r="AD7">
-        <v>0.11067399999999999</v>
+        <v>0.17707800000000001</v>
       </c>
       <c r="AE7">
-        <v>0.10401199999999999</v>
+        <v>0.16641900000000001</v>
       </c>
       <c r="AF7">
-        <v>0.111637</v>
+        <v>0.17862</v>
       </c>
       <c r="AG7">
-        <v>0.10735500000000001</v>
+        <v>0.17176900000000001</v>
       </c>
       <c r="AH7">
-        <v>9.3765000000000001E-2</v>
+        <v>0.151838</v>
       </c>
       <c r="AI7">
-        <v>9.5090999999999995E-2</v>
+        <v>0.152813</v>
       </c>
       <c r="AJ7">
-        <v>0.179254</v>
+        <v>0.28680600000000001</v>
       </c>
       <c r="AK7">
-        <v>0.16861999999999999</v>
+        <v>0.269791</v>
       </c>
       <c r="AL7">
-        <v>0.18509500000000001</v>
+        <v>0.29693700000000001</v>
       </c>
       <c r="AM7">
-        <v>0.17483699999999999</v>
+        <v>0.28405799999999998</v>
       </c>
       <c r="AN7">
-        <v>0.156947</v>
+        <v>0.25653799999999999</v>
       </c>
       <c r="AO7">
-        <v>0.16661599999999999</v>
+        <v>0.27262399999999998</v>
       </c>
       <c r="AP7">
         <v>57.241715999999997</v>
@@ -6456,58 +6456,58 @@
         <v>22.431415000000001</v>
       </c>
       <c r="X8">
-        <v>0.105599</v>
+        <v>0.168959</v>
       </c>
       <c r="Y8">
-        <v>9.7483E-2</v>
+        <v>0.16431200000000001</v>
       </c>
       <c r="Z8">
-        <v>0.106063</v>
+        <v>0.16970099999999999</v>
       </c>
       <c r="AA8">
-        <v>9.6311999999999995E-2</v>
+        <v>0.15409900000000001</v>
       </c>
       <c r="AB8">
-        <v>8.5885000000000003E-2</v>
+        <v>0.13741700000000001</v>
       </c>
       <c r="AC8">
-        <v>8.3389000000000005E-2</v>
+        <v>0.13341600000000001</v>
       </c>
       <c r="AD8">
-        <v>0.10932699999999999</v>
+        <v>0.174923</v>
       </c>
       <c r="AE8">
-        <v>0.105239</v>
+        <v>0.168382</v>
       </c>
       <c r="AF8">
-        <v>0.109449</v>
+        <v>0.175118</v>
       </c>
       <c r="AG8">
-        <v>0.102841</v>
+        <v>0.164545</v>
       </c>
       <c r="AH8">
-        <v>9.1664999999999996E-2</v>
+        <v>0.14891199999999999</v>
       </c>
       <c r="AI8">
-        <v>9.8308999999999994E-2</v>
+        <v>0.15784899999999999</v>
       </c>
       <c r="AJ8">
-        <v>0.17750199999999999</v>
+        <v>0.28400300000000001</v>
       </c>
       <c r="AK8">
-        <v>0.167938</v>
+        <v>0.26870100000000002</v>
       </c>
       <c r="AL8">
-        <v>0.179894</v>
+        <v>0.291103</v>
       </c>
       <c r="AM8">
-        <v>0.16956499999999999</v>
+        <v>0.27799800000000002</v>
       </c>
       <c r="AN8">
-        <v>0.15112500000000001</v>
+        <v>0.25132100000000002</v>
       </c>
       <c r="AO8">
-        <v>0.17630399999999999</v>
+        <v>0.283086</v>
       </c>
       <c r="AP8">
         <v>57.254651000000003</v>
@@ -6665,58 +6665,58 @@
         <v>23.175889999999999</v>
       </c>
       <c r="X9">
-        <v>0.10746</v>
+        <v>0.17193700000000001</v>
       </c>
       <c r="Y9">
-        <v>0.113147</v>
+        <v>0.18087</v>
       </c>
       <c r="Z9">
-        <v>0.107111</v>
+        <v>0.171378</v>
       </c>
       <c r="AA9">
-        <v>9.8302E-2</v>
+        <v>0.15728300000000001</v>
       </c>
       <c r="AB9">
-        <v>8.7459999999999996E-2</v>
+        <v>0.139936</v>
       </c>
       <c r="AC9">
-        <v>8.8249999999999995E-2</v>
+        <v>0.14119799999999999</v>
       </c>
       <c r="AD9">
-        <v>0.109764</v>
+        <v>0.175623</v>
       </c>
       <c r="AE9">
-        <v>0.115707</v>
+        <v>0.18513199999999999</v>
       </c>
       <c r="AF9">
-        <v>0.11287999999999999</v>
+        <v>0.18060799999999999</v>
       </c>
       <c r="AG9">
-        <v>0.10430399999999999</v>
+        <v>0.16688700000000001</v>
       </c>
       <c r="AH9">
-        <v>9.3441999999999997E-2</v>
+        <v>0.15135799999999999</v>
       </c>
       <c r="AI9">
-        <v>0.103021</v>
+        <v>0.164969</v>
       </c>
       <c r="AJ9">
-        <v>0.17943600000000001</v>
+        <v>0.28709699999999999</v>
       </c>
       <c r="AK9">
-        <v>0.184228</v>
+        <v>0.294765</v>
       </c>
       <c r="AL9">
-        <v>0.18121399999999999</v>
+        <v>0.29264200000000001</v>
       </c>
       <c r="AM9">
-        <v>0.170794</v>
+        <v>0.27917599999999998</v>
       </c>
       <c r="AN9">
-        <v>0.15571099999999999</v>
+        <v>0.255631</v>
       </c>
       <c r="AO9">
-        <v>0.18764600000000001</v>
+        <v>0.29485600000000001</v>
       </c>
       <c r="AP9">
         <v>57.131756000000003</v>
@@ -6874,58 +6874,58 @@
         <v>24.247035</v>
       </c>
       <c r="X10">
-        <v>0.108019</v>
+        <v>0.17283100000000001</v>
       </c>
       <c r="Y10">
-        <v>0.132082</v>
+        <v>0.199849</v>
       </c>
       <c r="Z10">
-        <v>0.116798</v>
+        <v>0.18687799999999999</v>
       </c>
       <c r="AA10">
-        <v>0.102156</v>
+        <v>0.16344900000000001</v>
       </c>
       <c r="AB10">
-        <v>9.3371999999999997E-2</v>
+        <v>0.149396</v>
       </c>
       <c r="AC10">
-        <v>9.8806000000000005E-2</v>
+        <v>0.15809400000000001</v>
       </c>
       <c r="AD10">
-        <v>0.109472</v>
+        <v>0.17515500000000001</v>
       </c>
       <c r="AE10">
-        <v>0.12882199999999999</v>
+        <v>0.20611499999999999</v>
       </c>
       <c r="AF10">
-        <v>0.12458</v>
+        <v>0.19932900000000001</v>
       </c>
       <c r="AG10">
-        <v>0.10478999999999999</v>
+        <v>0.16766500000000001</v>
       </c>
       <c r="AH10">
-        <v>9.7567000000000001E-2</v>
+        <v>0.157139</v>
       </c>
       <c r="AI10">
-        <v>0.10874300000000001</v>
+        <v>0.17339199999999999</v>
       </c>
       <c r="AJ10">
-        <v>0.18168599999999999</v>
+        <v>0.29069800000000001</v>
       </c>
       <c r="AK10">
-        <v>0.20189799999999999</v>
+        <v>0.32303700000000002</v>
       </c>
       <c r="AL10">
-        <v>0.19517899999999999</v>
+        <v>0.30766300000000002</v>
       </c>
       <c r="AM10">
-        <v>0.177649</v>
+        <v>0.28662100000000001</v>
       </c>
       <c r="AN10">
-        <v>0.16469900000000001</v>
+        <v>0.264517</v>
       </c>
       <c r="AO10">
-        <v>0.19445000000000001</v>
+        <v>0.30254500000000001</v>
       </c>
       <c r="AP10">
         <v>57.536451999999997</v>
@@ -7083,58 +7083,58 @@
         <v>25.136866000000001</v>
       </c>
       <c r="X11">
-        <v>0.106956</v>
+        <v>0.17113100000000001</v>
       </c>
       <c r="Y11">
-        <v>0.13483200000000001</v>
+        <v>0.20467399999999999</v>
       </c>
       <c r="Z11">
-        <v>0.118258</v>
+        <v>0.18921299999999999</v>
       </c>
       <c r="AA11">
-        <v>0.101006</v>
+        <v>0.161609</v>
       </c>
       <c r="AB11">
-        <v>9.4973000000000002E-2</v>
+        <v>0.15195600000000001</v>
       </c>
       <c r="AC11">
-        <v>0.103542</v>
+        <v>0.16567399999999999</v>
       </c>
       <c r="AD11">
-        <v>0.108335</v>
+        <v>0.17333599999999999</v>
       </c>
       <c r="AE11">
-        <v>0.132628</v>
+        <v>0.212205</v>
       </c>
       <c r="AF11">
-        <v>0.12837399999999999</v>
+        <v>0.205399</v>
       </c>
       <c r="AG11">
-        <v>0.101974</v>
+        <v>0.163158</v>
       </c>
       <c r="AH11">
-        <v>9.9990999999999997E-2</v>
+        <v>0.16058600000000001</v>
       </c>
       <c r="AI11">
-        <v>0.111454</v>
+        <v>0.177426</v>
       </c>
       <c r="AJ11">
-        <v>0.18000099999999999</v>
+        <v>0.28800100000000001</v>
       </c>
       <c r="AK11">
-        <v>0.20296700000000001</v>
+        <v>0.32474799999999998</v>
       </c>
       <c r="AL11">
-        <v>0.197215</v>
+        <v>0.31009100000000001</v>
       </c>
       <c r="AM11">
-        <v>0.17916799999999999</v>
+        <v>0.28851199999999999</v>
       </c>
       <c r="AN11">
-        <v>0.168821</v>
+        <v>0.26926800000000001</v>
       </c>
       <c r="AO11">
-        <v>0.19558500000000001</v>
+        <v>0.30459999999999998</v>
       </c>
       <c r="AP11">
         <v>57.725347999999997</v>
@@ -7295,58 +7295,58 @@
         <v>24.533000999999999</v>
       </c>
       <c r="X12">
-        <v>9.7457000000000002E-2</v>
+        <v>0.15593000000000001</v>
       </c>
       <c r="Y12">
-        <v>0.112441</v>
+        <v>0.17513400000000001</v>
       </c>
       <c r="Z12">
-        <v>0.12575800000000001</v>
+        <v>0.201213</v>
       </c>
       <c r="AA12">
-        <v>0.112039</v>
+        <v>0.17926300000000001</v>
       </c>
       <c r="AB12">
-        <v>9.8841999999999999E-2</v>
+        <v>0.15814700000000001</v>
       </c>
       <c r="AC12">
-        <v>8.5773000000000002E-2</v>
+        <v>0.13723299999999999</v>
       </c>
       <c r="AD12">
-        <v>0.108696</v>
+        <v>0.17391300000000001</v>
       </c>
       <c r="AE12">
-        <v>0.123193</v>
+        <v>0.19710900000000001</v>
       </c>
       <c r="AF12">
-        <v>0.14050499999999999</v>
+        <v>0.22480700000000001</v>
       </c>
       <c r="AG12">
-        <v>0.12851899999999999</v>
+        <v>0.20563000000000001</v>
       </c>
       <c r="AH12">
-        <v>0.11222</v>
+        <v>0.178286</v>
       </c>
       <c r="AI12">
-        <v>9.7850000000000006E-2</v>
+        <v>0.156524</v>
       </c>
       <c r="AJ12">
-        <v>0.17521200000000001</v>
+        <v>0.28033999999999998</v>
       </c>
       <c r="AK12">
-        <v>0.18757799999999999</v>
+        <v>0.30012499999999998</v>
       </c>
       <c r="AL12">
-        <v>0.208119</v>
+        <v>0.32410899999999998</v>
       </c>
       <c r="AM12">
-        <v>0.20583499999999999</v>
+        <v>0.31969399999999998</v>
       </c>
       <c r="AN12">
-        <v>0.183863</v>
+        <v>0.29109699999999999</v>
       </c>
       <c r="AO12">
-        <v>0.168577</v>
+        <v>0.27277800000000002</v>
       </c>
       <c r="AP12">
         <v>56.238022999999998</v>
@@ -7507,58 +7507,58 @@
         <v>24.245497</v>
       </c>
       <c r="X13">
-        <v>9.9060999999999996E-2</v>
+        <v>0.158498</v>
       </c>
       <c r="Y13">
-        <v>0.10874399999999999</v>
+        <v>0.17124900000000001</v>
       </c>
       <c r="Z13">
-        <v>0.12762699999999999</v>
+        <v>0.204204</v>
       </c>
       <c r="AA13">
-        <v>0.114719</v>
+        <v>0.18355099999999999</v>
       </c>
       <c r="AB13">
-        <v>0.100368</v>
+        <v>0.16058900000000001</v>
       </c>
       <c r="AC13">
-        <v>8.4696999999999995E-2</v>
+        <v>0.13550999999999999</v>
       </c>
       <c r="AD13">
-        <v>0.110235</v>
+        <v>0.17637700000000001</v>
       </c>
       <c r="AE13">
-        <v>0.11920699999999999</v>
+        <v>0.19073100000000001</v>
       </c>
       <c r="AF13">
-        <v>0.14186599999999999</v>
+        <v>0.22698499999999999</v>
       </c>
       <c r="AG13">
-        <v>0.12842200000000001</v>
+        <v>0.20547499999999999</v>
       </c>
       <c r="AH13">
-        <v>0.111858</v>
+        <v>0.177759</v>
       </c>
       <c r="AI13">
-        <v>9.6658999999999995E-2</v>
+        <v>0.15472900000000001</v>
       </c>
       <c r="AJ13">
-        <v>0.17795900000000001</v>
+        <v>0.28473399999999999</v>
       </c>
       <c r="AK13">
-        <v>0.18246799999999999</v>
+        <v>0.29194900000000001</v>
       </c>
       <c r="AL13">
-        <v>0.208396</v>
+        <v>0.32422600000000001</v>
       </c>
       <c r="AM13">
-        <v>0.20497599999999999</v>
+        <v>0.31882700000000003</v>
       </c>
       <c r="AN13">
-        <v>0.18416299999999999</v>
+        <v>0.29044599999999998</v>
       </c>
       <c r="AO13">
-        <v>0.16555300000000001</v>
+        <v>0.26951599999999998</v>
       </c>
       <c r="AP13">
         <v>56.133251000000001</v>
@@ -7719,58 +7719,58 @@
         <v>23.826983999999999</v>
       </c>
       <c r="X14">
-        <v>0.100064</v>
+        <v>0.16010199999999999</v>
       </c>
       <c r="Y14">
-        <v>0.10023</v>
+        <v>0.16272300000000001</v>
       </c>
       <c r="Z14">
-        <v>0.122833</v>
+        <v>0.19653399999999999</v>
       </c>
       <c r="AA14">
-        <v>0.114716</v>
+        <v>0.18354599999999999</v>
       </c>
       <c r="AB14">
-        <v>9.8990999999999996E-2</v>
+        <v>0.158385</v>
       </c>
       <c r="AC14">
-        <v>8.6315000000000003E-2</v>
+        <v>0.138101</v>
       </c>
       <c r="AD14">
-        <v>0.111593</v>
+        <v>0.17854900000000001</v>
       </c>
       <c r="AE14">
-        <v>0.111981</v>
+        <v>0.17916899999999999</v>
       </c>
       <c r="AF14">
-        <v>0.137985</v>
+        <v>0.220776</v>
       </c>
       <c r="AG14">
-        <v>0.127772</v>
+        <v>0.20443600000000001</v>
       </c>
       <c r="AH14">
-        <v>0.10909000000000001</v>
+        <v>0.173762</v>
       </c>
       <c r="AI14">
-        <v>9.4879000000000005E-2</v>
+        <v>0.152086</v>
       </c>
       <c r="AJ14">
-        <v>0.18022299999999999</v>
+        <v>0.28835699999999997</v>
       </c>
       <c r="AK14">
-        <v>0.17019200000000001</v>
+        <v>0.27230799999999999</v>
       </c>
       <c r="AL14">
-        <v>0.20239499999999999</v>
+        <v>0.31745200000000001</v>
       </c>
       <c r="AM14">
-        <v>0.19867699999999999</v>
+        <v>0.312033</v>
       </c>
       <c r="AN14">
-        <v>0.18015800000000001</v>
+        <v>0.28509499999999999</v>
       </c>
       <c r="AO14">
-        <v>0.161355</v>
+        <v>0.26532600000000001</v>
       </c>
       <c r="AP14">
         <v>55.843401</v>
@@ -7931,58 +7931,58 @@
         <v>23.093637000000001</v>
       </c>
       <c r="X15">
-        <v>9.8984000000000003E-2</v>
+        <v>0.15837399999999999</v>
       </c>
       <c r="Y15">
-        <v>9.7742999999999997E-2</v>
+        <v>0.15834899999999999</v>
       </c>
       <c r="Z15">
-        <v>0.113606</v>
+        <v>0.18176899999999999</v>
       </c>
       <c r="AA15">
-        <v>0.108045</v>
+        <v>0.172872</v>
       </c>
       <c r="AB15">
-        <v>9.5749000000000001E-2</v>
+        <v>0.153199</v>
       </c>
       <c r="AC15">
-        <v>8.4295999999999996E-2</v>
+        <v>0.13486799999999999</v>
       </c>
       <c r="AD15">
-        <v>0.110594</v>
+        <v>0.17695</v>
       </c>
       <c r="AE15">
-        <v>0.107943</v>
+        <v>0.172708</v>
       </c>
       <c r="AF15">
-        <v>0.127724</v>
+        <v>0.20435800000000001</v>
       </c>
       <c r="AG15">
-        <v>0.121295</v>
+        <v>0.19407199999999999</v>
       </c>
       <c r="AH15">
-        <v>0.10370799999999999</v>
+        <v>0.16608500000000001</v>
       </c>
       <c r="AI15">
-        <v>9.2737E-2</v>
+        <v>0.14913699999999999</v>
       </c>
       <c r="AJ15">
-        <v>0.17815500000000001</v>
+        <v>0.285049</v>
       </c>
       <c r="AK15">
-        <v>0.16777300000000001</v>
+        <v>0.26843699999999998</v>
       </c>
       <c r="AL15">
-        <v>0.19470199999999999</v>
+        <v>0.308388</v>
       </c>
       <c r="AM15">
-        <v>0.19367100000000001</v>
+        <v>0.305589</v>
       </c>
       <c r="AN15">
-        <v>0.173041</v>
+        <v>0.27649499999999999</v>
       </c>
       <c r="AO15">
-        <v>0.15876399999999999</v>
+        <v>0.26329900000000001</v>
       </c>
       <c r="AP15">
         <v>55.270803999999998</v>
@@ -8143,58 +8143,58 @@
         <v>22.386551000000001</v>
       </c>
       <c r="X16">
-        <v>9.6008999999999997E-2</v>
+        <v>0.153613</v>
       </c>
       <c r="Y16">
-        <v>9.5609E-2</v>
+        <v>0.15456</v>
       </c>
       <c r="Z16">
-        <v>0.10324700000000001</v>
+        <v>0.16519500000000001</v>
       </c>
       <c r="AA16">
-        <v>9.9139000000000005E-2</v>
+        <v>0.15862200000000001</v>
       </c>
       <c r="AB16">
-        <v>9.0049000000000004E-2</v>
+        <v>0.14407900000000001</v>
       </c>
       <c r="AC16">
-        <v>8.5304000000000005E-2</v>
+        <v>0.13648199999999999</v>
       </c>
       <c r="AD16">
-        <v>0.10766299999999999</v>
+        <v>0.172261</v>
       </c>
       <c r="AE16">
-        <v>0.10560899999999999</v>
+        <v>0.16897400000000001</v>
       </c>
       <c r="AF16">
-        <v>0.115841</v>
+        <v>0.18534500000000001</v>
       </c>
       <c r="AG16">
-        <v>0.111468</v>
+        <v>0.17834900000000001</v>
       </c>
       <c r="AH16">
-        <v>9.7498000000000001E-2</v>
+        <v>0.157245</v>
       </c>
       <c r="AI16">
-        <v>9.3814999999999996E-2</v>
+        <v>0.15078800000000001</v>
       </c>
       <c r="AJ16">
-        <v>0.17403199999999999</v>
+        <v>0.278451</v>
       </c>
       <c r="AK16">
-        <v>0.16939599999999999</v>
+        <v>0.271034</v>
       </c>
       <c r="AL16">
-        <v>0.182809</v>
+        <v>0.29465599999999997</v>
       </c>
       <c r="AM16">
-        <v>0.18229799999999999</v>
+        <v>0.29235</v>
       </c>
       <c r="AN16">
-        <v>0.16372700000000001</v>
+        <v>0.26596799999999998</v>
       </c>
       <c r="AO16">
-        <v>0.160936</v>
+        <v>0.26610800000000001</v>
       </c>
       <c r="AP16">
         <v>55.355507000000003</v>
@@ -8355,58 +8355,58 @@
         <v>22.009188000000002</v>
       </c>
       <c r="X17">
-        <v>9.4925999999999996E-2</v>
+        <v>0.15187999999999999</v>
       </c>
       <c r="Y17">
-        <v>9.0568999999999997E-2</v>
+        <v>0.15066299999999999</v>
       </c>
       <c r="Z17">
-        <v>9.7660999999999998E-2</v>
+        <v>0.15625800000000001</v>
       </c>
       <c r="AA17">
-        <v>9.4380000000000006E-2</v>
+        <v>0.151008</v>
       </c>
       <c r="AB17">
-        <v>8.8095000000000007E-2</v>
+        <v>0.14095199999999999</v>
       </c>
       <c r="AC17">
-        <v>8.9242000000000002E-2</v>
+        <v>0.142787</v>
       </c>
       <c r="AD17">
-        <v>0.106239</v>
+        <v>0.169983</v>
       </c>
       <c r="AE17">
-        <v>0.103627</v>
+        <v>0.16580400000000001</v>
       </c>
       <c r="AF17">
-        <v>0.110429</v>
+        <v>0.17668600000000001</v>
       </c>
       <c r="AG17">
-        <v>0.105975</v>
+        <v>0.16956099999999999</v>
       </c>
       <c r="AH17">
-        <v>9.4117000000000006E-2</v>
+        <v>0.152367</v>
       </c>
       <c r="AI17">
-        <v>9.7314999999999999E-2</v>
+        <v>0.15601100000000001</v>
       </c>
       <c r="AJ17">
-        <v>0.17236199999999999</v>
+        <v>0.27577800000000002</v>
       </c>
       <c r="AK17">
-        <v>0.164076</v>
+        <v>0.26252199999999998</v>
       </c>
       <c r="AL17">
-        <v>0.175874</v>
+        <v>0.28686400000000001</v>
       </c>
       <c r="AM17">
-        <v>0.173481</v>
+        <v>0.282333</v>
       </c>
       <c r="AN17">
-        <v>0.157004</v>
+        <v>0.25838800000000001</v>
       </c>
       <c r="AO17">
-        <v>0.16672200000000001</v>
+        <v>0.27279700000000001</v>
       </c>
       <c r="AP17">
         <v>55.978386999999998</v>
@@ -8567,58 +8567,58 @@
         <v>22.058318</v>
       </c>
       <c r="X18">
-        <v>9.7943000000000002E-2</v>
+        <v>0.15670799999999999</v>
       </c>
       <c r="Y18">
-        <v>9.894E-2</v>
+        <v>0.15954599999999999</v>
       </c>
       <c r="Z18">
-        <v>0.102418</v>
+        <v>0.16386899999999999</v>
       </c>
       <c r="AA18">
-        <v>9.554E-2</v>
+        <v>0.152864</v>
       </c>
       <c r="AB18">
-        <v>8.9147000000000004E-2</v>
+        <v>0.14263500000000001</v>
       </c>
       <c r="AC18">
-        <v>8.7166999999999994E-2</v>
+        <v>0.139464</v>
       </c>
       <c r="AD18">
-        <v>0.108095</v>
+        <v>0.17295199999999999</v>
       </c>
       <c r="AE18">
-        <v>0.11022800000000001</v>
+        <v>0.17636399999999999</v>
       </c>
       <c r="AF18">
-        <v>0.116794</v>
+        <v>0.18687000000000001</v>
       </c>
       <c r="AG18">
-        <v>0.10947800000000001</v>
+        <v>0.17516399999999999</v>
       </c>
       <c r="AH18">
-        <v>9.4694E-2</v>
+        <v>0.153027</v>
       </c>
       <c r="AI18">
-        <v>0.100456</v>
+        <v>0.16103500000000001</v>
       </c>
       <c r="AJ18">
-        <v>0.169736</v>
+        <v>0.27157799999999999</v>
       </c>
       <c r="AK18">
-        <v>0.16977</v>
+        <v>0.27163199999999998</v>
       </c>
       <c r="AL18">
-        <v>0.18647900000000001</v>
+        <v>0.29837200000000003</v>
       </c>
       <c r="AM18">
-        <v>0.17959900000000001</v>
+        <v>0.28828700000000002</v>
       </c>
       <c r="AN18">
-        <v>0.15840000000000001</v>
+        <v>0.25855299999999998</v>
       </c>
       <c r="AO18">
-        <v>0.17336699999999999</v>
+        <v>0.28092200000000001</v>
       </c>
       <c r="AP18">
         <v>56.828186000000002</v>
@@ -8779,58 +8779,58 @@
         <v>22.537140000000001</v>
       </c>
       <c r="X19">
-        <v>0.102356</v>
+        <v>0.163769</v>
       </c>
       <c r="Y19">
-        <v>0.110428</v>
+        <v>0.173259</v>
       </c>
       <c r="Z19">
-        <v>0.106284</v>
+        <v>0.17005400000000001</v>
       </c>
       <c r="AA19">
-        <v>9.9740999999999996E-2</v>
+        <v>0.159585</v>
       </c>
       <c r="AB19">
-        <v>9.0737999999999999E-2</v>
+        <v>0.145181</v>
       </c>
       <c r="AC19">
-        <v>8.8761999999999994E-2</v>
+        <v>0.142016</v>
       </c>
       <c r="AD19">
-        <v>0.10976</v>
+        <v>0.17561499999999999</v>
       </c>
       <c r="AE19">
-        <v>0.119861</v>
+        <v>0.191778</v>
       </c>
       <c r="AF19">
-        <v>0.12236900000000001</v>
+        <v>0.19578999999999999</v>
       </c>
       <c r="AG19">
-        <v>0.112967</v>
+        <v>0.18074799999999999</v>
       </c>
       <c r="AH19">
-        <v>9.7407999999999995E-2</v>
+        <v>0.156748</v>
       </c>
       <c r="AI19">
-        <v>0.10487100000000001</v>
+        <v>0.16791</v>
       </c>
       <c r="AJ19">
-        <v>0.16983000000000001</v>
+        <v>0.27172800000000003</v>
       </c>
       <c r="AK19">
-        <v>0.184693</v>
+        <v>0.29550900000000002</v>
       </c>
       <c r="AL19">
-        <v>0.19531499999999999</v>
+        <v>0.308286</v>
       </c>
       <c r="AM19">
-        <v>0.18371599999999999</v>
+        <v>0.29292899999999999</v>
       </c>
       <c r="AN19">
-        <v>0.16328300000000001</v>
+        <v>0.262907</v>
       </c>
       <c r="AO19">
-        <v>0.180895</v>
+        <v>0.28986000000000001</v>
       </c>
       <c r="AP19">
         <v>57.541859000000002</v>
@@ -8991,58 +8991,58 @@
         <v>23.808674</v>
       </c>
       <c r="X20">
-        <v>0.10567</v>
+        <v>0.169072</v>
       </c>
       <c r="Y20">
-        <v>0.115193</v>
+        <v>0.18246699999999999</v>
       </c>
       <c r="Z20">
-        <v>0.111138</v>
+        <v>0.17782100000000001</v>
       </c>
       <c r="AA20">
-        <v>0.10718999999999999</v>
+        <v>0.17150399999999999</v>
       </c>
       <c r="AB20">
-        <v>9.4894000000000006E-2</v>
+        <v>0.15182999999999999</v>
       </c>
       <c r="AC20">
-        <v>9.6067E-2</v>
+        <v>0.15370800000000001</v>
       </c>
       <c r="AD20">
-        <v>0.113636</v>
+        <v>0.18181700000000001</v>
       </c>
       <c r="AE20">
-        <v>0.125254</v>
+        <v>0.200407</v>
       </c>
       <c r="AF20">
-        <v>0.123741</v>
+        <v>0.197986</v>
       </c>
       <c r="AG20">
-        <v>0.113825</v>
+        <v>0.182119</v>
       </c>
       <c r="AH20">
-        <v>0.101276</v>
+        <v>0.16217899999999999</v>
       </c>
       <c r="AI20">
-        <v>0.11115</v>
+        <v>0.177263</v>
       </c>
       <c r="AJ20">
-        <v>0.178256</v>
+        <v>0.28520899999999999</v>
       </c>
       <c r="AK20">
-        <v>0.193136</v>
+        <v>0.30901800000000001</v>
       </c>
       <c r="AL20">
-        <v>0.19705500000000001</v>
+        <v>0.31072</v>
       </c>
       <c r="AM20">
-        <v>0.18528</v>
+        <v>0.29532000000000003</v>
       </c>
       <c r="AN20">
-        <v>0.167763</v>
+        <v>0.26796199999999998</v>
       </c>
       <c r="AO20">
-        <v>0.18862200000000001</v>
+        <v>0.29857600000000001</v>
       </c>
       <c r="AP20">
         <v>58.118811999999998</v>
@@ -9203,58 +9203,58 @@
         <v>25.090720999999998</v>
       </c>
       <c r="X21">
-        <v>0.105088</v>
+        <v>0.16814100000000001</v>
       </c>
       <c r="Y21">
-        <v>0.11598600000000001</v>
+        <v>0.18604699999999999</v>
       </c>
       <c r="Z21">
-        <v>0.11214300000000001</v>
+        <v>0.17943000000000001</v>
       </c>
       <c r="AA21">
-        <v>0.108061</v>
+        <v>0.172897</v>
       </c>
       <c r="AB21">
-        <v>9.7497E-2</v>
+        <v>0.15599499999999999</v>
       </c>
       <c r="AC21">
-        <v>0.102259</v>
+        <v>0.16361899999999999</v>
       </c>
       <c r="AD21">
-        <v>0.11453000000000001</v>
+        <v>0.18324799999999999</v>
       </c>
       <c r="AE21">
-        <v>0.12650900000000001</v>
+        <v>0.20241400000000001</v>
       </c>
       <c r="AF21">
-        <v>0.123947</v>
+        <v>0.19831599999999999</v>
       </c>
       <c r="AG21">
-        <v>0.113653</v>
+        <v>0.18184500000000001</v>
       </c>
       <c r="AH21">
-        <v>0.104195</v>
+        <v>0.166295</v>
       </c>
       <c r="AI21">
-        <v>0.11611399999999999</v>
+        <v>0.18443999999999999</v>
       </c>
       <c r="AJ21">
-        <v>0.18077299999999999</v>
+        <v>0.28923700000000002</v>
       </c>
       <c r="AK21">
-        <v>0.19278300000000001</v>
+        <v>0.308452</v>
       </c>
       <c r="AL21">
-        <v>0.19730800000000001</v>
+        <v>0.31128</v>
       </c>
       <c r="AM21">
-        <v>0.18831600000000001</v>
+        <v>0.29877100000000001</v>
       </c>
       <c r="AN21">
-        <v>0.17182</v>
+        <v>0.27251599999999998</v>
       </c>
       <c r="AO21">
-        <v>0.194492</v>
+        <v>0.30464200000000002</v>
       </c>
       <c r="AP21">
         <v>57.704504</v>
@@ -9412,58 +9412,58 @@
         <v>25.995097999999999</v>
       </c>
       <c r="X22">
-        <v>9.9321999999999994E-2</v>
+        <v>0.158915</v>
       </c>
       <c r="Y22">
-        <v>0.102172</v>
+        <v>0.16323399999999999</v>
       </c>
       <c r="Z22">
-        <v>0.122331</v>
+        <v>0.19572999999999999</v>
       </c>
       <c r="AA22">
-        <v>0.112028</v>
+        <v>0.17924399999999999</v>
       </c>
       <c r="AB22">
-        <v>0.100451</v>
+        <v>0.160722</v>
       </c>
       <c r="AC22">
-        <v>9.4363000000000002E-2</v>
+        <v>0.15098400000000001</v>
       </c>
       <c r="AD22">
-        <v>0.108419</v>
+        <v>0.17347099999999999</v>
       </c>
       <c r="AE22">
-        <v>0.11360199999999999</v>
+        <v>0.18176400000000001</v>
       </c>
       <c r="AF22">
-        <v>0.134413</v>
+        <v>0.215061</v>
       </c>
       <c r="AG22">
-        <v>0.122215</v>
+        <v>0.195545</v>
       </c>
       <c r="AH22">
-        <v>0.114832</v>
+        <v>0.182204</v>
       </c>
       <c r="AI22">
-        <v>0.103494</v>
+        <v>0.16478699999999999</v>
       </c>
       <c r="AJ22">
-        <v>0.17446999999999999</v>
+        <v>0.27915200000000001</v>
       </c>
       <c r="AK22">
-        <v>0.1762</v>
+        <v>0.28191899999999998</v>
       </c>
       <c r="AL22">
-        <v>0.20649899999999999</v>
+        <v>0.32230700000000001</v>
       </c>
       <c r="AM22">
-        <v>0.197074</v>
+        <v>0.31104199999999999</v>
       </c>
       <c r="AN22">
-        <v>0.19193399999999999</v>
+        <v>0.30180699999999999</v>
       </c>
       <c r="AO22">
-        <v>0.17970900000000001</v>
+        <v>0.28426800000000002</v>
       </c>
       <c r="AP22">
         <v>54.396189</v>
@@ -9621,58 +9621,58 @@
         <v>25.591555</v>
       </c>
       <c r="X23">
-        <v>0.10069</v>
+        <v>0.161104</v>
       </c>
       <c r="Y23">
-        <v>0.100171</v>
+        <v>0.16053600000000001</v>
       </c>
       <c r="Z23">
-        <v>0.123153</v>
+        <v>0.197044</v>
       </c>
       <c r="AA23">
-        <v>0.11368499999999999</v>
+        <v>0.181896</v>
       </c>
       <c r="AB23">
-        <v>0.100523</v>
+        <v>0.16083600000000001</v>
       </c>
       <c r="AC23">
-        <v>9.1996999999999995E-2</v>
+        <v>0.14719599999999999</v>
       </c>
       <c r="AD23">
-        <v>0.10960300000000001</v>
+        <v>0.17536499999999999</v>
       </c>
       <c r="AE23">
-        <v>0.110856</v>
+        <v>0.17737</v>
       </c>
       <c r="AF23">
-        <v>0.13472300000000001</v>
+        <v>0.215556</v>
       </c>
       <c r="AG23">
-        <v>0.12393899999999999</v>
+        <v>0.19830200000000001</v>
       </c>
       <c r="AH23">
-        <v>0.114359</v>
+        <v>0.18157799999999999</v>
       </c>
       <c r="AI23">
-        <v>0.101701</v>
+        <v>0.16214600000000001</v>
       </c>
       <c r="AJ23">
-        <v>0.176346</v>
+        <v>0.28215299999999999</v>
       </c>
       <c r="AK23">
-        <v>0.17365700000000001</v>
+        <v>0.27785100000000001</v>
       </c>
       <c r="AL23">
-        <v>0.20275799999999999</v>
+        <v>0.31810899999999998</v>
       </c>
       <c r="AM23">
-        <v>0.201289</v>
+        <v>0.31545499999999999</v>
       </c>
       <c r="AN23">
-        <v>0.191195</v>
+        <v>0.30032999999999999</v>
       </c>
       <c r="AO23">
-        <v>0.17583499999999999</v>
+        <v>0.28032000000000001</v>
       </c>
       <c r="AP23">
         <v>54.121915999999999</v>
@@ -9830,58 +9830,58 @@
         <v>24.798449000000002</v>
       </c>
       <c r="X24">
-        <v>0.10170700000000001</v>
+        <v>0.16273199999999999</v>
       </c>
       <c r="Y24">
-        <v>9.6000000000000002E-2</v>
+        <v>0.155833</v>
       </c>
       <c r="Z24">
-        <v>0.121174</v>
+        <v>0.19387799999999999</v>
       </c>
       <c r="AA24">
-        <v>0.113596</v>
+        <v>0.181753</v>
       </c>
       <c r="AB24">
-        <v>9.7458000000000003E-2</v>
+        <v>0.15593299999999999</v>
       </c>
       <c r="AC24">
-        <v>8.9205000000000007E-2</v>
+        <v>0.14272499999999999</v>
       </c>
       <c r="AD24">
-        <v>0.11211500000000001</v>
+        <v>0.17938399999999999</v>
       </c>
       <c r="AE24">
-        <v>0.1085</v>
+        <v>0.1736</v>
       </c>
       <c r="AF24">
-        <v>0.13444300000000001</v>
+        <v>0.21510899999999999</v>
       </c>
       <c r="AG24">
-        <v>0.124898</v>
+        <v>0.19983699999999999</v>
       </c>
       <c r="AH24">
-        <v>0.111786</v>
+        <v>0.17790700000000001</v>
       </c>
       <c r="AI24">
-        <v>9.8806000000000005E-2</v>
+        <v>0.15794800000000001</v>
       </c>
       <c r="AJ24">
-        <v>0.18063399999999999</v>
+        <v>0.28901399999999999</v>
       </c>
       <c r="AK24">
-        <v>0.16833899999999999</v>
+        <v>0.26934200000000003</v>
       </c>
       <c r="AL24">
-        <v>0.19945499999999999</v>
+        <v>0.31414799999999998</v>
       </c>
       <c r="AM24">
-        <v>0.20170199999999999</v>
+        <v>0.31587700000000002</v>
       </c>
       <c r="AN24">
-        <v>0.185778</v>
+        <v>0.29392200000000002</v>
       </c>
       <c r="AO24">
-        <v>0.16942699999999999</v>
+        <v>0.27429799999999999</v>
       </c>
       <c r="AP24">
         <v>54.143588999999999</v>
@@ -10039,58 +10039,58 @@
         <v>23.954070000000002</v>
       </c>
       <c r="X25">
-        <v>0.101301</v>
+        <v>0.162081</v>
       </c>
       <c r="Y25">
-        <v>9.4792000000000001E-2</v>
+        <v>0.15349399999999999</v>
       </c>
       <c r="Z25">
-        <v>0.116629</v>
+        <v>0.186607</v>
       </c>
       <c r="AA25">
-        <v>0.10950500000000001</v>
+        <v>0.175209</v>
       </c>
       <c r="AB25">
-        <v>9.5098000000000002E-2</v>
+        <v>0.15215699999999999</v>
       </c>
       <c r="AC25">
-        <v>9.4103999999999993E-2</v>
+        <v>0.15056800000000001</v>
       </c>
       <c r="AD25">
-        <v>0.11306099999999999</v>
+        <v>0.180898</v>
       </c>
       <c r="AE25">
-        <v>0.107909</v>
+        <v>0.172654</v>
       </c>
       <c r="AF25">
-        <v>0.13070000000000001</v>
+        <v>0.209121</v>
       </c>
       <c r="AG25">
-        <v>0.119847</v>
+        <v>0.19175600000000001</v>
       </c>
       <c r="AH25">
-        <v>0.10780099999999999</v>
+        <v>0.17216699999999999</v>
       </c>
       <c r="AI25">
-        <v>9.5910999999999996E-2</v>
+        <v>0.153889</v>
       </c>
       <c r="AJ25">
-        <v>0.18077199999999999</v>
+        <v>0.28923500000000002</v>
       </c>
       <c r="AK25">
-        <v>0.168881</v>
+        <v>0.27020899999999998</v>
       </c>
       <c r="AL25">
-        <v>0.20047999999999999</v>
+        <v>0.31472499999999998</v>
       </c>
       <c r="AM25">
-        <v>0.19490099999999999</v>
+        <v>0.30764999999999998</v>
       </c>
       <c r="AN25">
-        <v>0.17820800000000001</v>
+        <v>0.28503400000000001</v>
       </c>
       <c r="AO25">
-        <v>0.16581199999999999</v>
+        <v>0.271254</v>
       </c>
       <c r="AP25">
         <v>54.200412</v>
@@ -10248,58 +10248,58 @@
         <v>23.462899</v>
       </c>
       <c r="X26">
-        <v>9.8826999999999998E-2</v>
+        <v>0.15812300000000001</v>
       </c>
       <c r="Y26">
-        <v>9.4506999999999994E-2</v>
+        <v>0.152554</v>
       </c>
       <c r="Z26">
-        <v>0.111874</v>
+        <v>0.17899799999999999</v>
       </c>
       <c r="AA26">
-        <v>0.10047300000000001</v>
+        <v>0.16075700000000001</v>
       </c>
       <c r="AB26">
-        <v>9.5519999999999994E-2</v>
+        <v>0.152832</v>
       </c>
       <c r="AC26">
-        <v>9.4074000000000005E-2</v>
+        <v>0.15051800000000001</v>
       </c>
       <c r="AD26">
-        <v>0.112052</v>
+        <v>0.179284</v>
       </c>
       <c r="AE26">
-        <v>0.10867300000000001</v>
+        <v>0.173876</v>
       </c>
       <c r="AF26">
-        <v>0.12526100000000001</v>
+        <v>0.20041800000000001</v>
       </c>
       <c r="AG26">
-        <v>0.112306</v>
+        <v>0.17968899999999999</v>
       </c>
       <c r="AH26">
-        <v>0.103836</v>
+        <v>0.166406</v>
       </c>
       <c r="AI26">
-        <v>9.5187999999999995E-2</v>
+        <v>0.15301000000000001</v>
       </c>
       <c r="AJ26">
-        <v>0.17929300000000001</v>
+        <v>0.28686899999999999</v>
       </c>
       <c r="AK26">
-        <v>0.172287</v>
+        <v>0.27566000000000002</v>
       </c>
       <c r="AL26">
-        <v>0.19994100000000001</v>
+        <v>0.31393100000000002</v>
       </c>
       <c r="AM26">
-        <v>0.18151300000000001</v>
+        <v>0.29236400000000001</v>
       </c>
       <c r="AN26">
-        <v>0.17032600000000001</v>
+        <v>0.27580399999999999</v>
       </c>
       <c r="AO26">
-        <v>0.16714300000000001</v>
+        <v>0.27310400000000001</v>
       </c>
       <c r="AP26">
         <v>54.107413999999999</v>
@@ -10457,58 +10457,58 @@
         <v>23.118212</v>
       </c>
       <c r="X27">
-        <v>9.6409999999999996E-2</v>
+        <v>0.154256</v>
       </c>
       <c r="Y27">
-        <v>9.2465000000000006E-2</v>
+        <v>0.1515</v>
       </c>
       <c r="Z27">
-        <v>0.10811800000000001</v>
+        <v>0.172988</v>
       </c>
       <c r="AA27">
-        <v>9.2745999999999995E-2</v>
+        <v>0.148394</v>
       </c>
       <c r="AB27">
-        <v>9.4263E-2</v>
+        <v>0.15082100000000001</v>
       </c>
       <c r="AC27">
-        <v>8.8415999999999995E-2</v>
+        <v>0.14146</v>
       </c>
       <c r="AD27">
-        <v>0.11092200000000001</v>
+        <v>0.17747499999999999</v>
       </c>
       <c r="AE27">
-        <v>0.110598</v>
+        <v>0.176957</v>
       </c>
       <c r="AF27">
-        <v>0.120834</v>
+        <v>0.19333400000000001</v>
       </c>
       <c r="AG27">
-        <v>0.10633099999999999</v>
+        <v>0.17013</v>
       </c>
       <c r="AH27">
-        <v>0.100587</v>
+        <v>0.16167599999999999</v>
       </c>
       <c r="AI27">
-        <v>9.6698000000000006E-2</v>
+        <v>0.15547900000000001</v>
       </c>
       <c r="AJ27">
-        <v>0.18190799999999999</v>
+        <v>0.29105300000000001</v>
       </c>
       <c r="AK27">
-        <v>0.17168700000000001</v>
+        <v>0.27469900000000003</v>
       </c>
       <c r="AL27">
-        <v>0.19431200000000001</v>
+        <v>0.307529</v>
       </c>
       <c r="AM27">
-        <v>0.17482300000000001</v>
+        <v>0.28460000000000002</v>
       </c>
       <c r="AN27">
-        <v>0.16620199999999999</v>
+        <v>0.27006799999999997</v>
       </c>
       <c r="AO27">
-        <v>0.17091799999999999</v>
+        <v>0.27781</v>
       </c>
       <c r="AP27">
         <v>54.268611</v>
@@ -10666,58 +10666,58 @@
         <v>22.928881000000001</v>
       </c>
       <c r="X28">
-        <v>9.6569000000000002E-2</v>
+        <v>0.15451000000000001</v>
       </c>
       <c r="Y28">
-        <v>9.1032000000000002E-2</v>
+        <v>0.15248300000000001</v>
       </c>
       <c r="Z28">
-        <v>0.106797</v>
+        <v>0.170875</v>
       </c>
       <c r="AA28">
-        <v>9.3668000000000001E-2</v>
+        <v>0.149868</v>
       </c>
       <c r="AB28">
-        <v>8.9627999999999999E-2</v>
+        <v>0.143405</v>
       </c>
       <c r="AC28">
-        <v>8.6055000000000006E-2</v>
+        <v>0.137681</v>
       </c>
       <c r="AD28">
-        <v>0.10996499999999999</v>
+        <v>0.17594399999999999</v>
       </c>
       <c r="AE28">
-        <v>0.111399</v>
+        <v>0.17823800000000001</v>
       </c>
       <c r="AF28">
-        <v>0.120282</v>
+        <v>0.19245100000000001</v>
       </c>
       <c r="AG28">
-        <v>0.10920100000000001</v>
+        <v>0.17472099999999999</v>
       </c>
       <c r="AH28">
-        <v>9.9088999999999997E-2</v>
+        <v>0.15945400000000001</v>
       </c>
       <c r="AI28">
-        <v>9.9376000000000006E-2</v>
+        <v>0.159854</v>
       </c>
       <c r="AJ28">
-        <v>0.17719599999999999</v>
+        <v>0.28351300000000001</v>
       </c>
       <c r="AK28">
-        <v>0.16720499999999999</v>
+        <v>0.26752799999999999</v>
       </c>
       <c r="AL28">
-        <v>0.19031100000000001</v>
+        <v>0.302865</v>
       </c>
       <c r="AM28">
-        <v>0.18054999999999999</v>
+        <v>0.29016700000000001</v>
       </c>
       <c r="AN28">
-        <v>0.165301</v>
+        <v>0.26794499999999999</v>
       </c>
       <c r="AO28">
-        <v>0.17473900000000001</v>
+        <v>0.28326800000000002</v>
       </c>
       <c r="AP28">
         <v>54.950153</v>
@@ -10875,58 +10875,58 @@
         <v>23.570398999999998</v>
       </c>
       <c r="X29">
-        <v>9.9264000000000005E-2</v>
+        <v>0.15882199999999999</v>
       </c>
       <c r="Y29">
-        <v>9.5968999999999999E-2</v>
+        <v>0.159854</v>
       </c>
       <c r="Z29">
-        <v>0.107877</v>
+        <v>0.17260300000000001</v>
       </c>
       <c r="AA29">
-        <v>9.7453999999999999E-2</v>
+        <v>0.15592600000000001</v>
       </c>
       <c r="AB29">
-        <v>8.8944999999999996E-2</v>
+        <v>0.14231099999999999</v>
       </c>
       <c r="AC29">
-        <v>9.2162999999999995E-2</v>
+        <v>0.14746000000000001</v>
       </c>
       <c r="AD29">
-        <v>0.109555</v>
+        <v>0.175287</v>
       </c>
       <c r="AE29">
-        <v>0.114872</v>
+        <v>0.18379499999999999</v>
       </c>
       <c r="AF29">
-        <v>0.120375</v>
+        <v>0.19260099999999999</v>
       </c>
       <c r="AG29">
-        <v>0.112055</v>
+        <v>0.179288</v>
       </c>
       <c r="AH29">
-        <v>0.100117</v>
+        <v>0.16081899999999999</v>
       </c>
       <c r="AI29">
-        <v>0.105903</v>
+        <v>0.169627</v>
       </c>
       <c r="AJ29">
-        <v>0.17185700000000001</v>
+        <v>0.27497100000000002</v>
       </c>
       <c r="AK29">
-        <v>0.16809299999999999</v>
+        <v>0.26894800000000002</v>
       </c>
       <c r="AL29">
-        <v>0.18998799999999999</v>
+        <v>0.30259799999999998</v>
       </c>
       <c r="AM29">
-        <v>0.18268100000000001</v>
+        <v>0.29289799999999999</v>
       </c>
       <c r="AN29">
-        <v>0.165794</v>
+        <v>0.26808799999999999</v>
       </c>
       <c r="AO29">
-        <v>0.18234500000000001</v>
+        <v>0.29204200000000002</v>
       </c>
       <c r="AP29">
         <v>56.286966999999997</v>
@@ -11084,58 +11084,58 @@
         <v>24.930678</v>
       </c>
       <c r="X30">
-        <v>0.100707</v>
+        <v>0.161132</v>
       </c>
       <c r="Y30">
-        <v>0.10871</v>
+        <v>0.173066</v>
       </c>
       <c r="Z30">
-        <v>0.10999200000000001</v>
+        <v>0.175987</v>
       </c>
       <c r="AA30">
-        <v>0.100568</v>
+        <v>0.160909</v>
       </c>
       <c r="AB30">
-        <v>9.0636999999999995E-2</v>
+        <v>0.14502000000000001</v>
       </c>
       <c r="AC30">
-        <v>0.10165399999999999</v>
+        <v>0.16265099999999999</v>
       </c>
       <c r="AD30">
-        <v>0.109316</v>
+        <v>0.17490600000000001</v>
       </c>
       <c r="AE30">
-        <v>0.12078</v>
+        <v>0.193248</v>
       </c>
       <c r="AF30">
-        <v>0.121366</v>
+        <v>0.194186</v>
       </c>
       <c r="AG30">
-        <v>0.11226999999999999</v>
+        <v>0.17963100000000001</v>
       </c>
       <c r="AH30">
-        <v>0.10288700000000001</v>
+        <v>0.16466900000000001</v>
       </c>
       <c r="AI30">
-        <v>0.11475399999999999</v>
+        <v>0.182504</v>
       </c>
       <c r="AJ30">
-        <v>0.171789</v>
+        <v>0.27486300000000002</v>
       </c>
       <c r="AK30">
-        <v>0.17682400000000001</v>
+        <v>0.28291899999999998</v>
       </c>
       <c r="AL30">
-        <v>0.18832299999999999</v>
+        <v>0.30096200000000001</v>
       </c>
       <c r="AM30">
-        <v>0.18152599999999999</v>
+        <v>0.29253400000000002</v>
       </c>
       <c r="AN30">
-        <v>0.16764799999999999</v>
+        <v>0.27016200000000001</v>
       </c>
       <c r="AO30">
-        <v>0.19220699999999999</v>
+        <v>0.302315</v>
       </c>
       <c r="AP30">
         <v>57.276034000000003</v>
@@ -11293,58 +11293,58 @@
         <v>26.00873</v>
       </c>
       <c r="X31">
-        <v>0.100304</v>
+        <v>0.16048599999999999</v>
       </c>
       <c r="Y31">
-        <v>0.11373800000000001</v>
+        <v>0.17926800000000001</v>
       </c>
       <c r="Z31">
-        <v>0.110472</v>
+        <v>0.176755</v>
       </c>
       <c r="AA31">
-        <v>0.101615</v>
+        <v>0.16258400000000001</v>
       </c>
       <c r="AB31">
-        <v>9.2816999999999997E-2</v>
+        <v>0.148508</v>
       </c>
       <c r="AC31">
-        <v>0.106767</v>
+        <v>0.17083599999999999</v>
       </c>
       <c r="AD31">
-        <v>0.108653</v>
+        <v>0.173844</v>
       </c>
       <c r="AE31">
-        <v>0.122957</v>
+        <v>0.19673099999999999</v>
       </c>
       <c r="AF31">
-        <v>0.12346500000000001</v>
+        <v>0.197544</v>
       </c>
       <c r="AG31">
-        <v>0.114152</v>
+        <v>0.182643</v>
       </c>
       <c r="AH31">
-        <v>0.105264</v>
+        <v>0.167962</v>
       </c>
       <c r="AI31">
-        <v>0.120271</v>
+        <v>0.19042000000000001</v>
       </c>
       <c r="AJ31">
-        <v>0.17260300000000001</v>
+        <v>0.27616499999999999</v>
       </c>
       <c r="AK31">
-        <v>0.180673</v>
+        <v>0.28907699999999997</v>
       </c>
       <c r="AL31">
-        <v>0.18934200000000001</v>
+        <v>0.302033</v>
       </c>
       <c r="AM31">
-        <v>0.184756</v>
+        <v>0.29600599999999999</v>
       </c>
       <c r="AN31">
-        <v>0.17047300000000001</v>
+        <v>0.27303899999999998</v>
       </c>
       <c r="AO31">
-        <v>0.19831699999999999</v>
+        <v>0.30843599999999999</v>
       </c>
       <c r="AP31">
         <v>57.138852</v>
@@ -11505,58 +11505,58 @@
         <v>26.654526000000001</v>
       </c>
       <c r="X32">
-        <v>9.9611000000000005E-2</v>
+        <v>0.15937799999999999</v>
       </c>
       <c r="Y32">
-        <v>9.5422000000000007E-2</v>
+        <v>0.154645</v>
       </c>
       <c r="Z32">
-        <v>0.11786000000000001</v>
+        <v>0.18857699999999999</v>
       </c>
       <c r="AA32">
-        <v>0.115269</v>
+        <v>0.18443100000000001</v>
       </c>
       <c r="AB32">
-        <v>9.9736000000000005E-2</v>
+        <v>0.159577</v>
       </c>
       <c r="AC32">
-        <v>9.0952000000000005E-2</v>
+        <v>0.14552100000000001</v>
       </c>
       <c r="AD32">
-        <v>0.10970100000000001</v>
+        <v>0.17552200000000001</v>
       </c>
       <c r="AE32">
-        <v>0.110664</v>
+        <v>0.177062</v>
       </c>
       <c r="AF32">
-        <v>0.13120799999999999</v>
+        <v>0.20993200000000001</v>
       </c>
       <c r="AG32">
-        <v>0.1275</v>
+        <v>0.20400099999999999</v>
       </c>
       <c r="AH32">
-        <v>0.115762</v>
+        <v>0.18373300000000001</v>
       </c>
       <c r="AI32">
-        <v>0.10337300000000001</v>
+        <v>0.165155</v>
       </c>
       <c r="AJ32">
-        <v>0.177953</v>
+        <v>0.28472500000000001</v>
       </c>
       <c r="AK32">
-        <v>0.16562399999999999</v>
+        <v>0.26499800000000001</v>
       </c>
       <c r="AL32">
-        <v>0.20674200000000001</v>
+        <v>0.32214599999999999</v>
       </c>
       <c r="AM32">
-        <v>0.203096</v>
+        <v>0.31694</v>
       </c>
       <c r="AN32">
-        <v>0.193719</v>
+        <v>0.30641099999999999</v>
       </c>
       <c r="AO32">
-        <v>0.18304599999999999</v>
+        <v>0.290132</v>
       </c>
       <c r="AP32">
         <v>53.397272999999998</v>
@@ -11717,58 +11717,58 @@
         <v>26.313616</v>
       </c>
       <c r="X33">
-        <v>0.10049</v>
+        <v>0.16078500000000001</v>
       </c>
       <c r="Y33">
-        <v>9.6504999999999994E-2</v>
+        <v>0.15483</v>
       </c>
       <c r="Z33">
-        <v>0.114593</v>
+        <v>0.18334900000000001</v>
       </c>
       <c r="AA33">
-        <v>0.11384900000000001</v>
+        <v>0.18215899999999999</v>
       </c>
       <c r="AB33">
-        <v>9.8077999999999999E-2</v>
+        <v>0.15692500000000001</v>
       </c>
       <c r="AC33">
-        <v>8.8371000000000005E-2</v>
+        <v>0.14138999999999999</v>
       </c>
       <c r="AD33">
-        <v>0.109726</v>
+        <v>0.175562</v>
       </c>
       <c r="AE33">
-        <v>0.10867599999999999</v>
+        <v>0.17388200000000001</v>
       </c>
       <c r="AF33">
-        <v>0.12672700000000001</v>
+        <v>0.202764</v>
       </c>
       <c r="AG33">
-        <v>0.12424200000000001</v>
+        <v>0.19878799999999999</v>
       </c>
       <c r="AH33">
-        <v>0.114399</v>
+        <v>0.182009</v>
       </c>
       <c r="AI33">
-        <v>0.10156900000000001</v>
+        <v>0.16251599999999999</v>
       </c>
       <c r="AJ33">
-        <v>0.177145</v>
+        <v>0.28343200000000002</v>
       </c>
       <c r="AK33">
-        <v>0.16709599999999999</v>
+        <v>0.26735399999999998</v>
       </c>
       <c r="AL33">
-        <v>0.196382</v>
+        <v>0.31076599999999999</v>
       </c>
       <c r="AM33">
-        <v>0.20360800000000001</v>
+        <v>0.31750800000000001</v>
       </c>
       <c r="AN33">
-        <v>0.192217</v>
+        <v>0.304919</v>
       </c>
       <c r="AO33">
-        <v>0.18065700000000001</v>
+        <v>0.28765200000000002</v>
       </c>
       <c r="AP33">
         <v>53.151899999999998</v>
@@ -11929,58 +11929,58 @@
         <v>25.767952999999999</v>
       </c>
       <c r="X34">
-        <v>0.10093199999999999</v>
+        <v>0.161491</v>
       </c>
       <c r="Y34">
-        <v>9.8459000000000005E-2</v>
+        <v>0.156249</v>
       </c>
       <c r="Z34">
-        <v>0.11032599999999999</v>
+        <v>0.17652100000000001</v>
       </c>
       <c r="AA34">
-        <v>0.10527400000000001</v>
+        <v>0.168438</v>
       </c>
       <c r="AB34">
-        <v>9.2199000000000003E-2</v>
+        <v>0.14751900000000001</v>
       </c>
       <c r="AC34">
-        <v>8.8444999999999996E-2</v>
+        <v>0.141509</v>
       </c>
       <c r="AD34">
-        <v>0.110177</v>
+        <v>0.176283</v>
       </c>
       <c r="AE34">
-        <v>0.1076</v>
+        <v>0.17216100000000001</v>
       </c>
       <c r="AF34">
-        <v>0.122214</v>
+        <v>0.19554199999999999</v>
       </c>
       <c r="AG34">
-        <v>0.114939</v>
+        <v>0.18390300000000001</v>
       </c>
       <c r="AH34">
-        <v>0.11094900000000001</v>
+        <v>0.17727499999999999</v>
       </c>
       <c r="AI34">
-        <v>9.9222000000000005E-2</v>
+        <v>0.159054</v>
       </c>
       <c r="AJ34">
-        <v>0.17599500000000001</v>
+        <v>0.28159200000000001</v>
       </c>
       <c r="AK34">
-        <v>0.16805100000000001</v>
+        <v>0.26888099999999998</v>
       </c>
       <c r="AL34">
-        <v>0.186809</v>
+        <v>0.29988599999999999</v>
       </c>
       <c r="AM34">
-        <v>0.19678100000000001</v>
+        <v>0.31028899999999998</v>
       </c>
       <c r="AN34">
-        <v>0.186275</v>
+        <v>0.29892800000000003</v>
       </c>
       <c r="AO34">
-        <v>0.176734</v>
+        <v>0.28376800000000002</v>
       </c>
       <c r="AP34">
         <v>52.892809</v>
@@ -12141,58 +12141,58 @@
         <v>25.147416</v>
       </c>
       <c r="X35">
-        <v>0.101533</v>
+        <v>0.16245200000000001</v>
       </c>
       <c r="Y35">
-        <v>9.9060999999999996E-2</v>
+        <v>0.15728500000000001</v>
       </c>
       <c r="Z35">
-        <v>0.112785</v>
+        <v>0.18045600000000001</v>
       </c>
       <c r="AA35">
-        <v>9.7517999999999994E-2</v>
+        <v>0.156028</v>
       </c>
       <c r="AB35">
-        <v>9.0505000000000002E-2</v>
+        <v>0.14480899999999999</v>
       </c>
       <c r="AC35">
-        <v>9.3668000000000001E-2</v>
+        <v>0.14987200000000001</v>
       </c>
       <c r="AD35">
-        <v>0.111526</v>
+        <v>0.17844099999999999</v>
       </c>
       <c r="AE35">
-        <v>0.10829999999999999</v>
+        <v>0.17327999999999999</v>
       </c>
       <c r="AF35">
-        <v>0.12562300000000001</v>
+        <v>0.20099700000000001</v>
       </c>
       <c r="AG35">
-        <v>0.107687</v>
+        <v>0.17230000000000001</v>
       </c>
       <c r="AH35">
-        <v>0.10915800000000001</v>
+        <v>0.17463300000000001</v>
       </c>
       <c r="AI35">
-        <v>9.7623000000000001E-2</v>
+        <v>0.15669</v>
       </c>
       <c r="AJ35">
-        <v>0.175591</v>
+        <v>0.28094599999999997</v>
       </c>
       <c r="AK35">
-        <v>0.1709</v>
+        <v>0.27343899999999999</v>
       </c>
       <c r="AL35">
-        <v>0.19468299999999999</v>
+        <v>0.30813800000000002</v>
       </c>
       <c r="AM35">
-        <v>0.18868699999999999</v>
+        <v>0.30119000000000001</v>
       </c>
       <c r="AN35">
-        <v>0.18293200000000001</v>
+        <v>0.29424400000000001</v>
       </c>
       <c r="AO35">
-        <v>0.173485</v>
+        <v>0.28079900000000002</v>
       </c>
       <c r="AP35">
         <v>52.757171999999997</v>
@@ -12353,58 +12353,58 @@
         <v>24.917732999999998</v>
       </c>
       <c r="X36">
-        <v>9.9929000000000004E-2</v>
+        <v>0.159886</v>
       </c>
       <c r="Y36">
-        <v>9.6624000000000002E-2</v>
+        <v>0.15707699999999999</v>
       </c>
       <c r="Z36">
-        <v>0.112327</v>
+        <v>0.17972399999999999</v>
       </c>
       <c r="AA36">
-        <v>9.3997999999999998E-2</v>
+        <v>0.150396</v>
       </c>
       <c r="AB36">
-        <v>9.2543E-2</v>
+        <v>0.14806900000000001</v>
       </c>
       <c r="AC36">
-        <v>9.5183000000000004E-2</v>
+        <v>0.15229699999999999</v>
       </c>
       <c r="AD36">
-        <v>0.11156000000000001</v>
+        <v>0.17849699999999999</v>
       </c>
       <c r="AE36">
-        <v>0.11092</v>
+        <v>0.17747199999999999</v>
       </c>
       <c r="AF36">
-        <v>0.12712200000000001</v>
+        <v>0.20339499999999999</v>
       </c>
       <c r="AG36">
-        <v>0.10485800000000001</v>
+        <v>0.167772</v>
       </c>
       <c r="AH36">
-        <v>0.108427</v>
+        <v>0.173347</v>
       </c>
       <c r="AI36">
-        <v>9.7642999999999994E-2</v>
+        <v>0.156722</v>
       </c>
       <c r="AJ36">
-        <v>0.17683499999999999</v>
+        <v>0.28293600000000002</v>
       </c>
       <c r="AK36">
-        <v>0.173544</v>
+        <v>0.27766999999999997</v>
       </c>
       <c r="AL36">
-        <v>0.19601299999999999</v>
+        <v>0.309803</v>
       </c>
       <c r="AM36">
-        <v>0.18376500000000001</v>
+        <v>0.29496600000000001</v>
       </c>
       <c r="AN36">
-        <v>0.18310000000000001</v>
+        <v>0.29200999999999999</v>
       </c>
       <c r="AO36">
-        <v>0.17382500000000001</v>
+        <v>0.28140900000000002</v>
       </c>
       <c r="AP36">
         <v>53.073276</v>
@@ -12565,58 +12565,58 @@
         <v>25.015861999999998</v>
       </c>
       <c r="X37">
-        <v>9.7144999999999995E-2</v>
+        <v>0.15543100000000001</v>
       </c>
       <c r="Y37">
-        <v>0.100663</v>
+        <v>0.161801</v>
       </c>
       <c r="Z37">
-        <v>0.11305999999999999</v>
+        <v>0.180896</v>
       </c>
       <c r="AA37">
-        <v>9.1356999999999994E-2</v>
+        <v>0.146172</v>
       </c>
       <c r="AB37">
-        <v>9.1465000000000005E-2</v>
+        <v>0.146345</v>
       </c>
       <c r="AC37">
-        <v>8.9185E-2</v>
+        <v>0.14269299999999999</v>
       </c>
       <c r="AD37">
-        <v>0.110037</v>
+        <v>0.17605899999999999</v>
       </c>
       <c r="AE37">
-        <v>0.11725099999999999</v>
+        <v>0.18760199999999999</v>
       </c>
       <c r="AF37">
-        <v>0.12676699999999999</v>
+        <v>0.20282600000000001</v>
       </c>
       <c r="AG37">
-        <v>0.10396900000000001</v>
+        <v>0.16635</v>
       </c>
       <c r="AH37">
-        <v>0.10623299999999999</v>
+        <v>0.17008200000000001</v>
       </c>
       <c r="AI37">
-        <v>9.8573999999999995E-2</v>
+        <v>0.15828100000000001</v>
       </c>
       <c r="AJ37">
-        <v>0.17962700000000001</v>
+        <v>0.28740300000000002</v>
       </c>
       <c r="AK37">
-        <v>0.17882100000000001</v>
+        <v>0.28611399999999998</v>
       </c>
       <c r="AL37">
-        <v>0.18924099999999999</v>
+        <v>0.30233900000000002</v>
       </c>
       <c r="AM37">
-        <v>0.18073</v>
+        <v>0.29127799999999998</v>
       </c>
       <c r="AN37">
-        <v>0.18037600000000001</v>
+        <v>0.287661</v>
       </c>
       <c r="AO37">
-        <v>0.17691399999999999</v>
+        <v>0.285022</v>
       </c>
       <c r="AP37">
         <v>53.536963999999998</v>
@@ -12777,58 +12777,58 @@
         <v>25.289721</v>
       </c>
       <c r="X38">
-        <v>9.6194000000000002E-2</v>
+        <v>0.15390899999999999</v>
       </c>
       <c r="Y38">
-        <v>0.104856</v>
+        <v>0.16688600000000001</v>
       </c>
       <c r="Z38">
-        <v>0.113889</v>
+        <v>0.182222</v>
       </c>
       <c r="AA38">
-        <v>9.4320000000000001E-2</v>
+        <v>0.15091099999999999</v>
       </c>
       <c r="AB38">
-        <v>9.0490000000000001E-2</v>
+        <v>0.144784</v>
       </c>
       <c r="AC38">
-        <v>8.4838999999999998E-2</v>
+        <v>0.13573499999999999</v>
       </c>
       <c r="AD38">
-        <v>0.108389</v>
+        <v>0.17342299999999999</v>
       </c>
       <c r="AE38">
-        <v>0.121208</v>
+        <v>0.19393199999999999</v>
       </c>
       <c r="AF38">
-        <v>0.126004</v>
+        <v>0.20160600000000001</v>
       </c>
       <c r="AG38">
-        <v>0.107422</v>
+        <v>0.171875</v>
       </c>
       <c r="AH38">
-        <v>0.104244</v>
+        <v>0.16711899999999999</v>
       </c>
       <c r="AI38">
-        <v>0.10118000000000001</v>
+        <v>0.162414</v>
       </c>
       <c r="AJ38">
-        <v>0.17777899999999999</v>
+        <v>0.28444599999999998</v>
       </c>
       <c r="AK38">
-        <v>0.18010200000000001</v>
+        <v>0.28816399999999998</v>
       </c>
       <c r="AL38">
-        <v>0.18515100000000001</v>
+        <v>0.29748599999999997</v>
       </c>
       <c r="AM38">
-        <v>0.18178900000000001</v>
+        <v>0.29226099999999999</v>
       </c>
       <c r="AN38">
-        <v>0.17616599999999999</v>
+        <v>0.28231600000000001</v>
       </c>
       <c r="AO38">
-        <v>0.180898</v>
+        <v>0.289966</v>
       </c>
       <c r="AP38">
         <v>54.083998999999999</v>
@@ -12989,58 +12989,58 @@
         <v>26.019247</v>
       </c>
       <c r="X39">
-        <v>9.6865000000000007E-2</v>
+        <v>0.15498400000000001</v>
       </c>
       <c r="Y39">
-        <v>0.10539900000000001</v>
+        <v>0.16948099999999999</v>
       </c>
       <c r="Z39">
-        <v>0.114172</v>
+        <v>0.182675</v>
       </c>
       <c r="AA39">
-        <v>9.9562999999999999E-2</v>
+        <v>0.159301</v>
       </c>
       <c r="AB39">
-        <v>9.307E-2</v>
+        <v>0.14891199999999999</v>
       </c>
       <c r="AC39">
-        <v>9.1195999999999999E-2</v>
+        <v>0.14591100000000001</v>
       </c>
       <c r="AD39">
-        <v>0.106753</v>
+        <v>0.17080600000000001</v>
       </c>
       <c r="AE39">
-        <v>0.120423</v>
+        <v>0.19267699999999999</v>
       </c>
       <c r="AF39">
-        <v>0.122624</v>
+        <v>0.19619900000000001</v>
       </c>
       <c r="AG39">
-        <v>0.111868</v>
+        <v>0.17898900000000001</v>
       </c>
       <c r="AH39">
-        <v>0.103821</v>
+        <v>0.16636000000000001</v>
       </c>
       <c r="AI39">
-        <v>0.107365</v>
+        <v>0.171574</v>
       </c>
       <c r="AJ39">
-        <v>0.17318500000000001</v>
+        <v>0.27709600000000001</v>
       </c>
       <c r="AK39">
-        <v>0.17580699999999999</v>
+        <v>0.28129199999999999</v>
       </c>
       <c r="AL39">
-        <v>0.18495700000000001</v>
+        <v>0.297178</v>
       </c>
       <c r="AM39">
-        <v>0.18396000000000001</v>
+        <v>0.29478799999999999</v>
       </c>
       <c r="AN39">
-        <v>0.17332500000000001</v>
+        <v>0.27865200000000001</v>
       </c>
       <c r="AO39">
-        <v>0.187749</v>
+        <v>0.29748400000000003</v>
       </c>
       <c r="AP39">
         <v>54.748437000000003</v>
@@ -13201,58 +13201,58 @@
         <v>26.981983</v>
       </c>
       <c r="X40">
-        <v>9.7118999999999997E-2</v>
+        <v>0.155391</v>
       </c>
       <c r="Y40">
-        <v>0.10922900000000001</v>
+        <v>0.17439199999999999</v>
       </c>
       <c r="Z40">
-        <v>0.117134</v>
+        <v>0.187415</v>
       </c>
       <c r="AA40">
-        <v>0.102232</v>
+        <v>0.16356999999999999</v>
       </c>
       <c r="AB40">
-        <v>9.5362000000000002E-2</v>
+        <v>0.15257899999999999</v>
       </c>
       <c r="AC40">
-        <v>0.102936</v>
+        <v>0.16470399999999999</v>
       </c>
       <c r="AD40">
-        <v>0.103867</v>
+        <v>0.166188</v>
       </c>
       <c r="AE40">
-        <v>0.120668</v>
+        <v>0.19306899999999999</v>
       </c>
       <c r="AF40">
-        <v>0.125972</v>
+        <v>0.20155500000000001</v>
       </c>
       <c r="AG40">
-        <v>0.11629</v>
+        <v>0.18606400000000001</v>
       </c>
       <c r="AH40">
-        <v>0.10433000000000001</v>
+        <v>0.166961</v>
       </c>
       <c r="AI40">
-        <v>0.115303</v>
+        <v>0.183091</v>
       </c>
       <c r="AJ40">
-        <v>0.170575</v>
+        <v>0.27291900000000002</v>
       </c>
       <c r="AK40">
-        <v>0.17823900000000001</v>
+        <v>0.28518199999999999</v>
       </c>
       <c r="AL40">
-        <v>0.19103999999999999</v>
+        <v>0.30406</v>
       </c>
       <c r="AM40">
-        <v>0.19259100000000001</v>
+        <v>0.30392400000000003</v>
       </c>
       <c r="AN40">
-        <v>0.172152</v>
+        <v>0.27701599999999998</v>
       </c>
       <c r="AO40">
-        <v>0.19539200000000001</v>
+        <v>0.30545099999999997</v>
       </c>
       <c r="AP40">
         <v>55.084144999999999</v>
@@ -13413,58 +13413,58 @@
         <v>27.625858000000001</v>
       </c>
       <c r="X41">
-        <v>9.7208000000000003E-2</v>
+        <v>0.155533</v>
       </c>
       <c r="Y41">
-        <v>0.112541</v>
+        <v>0.17780499999999999</v>
       </c>
       <c r="Z41">
-        <v>0.118523</v>
+        <v>0.189637</v>
       </c>
       <c r="AA41">
-        <v>0.101968</v>
+        <v>0.16314899999999999</v>
       </c>
       <c r="AB41">
-        <v>9.7197000000000006E-2</v>
+        <v>0.15551400000000001</v>
       </c>
       <c r="AC41">
-        <v>0.106603</v>
+        <v>0.170574</v>
       </c>
       <c r="AD41">
-        <v>0.10209699999999999</v>
+        <v>0.163355</v>
       </c>
       <c r="AE41">
-        <v>0.121221</v>
+        <v>0.19395399999999999</v>
       </c>
       <c r="AF41">
-        <v>0.12951699999999999</v>
+        <v>0.20722699999999999</v>
       </c>
       <c r="AG41">
-        <v>0.11648</v>
+        <v>0.18636800000000001</v>
       </c>
       <c r="AH41">
-        <v>0.104814</v>
+        <v>0.16759199999999999</v>
       </c>
       <c r="AI41">
-        <v>0.119199</v>
+        <v>0.188745</v>
       </c>
       <c r="AJ41">
-        <v>0.170011</v>
+        <v>0.27201700000000001</v>
       </c>
       <c r="AK41">
-        <v>0.181284</v>
+        <v>0.29005500000000001</v>
       </c>
       <c r="AL41">
-        <v>0.19559699999999999</v>
+        <v>0.30915900000000002</v>
       </c>
       <c r="AM41">
-        <v>0.19539500000000001</v>
+        <v>0.307085</v>
       </c>
       <c r="AN41">
-        <v>0.17254</v>
+        <v>0.27718399999999999</v>
       </c>
       <c r="AO41">
-        <v>0.199182</v>
+        <v>0.30939299999999997</v>
       </c>
       <c r="AP41">
         <v>55.853771000000002</v>
@@ -13625,58 +13625,58 @@
         <v>26.964779</v>
       </c>
       <c r="X42">
-        <v>9.6320000000000003E-2</v>
+        <v>0.154112</v>
       </c>
       <c r="Y42">
-        <v>9.4148999999999997E-2</v>
+        <v>0.153864</v>
       </c>
       <c r="Z42">
-        <v>0.10965</v>
+        <v>0.17544000000000001</v>
       </c>
       <c r="AA42">
-        <v>9.8905000000000007E-2</v>
+        <v>0.158249</v>
       </c>
       <c r="AB42">
-        <v>9.4183000000000003E-2</v>
+        <v>0.15069299999999999</v>
       </c>
       <c r="AC42">
-        <v>9.1123999999999997E-2</v>
+        <v>0.14579700000000001</v>
       </c>
       <c r="AD42">
-        <v>0.109815</v>
+        <v>0.175705</v>
       </c>
       <c r="AE42">
-        <v>0.113802</v>
+        <v>0.18208299999999999</v>
       </c>
       <c r="AF42">
-        <v>0.125052</v>
+        <v>0.20008300000000001</v>
       </c>
       <c r="AG42">
-        <v>0.111514</v>
+        <v>0.178423</v>
       </c>
       <c r="AH42">
-        <v>0.114631</v>
+        <v>0.182367</v>
       </c>
       <c r="AI42">
-        <v>0.10399899999999999</v>
+        <v>0.16644400000000001</v>
       </c>
       <c r="AJ42">
-        <v>0.180116</v>
+        <v>0.28818500000000002</v>
       </c>
       <c r="AK42">
-        <v>0.169713</v>
+        <v>0.27154099999999998</v>
       </c>
       <c r="AL42">
-        <v>0.19323499999999999</v>
+        <v>0.30617699999999998</v>
       </c>
       <c r="AM42">
-        <v>0.18226000000000001</v>
+        <v>0.29343799999999998</v>
       </c>
       <c r="AN42">
-        <v>0.19369400000000001</v>
+        <v>0.307809</v>
       </c>
       <c r="AO42">
-        <v>0.18501400000000001</v>
+        <v>0.29417300000000002</v>
       </c>
       <c r="AP42">
         <v>52.471859000000002</v>
@@ -13837,58 +13837,58 @@
         <v>26.910156000000001</v>
       </c>
       <c r="X43">
-        <v>9.7004999999999994E-2</v>
+        <v>0.15520700000000001</v>
       </c>
       <c r="Y43">
-        <v>9.2000999999999999E-2</v>
+        <v>0.15135899999999999</v>
       </c>
       <c r="Z43">
-        <v>0.10603799999999999</v>
+        <v>0.16966000000000001</v>
       </c>
       <c r="AA43">
-        <v>0.100287</v>
+        <v>0.16045899999999999</v>
       </c>
       <c r="AB43">
-        <v>9.5531000000000005E-2</v>
+        <v>0.15284900000000001</v>
       </c>
       <c r="AC43">
-        <v>8.7501999999999996E-2</v>
+        <v>0.13999800000000001</v>
       </c>
       <c r="AD43">
-        <v>0.109412</v>
+        <v>0.17505999999999999</v>
       </c>
       <c r="AE43">
-        <v>0.10956100000000001</v>
+        <v>0.17529800000000001</v>
       </c>
       <c r="AF43">
-        <v>0.12049</v>
+        <v>0.19278500000000001</v>
       </c>
       <c r="AG43">
-        <v>0.11178100000000001</v>
+        <v>0.17885000000000001</v>
       </c>
       <c r="AH43">
-        <v>0.11519799999999999</v>
+        <v>0.18332999999999999</v>
       </c>
       <c r="AI43">
-        <v>0.102849</v>
+        <v>0.16471</v>
       </c>
       <c r="AJ43">
-        <v>0.178479</v>
+        <v>0.28556599999999999</v>
       </c>
       <c r="AK43">
-        <v>0.16838700000000001</v>
+        <v>0.26941900000000002</v>
       </c>
       <c r="AL43">
-        <v>0.18617300000000001</v>
+        <v>0.29842800000000003</v>
       </c>
       <c r="AM43">
-        <v>0.18584000000000001</v>
+        <v>0.29747699999999999</v>
       </c>
       <c r="AN43">
-        <v>0.196134</v>
+        <v>0.31013200000000002</v>
       </c>
       <c r="AO43">
-        <v>0.183838</v>
+        <v>0.292877</v>
       </c>
       <c r="AP43">
         <v>52.029615</v>
@@ -14049,58 +14049,58 @@
         <v>26.866558999999999</v>
       </c>
       <c r="X44">
-        <v>9.9519999999999997E-2</v>
+        <v>0.15923200000000001</v>
       </c>
       <c r="Y44">
-        <v>9.3970999999999999E-2</v>
+        <v>0.15232200000000001</v>
       </c>
       <c r="Z44">
-        <v>0.103644</v>
+        <v>0.16583000000000001</v>
       </c>
       <c r="AA44">
-        <v>0.10519299999999999</v>
+        <v>0.16830800000000001</v>
       </c>
       <c r="AB44">
-        <v>0.10069400000000001</v>
+        <v>0.16111</v>
       </c>
       <c r="AC44">
-        <v>9.0606999999999993E-2</v>
+        <v>0.14497199999999999</v>
       </c>
       <c r="AD44">
-        <v>0.10830099999999999</v>
+        <v>0.17328099999999999</v>
       </c>
       <c r="AE44">
-        <v>0.105166</v>
+        <v>0.168266</v>
       </c>
       <c r="AF44">
-        <v>0.117117</v>
+        <v>0.187388</v>
       </c>
       <c r="AG44">
-        <v>0.11562799999999999</v>
+        <v>0.185005</v>
       </c>
       <c r="AH44">
-        <v>0.1157</v>
+        <v>0.184084</v>
       </c>
       <c r="AI44">
-        <v>0.102274</v>
+        <v>0.16364500000000001</v>
       </c>
       <c r="AJ44">
-        <v>0.17700399999999999</v>
+        <v>0.28320699999999999</v>
       </c>
       <c r="AK44">
-        <v>0.16853199999999999</v>
+        <v>0.269652</v>
       </c>
       <c r="AL44">
-        <v>0.182397</v>
+        <v>0.29404999999999998</v>
       </c>
       <c r="AM44">
-        <v>0.19394800000000001</v>
+        <v>0.306033</v>
       </c>
       <c r="AN44">
-        <v>0.19741600000000001</v>
+        <v>0.31095499999999998</v>
       </c>
       <c r="AO44">
-        <v>0.18302299999999999</v>
+        <v>0.291655</v>
       </c>
       <c r="AP44">
         <v>51.886127999999999</v>
@@ -14261,58 +14261,58 @@
         <v>26.49202</v>
       </c>
       <c r="X45">
-        <v>0.104477</v>
+        <v>0.16716400000000001</v>
       </c>
       <c r="Y45">
-        <v>9.7448999999999994E-2</v>
+        <v>0.15592700000000001</v>
       </c>
       <c r="Z45">
-        <v>0.110721</v>
+        <v>0.17715400000000001</v>
       </c>
       <c r="AA45">
-        <v>0.102446</v>
+        <v>0.163913</v>
       </c>
       <c r="AB45">
-        <v>0.10211000000000001</v>
+        <v>0.16337499999999999</v>
       </c>
       <c r="AC45">
-        <v>8.9744000000000004E-2</v>
+        <v>0.143591</v>
       </c>
       <c r="AD45">
-        <v>0.107377</v>
+        <v>0.17180300000000001</v>
       </c>
       <c r="AE45">
-        <v>0.10528800000000001</v>
+        <v>0.168461</v>
       </c>
       <c r="AF45">
-        <v>0.12314</v>
+        <v>0.197023</v>
       </c>
       <c r="AG45">
-        <v>0.114671</v>
+        <v>0.183473</v>
       </c>
       <c r="AH45">
-        <v>0.115272</v>
+        <v>0.18341099999999999</v>
       </c>
       <c r="AI45">
-        <v>0.100827</v>
+        <v>0.161469</v>
       </c>
       <c r="AJ45">
-        <v>0.17457700000000001</v>
+        <v>0.27932299999999999</v>
       </c>
       <c r="AK45">
-        <v>0.170459</v>
+        <v>0.27273500000000001</v>
       </c>
       <c r="AL45">
-        <v>0.19136600000000001</v>
+        <v>0.30386099999999999</v>
       </c>
       <c r="AM45">
-        <v>0.19149099999999999</v>
+        <v>0.30351299999999998</v>
       </c>
       <c r="AN45">
-        <v>0.19473399999999999</v>
+        <v>0.30780999999999997</v>
       </c>
       <c r="AO45">
-        <v>0.18041699999999999</v>
+        <v>0.28920800000000002</v>
       </c>
       <c r="AP45">
         <v>52.139758999999998</v>
@@ -14473,58 +14473,58 @@
         <v>26.124853999999999</v>
       </c>
       <c r="X46">
-        <v>0.10496900000000001</v>
+        <v>0.16795199999999999</v>
       </c>
       <c r="Y46">
-        <v>0.101503</v>
+        <v>0.16125900000000001</v>
       </c>
       <c r="Z46">
-        <v>0.118247</v>
+        <v>0.189196</v>
       </c>
       <c r="AA46">
-        <v>0.10334400000000001</v>
+        <v>0.165351</v>
       </c>
       <c r="AB46">
-        <v>9.9581000000000003E-2</v>
+        <v>0.15933</v>
       </c>
       <c r="AC46">
-        <v>8.4184999999999996E-2</v>
+        <v>0.13469</v>
       </c>
       <c r="AD46">
-        <v>0.105728</v>
+        <v>0.16916500000000001</v>
       </c>
       <c r="AE46">
-        <v>0.109005</v>
+        <v>0.17440900000000001</v>
       </c>
       <c r="AF46">
-        <v>0.12959499999999999</v>
+        <v>0.20735200000000001</v>
       </c>
       <c r="AG46">
-        <v>0.115173</v>
+        <v>0.184276</v>
       </c>
       <c r="AH46">
-        <v>0.11400299999999999</v>
+        <v>0.18146200000000001</v>
       </c>
       <c r="AI46">
-        <v>9.8998000000000003E-2</v>
+        <v>0.158889</v>
       </c>
       <c r="AJ46">
-        <v>0.17274200000000001</v>
+        <v>0.27638800000000002</v>
       </c>
       <c r="AK46">
-        <v>0.17593200000000001</v>
+        <v>0.28149099999999999</v>
       </c>
       <c r="AL46">
-        <v>0.20124400000000001</v>
+        <v>0.314915</v>
       </c>
       <c r="AM46">
-        <v>0.19076599999999999</v>
+        <v>0.30255700000000002</v>
       </c>
       <c r="AN46">
-        <v>0.190247</v>
+        <v>0.30234</v>
       </c>
       <c r="AO46">
-        <v>0.17793900000000001</v>
+        <v>0.28711900000000001</v>
       </c>
       <c r="AP46">
         <v>52.794263000000001</v>
@@ -14685,58 +14685,58 @@
         <v>26.190186000000001</v>
       </c>
       <c r="X47">
-        <v>9.9376999999999993E-2</v>
+        <v>0.15900300000000001</v>
       </c>
       <c r="Y47">
-        <v>0.10838399999999999</v>
+        <v>0.168265</v>
       </c>
       <c r="Z47">
-        <v>0.117116</v>
+        <v>0.187386</v>
       </c>
       <c r="AA47">
-        <v>0.10653799999999999</v>
+        <v>0.170461</v>
       </c>
       <c r="AB47">
-        <v>9.8773E-2</v>
+        <v>0.15803600000000001</v>
       </c>
       <c r="AC47">
-        <v>8.5664000000000004E-2</v>
+        <v>0.13705800000000001</v>
       </c>
       <c r="AD47">
-        <v>0.104237</v>
+        <v>0.16678000000000001</v>
       </c>
       <c r="AE47">
-        <v>0.11204799999999999</v>
+        <v>0.17927699999999999</v>
       </c>
       <c r="AF47">
-        <v>0.12840599999999999</v>
+        <v>0.20544999999999999</v>
       </c>
       <c r="AG47">
-        <v>0.11712400000000001</v>
+        <v>0.18739900000000001</v>
       </c>
       <c r="AH47">
-        <v>0.112357</v>
+        <v>0.178924</v>
       </c>
       <c r="AI47">
-        <v>9.9333000000000005E-2</v>
+        <v>0.159473</v>
       </c>
       <c r="AJ47">
-        <v>0.17119500000000001</v>
+        <v>0.27391199999999999</v>
       </c>
       <c r="AK47">
-        <v>0.18052299999999999</v>
+        <v>0.28883700000000001</v>
       </c>
       <c r="AL47">
-        <v>0.19503000000000001</v>
+        <v>0.30833199999999999</v>
       </c>
       <c r="AM47">
-        <v>0.19262199999999999</v>
+        <v>0.30413499999999999</v>
       </c>
       <c r="AN47">
-        <v>0.18648700000000001</v>
+        <v>0.29708400000000001</v>
       </c>
       <c r="AO47">
-        <v>0.17860200000000001</v>
+        <v>0.288136</v>
       </c>
       <c r="AP47">
         <v>53.539254</v>
@@ -14897,58 +14897,58 @@
         <v>26.633465000000001</v>
       </c>
       <c r="X48">
-        <v>9.5322000000000004E-2</v>
+        <v>0.15251400000000001</v>
       </c>
       <c r="Y48">
-        <v>0.114728</v>
+        <v>0.17360999999999999</v>
       </c>
       <c r="Z48">
-        <v>0.11086500000000001</v>
+        <v>0.17738399999999999</v>
       </c>
       <c r="AA48">
-        <v>0.100756</v>
+        <v>0.16120999999999999</v>
       </c>
       <c r="AB48">
-        <v>9.9991999999999998E-2</v>
+        <v>0.15998799999999999</v>
       </c>
       <c r="AC48">
-        <v>9.5212000000000005E-2</v>
+        <v>0.15234300000000001</v>
       </c>
       <c r="AD48">
-        <v>0.102849</v>
+        <v>0.16455900000000001</v>
       </c>
       <c r="AE48">
-        <v>0.114951</v>
+        <v>0.183921</v>
       </c>
       <c r="AF48">
-        <v>0.122139</v>
+        <v>0.19542200000000001</v>
       </c>
       <c r="AG48">
-        <v>0.11340600000000001</v>
+        <v>0.18145</v>
       </c>
       <c r="AH48">
-        <v>0.109223</v>
+        <v>0.17433399999999999</v>
       </c>
       <c r="AI48">
-        <v>0.10230400000000001</v>
+        <v>0.16386800000000001</v>
       </c>
       <c r="AJ48">
-        <v>0.169208</v>
+        <v>0.270733</v>
       </c>
       <c r="AK48">
-        <v>0.184721</v>
+        <v>0.29555399999999998</v>
       </c>
       <c r="AL48">
-        <v>0.18912100000000001</v>
+        <v>0.30178100000000002</v>
       </c>
       <c r="AM48">
-        <v>0.187834</v>
+        <v>0.29919099999999998</v>
       </c>
       <c r="AN48">
-        <v>0.182694</v>
+        <v>0.29180200000000001</v>
       </c>
       <c r="AO48">
-        <v>0.18245</v>
+        <v>0.29225299999999999</v>
       </c>
       <c r="AP48">
         <v>54.245089</v>
@@ -15109,58 +15109,58 @@
         <v>26.997136000000001</v>
       </c>
       <c r="X49">
-        <v>9.3470999999999999E-2</v>
+        <v>0.14955399999999999</v>
       </c>
       <c r="Y49">
-        <v>0.111688</v>
+        <v>0.17094000000000001</v>
       </c>
       <c r="Z49">
-        <v>0.10872999999999999</v>
+        <v>0.17396800000000001</v>
       </c>
       <c r="AA49">
-        <v>9.4829999999999998E-2</v>
+        <v>0.151728</v>
       </c>
       <c r="AB49">
-        <v>0.103712</v>
+        <v>0.16594</v>
       </c>
       <c r="AC49">
-        <v>9.9979999999999999E-2</v>
+        <v>0.15997500000000001</v>
       </c>
       <c r="AD49">
-        <v>0.101101</v>
+        <v>0.16176199999999999</v>
       </c>
       <c r="AE49">
-        <v>0.114648</v>
+        <v>0.18343799999999999</v>
       </c>
       <c r="AF49">
-        <v>0.11859699999999999</v>
+        <v>0.18975500000000001</v>
       </c>
       <c r="AG49">
-        <v>0.112815</v>
+        <v>0.180504</v>
       </c>
       <c r="AH49">
-        <v>0.10648299999999999</v>
+        <v>0.17033599999999999</v>
       </c>
       <c r="AI49">
-        <v>0.105893</v>
+        <v>0.16922200000000001</v>
       </c>
       <c r="AJ49">
-        <v>0.16907700000000001</v>
+        <v>0.27052300000000001</v>
       </c>
       <c r="AK49">
-        <v>0.184248</v>
+        <v>0.29479699999999998</v>
       </c>
       <c r="AL49">
-        <v>0.193684</v>
+        <v>0.30649500000000002</v>
       </c>
       <c r="AM49">
-        <v>0.18796299999999999</v>
+        <v>0.29927300000000001</v>
       </c>
       <c r="AN49">
-        <v>0.180729</v>
+        <v>0.28841499999999998</v>
       </c>
       <c r="AO49">
-        <v>0.18720000000000001</v>
+        <v>0.29730899999999999</v>
       </c>
       <c r="AP49">
         <v>54.899351000000003</v>
@@ -15321,58 +15321,58 @@
         <v>27.028941</v>
       </c>
       <c r="X50">
-        <v>9.2904E-2</v>
+        <v>0.148647</v>
       </c>
       <c r="Y50">
-        <v>0.105777</v>
+        <v>0.165829</v>
       </c>
       <c r="Z50">
-        <v>0.113497</v>
+        <v>0.18159500000000001</v>
       </c>
       <c r="AA50">
-        <v>9.9834999999999993E-2</v>
+        <v>0.15973599999999999</v>
       </c>
       <c r="AB50">
-        <v>0.10390199999999999</v>
+        <v>0.166244</v>
       </c>
       <c r="AC50">
-        <v>0.101755</v>
+        <v>0.16281499999999999</v>
       </c>
       <c r="AD50">
-        <v>9.9708000000000005E-2</v>
+        <v>0.15953200000000001</v>
       </c>
       <c r="AE50">
-        <v>0.111595</v>
+        <v>0.17855199999999999</v>
       </c>
       <c r="AF50">
-        <v>0.12234100000000001</v>
+        <v>0.195746</v>
       </c>
       <c r="AG50">
-        <v>0.113967</v>
+        <v>0.18234700000000001</v>
       </c>
       <c r="AH50">
-        <v>0.104342</v>
+        <v>0.16719600000000001</v>
       </c>
       <c r="AI50">
-        <v>0.109717</v>
+        <v>0.17491999999999999</v>
       </c>
       <c r="AJ50">
-        <v>0.16939199999999999</v>
+        <v>0.27102700000000002</v>
       </c>
       <c r="AK50">
-        <v>0.17824799999999999</v>
+        <v>0.28519699999999998</v>
       </c>
       <c r="AL50">
-        <v>0.19808300000000001</v>
+        <v>0.31145600000000001</v>
       </c>
       <c r="AM50">
-        <v>0.19439400000000001</v>
+        <v>0.30574800000000002</v>
       </c>
       <c r="AN50">
-        <v>0.17904999999999999</v>
+        <v>0.28550700000000001</v>
       </c>
       <c r="AO50">
-        <v>0.19240199999999999</v>
+        <v>0.30265799999999998</v>
       </c>
       <c r="AP50">
         <v>55.423971000000002</v>
@@ -15533,58 +15533,58 @@
         <v>27.155783</v>
       </c>
       <c r="X51">
-        <v>9.2893000000000003E-2</v>
+        <v>0.14862800000000001</v>
       </c>
       <c r="Y51">
-        <v>0.10725999999999999</v>
+        <v>0.16603299999999999</v>
       </c>
       <c r="Z51">
-        <v>0.115963</v>
+        <v>0.18554000000000001</v>
       </c>
       <c r="AA51">
-        <v>0.104842</v>
+        <v>0.16774700000000001</v>
       </c>
       <c r="AB51">
-        <v>0.102716</v>
+        <v>0.16434599999999999</v>
       </c>
       <c r="AC51">
-        <v>0.103356</v>
+        <v>0.165377</v>
       </c>
       <c r="AD51">
-        <v>9.9720000000000003E-2</v>
+        <v>0.159552</v>
       </c>
       <c r="AE51">
-        <v>0.111628</v>
+        <v>0.17860599999999999</v>
       </c>
       <c r="AF51">
-        <v>0.124919</v>
+        <v>0.19986999999999999</v>
       </c>
       <c r="AG51">
-        <v>0.11304</v>
+        <v>0.180864</v>
       </c>
       <c r="AH51">
-        <v>0.103356</v>
+        <v>0.16575599999999999</v>
       </c>
       <c r="AI51">
-        <v>0.11188099999999999</v>
+        <v>0.178121</v>
       </c>
       <c r="AJ51">
-        <v>0.169124</v>
+        <v>0.27059899999999998</v>
       </c>
       <c r="AK51">
-        <v>0.17706</v>
+        <v>0.28329599999999999</v>
       </c>
       <c r="AL51">
-        <v>0.20030999999999999</v>
+        <v>0.31400400000000001</v>
       </c>
       <c r="AM51">
-        <v>0.19454399999999999</v>
+        <v>0.30605700000000002</v>
       </c>
       <c r="AN51">
-        <v>0.177728</v>
+        <v>0.28360999999999997</v>
       </c>
       <c r="AO51">
-        <v>0.19500700000000001</v>
+        <v>0.30530099999999999</v>
       </c>
       <c r="AP51">
         <v>56.259003</v>
@@ -15745,58 +15745,58 @@
         <v>27.564921999999999</v>
       </c>
       <c r="X52">
-        <v>9.6297999999999995E-2</v>
+        <v>0.15407699999999999</v>
       </c>
       <c r="Y52">
-        <v>0.105409</v>
+        <v>0.16667899999999999</v>
       </c>
       <c r="Z52">
-        <v>9.0951000000000004E-2</v>
+        <v>0.14552200000000001</v>
       </c>
       <c r="AA52">
-        <v>8.5878999999999997E-2</v>
+        <v>0.137406</v>
       </c>
       <c r="AB52">
-        <v>8.9662000000000006E-2</v>
+        <v>0.143459</v>
       </c>
       <c r="AC52">
-        <v>8.5292000000000007E-2</v>
+        <v>0.136461</v>
       </c>
       <c r="AD52">
-        <v>0.11214200000000001</v>
+        <v>0.179426</v>
       </c>
       <c r="AE52">
-        <v>0.11870799999999999</v>
+        <v>0.18993299999999999</v>
       </c>
       <c r="AF52">
-        <v>0.10584300000000001</v>
+        <v>0.169349</v>
       </c>
       <c r="AG52">
-        <v>0.10056900000000001</v>
+        <v>0.16091</v>
       </c>
       <c r="AH52">
-        <v>0.112312</v>
+        <v>0.17929100000000001</v>
       </c>
       <c r="AI52">
-        <v>0.107486</v>
+        <v>0.17186499999999999</v>
       </c>
       <c r="AJ52">
-        <v>0.18271999999999999</v>
+        <v>0.292352</v>
       </c>
       <c r="AK52">
-        <v>0.175817</v>
+        <v>0.281306</v>
       </c>
       <c r="AL52">
-        <v>0.17391100000000001</v>
+        <v>0.28326099999999999</v>
       </c>
       <c r="AM52">
-        <v>0.17114699999999999</v>
+        <v>0.279752</v>
       </c>
       <c r="AN52">
-        <v>0.18772800000000001</v>
+        <v>0.30291200000000001</v>
       </c>
       <c r="AO52">
-        <v>0.18770899999999999</v>
+        <v>0.29880099999999998</v>
       </c>
       <c r="AP52">
         <v>52.145544999999998</v>
@@ -15957,58 +15957,58 @@
         <v>27.687649</v>
       </c>
       <c r="X53">
-        <v>9.6776000000000001E-2</v>
+        <v>0.15484100000000001</v>
       </c>
       <c r="Y53">
-        <v>9.5732999999999999E-2</v>
+        <v>0.15779699999999999</v>
       </c>
       <c r="Z53">
-        <v>9.0661000000000005E-2</v>
+        <v>0.14505799999999999</v>
       </c>
       <c r="AA53">
-        <v>8.9344000000000007E-2</v>
+        <v>0.14294999999999999</v>
       </c>
       <c r="AB53">
-        <v>9.1749999999999998E-2</v>
+        <v>0.14679900000000001</v>
       </c>
       <c r="AC53">
-        <v>8.5414000000000004E-2</v>
+        <v>0.136657</v>
       </c>
       <c r="AD53">
-        <v>0.111873</v>
+        <v>0.17899599999999999</v>
       </c>
       <c r="AE53">
-        <v>0.11345</v>
+        <v>0.18151999999999999</v>
       </c>
       <c r="AF53">
-        <v>0.10563699999999999</v>
+        <v>0.169019</v>
       </c>
       <c r="AG53">
-        <v>0.10441300000000001</v>
+        <v>0.16706099999999999</v>
       </c>
       <c r="AH53">
-        <v>0.113761</v>
+        <v>0.18151500000000001</v>
       </c>
       <c r="AI53">
-        <v>0.10682899999999999</v>
+        <v>0.17081099999999999</v>
       </c>
       <c r="AJ53">
-        <v>0.181177</v>
+        <v>0.289883</v>
       </c>
       <c r="AK53">
-        <v>0.17206399999999999</v>
+        <v>0.27530199999999999</v>
       </c>
       <c r="AL53">
-        <v>0.17461499999999999</v>
+        <v>0.284057</v>
       </c>
       <c r="AM53">
-        <v>0.17741000000000001</v>
+        <v>0.28705700000000001</v>
       </c>
       <c r="AN53">
-        <v>0.19193199999999999</v>
+        <v>0.30724600000000002</v>
       </c>
       <c r="AO53">
-        <v>0.18714500000000001</v>
+        <v>0.298155</v>
       </c>
       <c r="AP53">
         <v>51.390807000000002</v>
@@ -16169,58 +16169,58 @@
         <v>27.768025000000002</v>
       </c>
       <c r="X54">
-        <v>9.8995E-2</v>
+        <v>0.15839200000000001</v>
       </c>
       <c r="Y54">
-        <v>9.2383000000000007E-2</v>
+        <v>0.15235099999999999</v>
       </c>
       <c r="Z54">
-        <v>9.4622999999999999E-2</v>
+        <v>0.151397</v>
       </c>
       <c r="AA54">
-        <v>9.6643999999999994E-2</v>
+        <v>0.15462999999999999</v>
       </c>
       <c r="AB54">
-        <v>9.5707E-2</v>
+        <v>0.15313099999999999</v>
       </c>
       <c r="AC54">
-        <v>8.8333999999999996E-2</v>
+        <v>0.14133200000000001</v>
       </c>
       <c r="AD54">
-        <v>0.109555</v>
+        <v>0.175288</v>
       </c>
       <c r="AE54">
-        <v>0.106451</v>
+        <v>0.170322</v>
       </c>
       <c r="AF54">
-        <v>0.107111</v>
+        <v>0.171378</v>
       </c>
       <c r="AG54">
-        <v>0.11095099999999999</v>
+        <v>0.17752100000000001</v>
       </c>
       <c r="AH54">
-        <v>0.115718</v>
+        <v>0.18432899999999999</v>
       </c>
       <c r="AI54">
-        <v>0.10510899999999999</v>
+        <v>0.16817599999999999</v>
       </c>
       <c r="AJ54">
-        <v>0.17887400000000001</v>
+        <v>0.28619899999999998</v>
       </c>
       <c r="AK54">
-        <v>0.169013</v>
+        <v>0.27041999999999999</v>
       </c>
       <c r="AL54">
-        <v>0.17594699999999999</v>
+        <v>0.28579399999999999</v>
       </c>
       <c r="AM54">
-        <v>0.18873200000000001</v>
+        <v>0.300095</v>
       </c>
       <c r="AN54">
-        <v>0.19792100000000001</v>
+        <v>0.31288500000000002</v>
       </c>
       <c r="AO54">
-        <v>0.18637400000000001</v>
+        <v>0.29704700000000001</v>
       </c>
       <c r="AP54">
         <v>51.379570999999999</v>
@@ -16381,58 +16381,58 @@
         <v>27.298787000000001</v>
       </c>
       <c r="X55">
-        <v>0.10299700000000001</v>
+        <v>0.164796</v>
       </c>
       <c r="Y55">
-        <v>9.4585000000000002E-2</v>
+        <v>0.15296599999999999</v>
       </c>
       <c r="Z55">
-        <v>0.10259600000000001</v>
+        <v>0.16415299999999999</v>
       </c>
       <c r="AA55">
-        <v>9.9584000000000006E-2</v>
+        <v>0.159334</v>
       </c>
       <c r="AB55">
-        <v>9.8752000000000006E-2</v>
+        <v>0.158003</v>
       </c>
       <c r="AC55">
-        <v>8.7056999999999995E-2</v>
+        <v>0.139288</v>
       </c>
       <c r="AD55">
-        <v>0.106888</v>
+        <v>0.17102100000000001</v>
       </c>
       <c r="AE55">
-        <v>0.10378900000000001</v>
+        <v>0.16606199999999999</v>
       </c>
       <c r="AF55">
-        <v>0.111358</v>
+        <v>0.178172</v>
       </c>
       <c r="AG55">
-        <v>0.112526</v>
+        <v>0.18004200000000001</v>
       </c>
       <c r="AH55">
-        <v>0.11586200000000001</v>
+        <v>0.18448700000000001</v>
       </c>
       <c r="AI55">
-        <v>0.102544</v>
+        <v>0.16436200000000001</v>
       </c>
       <c r="AJ55">
-        <v>0.17835899999999999</v>
+        <v>0.28537400000000002</v>
       </c>
       <c r="AK55">
-        <v>0.16856399999999999</v>
+        <v>0.269702</v>
       </c>
       <c r="AL55">
-        <v>0.18013499999999999</v>
+        <v>0.291107</v>
       </c>
       <c r="AM55">
-        <v>0.191827</v>
+        <v>0.30399599999999999</v>
       </c>
       <c r="AN55">
-        <v>0.19782</v>
+        <v>0.31270100000000001</v>
       </c>
       <c r="AO55">
-        <v>0.184169</v>
+        <v>0.29467199999999999</v>
       </c>
       <c r="AP55">
         <v>51.630420000000001</v>
@@ -16593,58 +16593,58 @@
         <v>26.807836000000002</v>
       </c>
       <c r="X56">
-        <v>0.10353</v>
+        <v>0.16564999999999999</v>
       </c>
       <c r="Y56">
-        <v>9.6889000000000003E-2</v>
+        <v>0.15457000000000001</v>
       </c>
       <c r="Z56">
-        <v>0.11045000000000001</v>
+        <v>0.17671999999999999</v>
       </c>
       <c r="AA56">
-        <v>0.104211</v>
+        <v>0.166738</v>
       </c>
       <c r="AB56">
-        <v>9.9363000000000007E-2</v>
+        <v>0.15898200000000001</v>
       </c>
       <c r="AC56">
-        <v>8.4305000000000005E-2</v>
+        <v>0.134883</v>
       </c>
       <c r="AD56">
-        <v>0.104909</v>
+        <v>0.167854</v>
       </c>
       <c r="AE56">
-        <v>0.10294200000000001</v>
+        <v>0.16470799999999999</v>
       </c>
       <c r="AF56">
-        <v>0.118663</v>
+        <v>0.189861</v>
       </c>
       <c r="AG56">
-        <v>0.11636100000000001</v>
+        <v>0.18617700000000001</v>
       </c>
       <c r="AH56">
-        <v>0.11466</v>
+        <v>0.18268200000000001</v>
       </c>
       <c r="AI56">
-        <v>0.100164</v>
+        <v>0.16088</v>
       </c>
       <c r="AJ56">
-        <v>0.17948500000000001</v>
+        <v>0.28717599999999999</v>
       </c>
       <c r="AK56">
-        <v>0.16986200000000001</v>
+        <v>0.27177899999999999</v>
       </c>
       <c r="AL56">
-        <v>0.18909000000000001</v>
+        <v>0.30124099999999998</v>
       </c>
       <c r="AM56">
-        <v>0.191826</v>
+        <v>0.30398799999999998</v>
       </c>
       <c r="AN56">
-        <v>0.193441</v>
+        <v>0.30812400000000001</v>
       </c>
       <c r="AO56">
-        <v>0.181648</v>
+        <v>0.29219699999999998</v>
       </c>
       <c r="AP56">
         <v>52.220823000000003</v>
@@ -16805,58 +16805,58 @@
         <v>26.695518</v>
       </c>
       <c r="X57">
-        <v>9.8155000000000006E-2</v>
+        <v>0.15704799999999999</v>
       </c>
       <c r="Y57">
-        <v>9.6949999999999995E-2</v>
+        <v>0.15345400000000001</v>
       </c>
       <c r="Z57">
-        <v>0.10939500000000001</v>
+        <v>0.17503199999999999</v>
       </c>
       <c r="AA57">
-        <v>0.102784</v>
+        <v>0.16445499999999999</v>
       </c>
       <c r="AB57">
-        <v>9.7111000000000003E-2</v>
+        <v>0.15537699999999999</v>
       </c>
       <c r="AC57">
-        <v>8.5683999999999996E-2</v>
+        <v>0.13708999999999999</v>
       </c>
       <c r="AD57">
-        <v>0.10223500000000001</v>
+        <v>0.163576</v>
       </c>
       <c r="AE57">
-        <v>0.10004300000000001</v>
+        <v>0.16006799999999999</v>
       </c>
       <c r="AF57">
-        <v>0.119889</v>
+        <v>0.19182199999999999</v>
       </c>
       <c r="AG57">
-        <v>0.11441</v>
+        <v>0.183055</v>
       </c>
       <c r="AH57">
-        <v>0.11294899999999999</v>
+        <v>0.180058</v>
       </c>
       <c r="AI57">
-        <v>9.9635000000000001E-2</v>
+        <v>0.160027</v>
       </c>
       <c r="AJ57">
-        <v>0.176791</v>
+        <v>0.28286600000000001</v>
       </c>
       <c r="AK57">
-        <v>0.16878899999999999</v>
+        <v>0.27006200000000002</v>
       </c>
       <c r="AL57">
-        <v>0.189836</v>
+        <v>0.30197099999999999</v>
       </c>
       <c r="AM57">
-        <v>0.18879499999999999</v>
+        <v>0.30041699999999999</v>
       </c>
       <c r="AN57">
-        <v>0.188252</v>
+        <v>0.30199700000000002</v>
       </c>
       <c r="AO57">
-        <v>0.180814</v>
+        <v>0.29128500000000002</v>
       </c>
       <c r="AP57">
         <v>52.966684000000001</v>
@@ -17017,58 +17017,58 @@
         <v>26.726752000000001</v>
       </c>
       <c r="X58">
-        <v>9.2969999999999997E-2</v>
+        <v>0.148752</v>
       </c>
       <c r="Y58">
-        <v>9.3504000000000004E-2</v>
+        <v>0.14738200000000001</v>
       </c>
       <c r="Z58">
-        <v>0.100771</v>
+        <v>0.16123399999999999</v>
       </c>
       <c r="AA58">
-        <v>9.8575999999999997E-2</v>
+        <v>0.157722</v>
       </c>
       <c r="AB58">
-        <v>9.7141000000000005E-2</v>
+        <v>0.15542600000000001</v>
       </c>
       <c r="AC58">
-        <v>9.3637999999999999E-2</v>
+        <v>0.14982400000000001</v>
       </c>
       <c r="AD58">
-        <v>0.100109</v>
+        <v>0.16017500000000001</v>
       </c>
       <c r="AE58">
-        <v>9.6231999999999998E-2</v>
+        <v>0.153972</v>
       </c>
       <c r="AF58">
-        <v>0.110946</v>
+        <v>0.17751400000000001</v>
       </c>
       <c r="AG58">
-        <v>0.109473</v>
+        <v>0.17515600000000001</v>
       </c>
       <c r="AH58">
-        <v>0.11013000000000001</v>
+        <v>0.17585899999999999</v>
       </c>
       <c r="AI58">
-        <v>0.100909</v>
+        <v>0.161769</v>
       </c>
       <c r="AJ58">
-        <v>0.17293</v>
+        <v>0.27668799999999999</v>
       </c>
       <c r="AK58">
-        <v>0.163997</v>
+        <v>0.26239499999999999</v>
       </c>
       <c r="AL58">
-        <v>0.18354200000000001</v>
+        <v>0.294408</v>
       </c>
       <c r="AM58">
-        <v>0.18648000000000001</v>
+        <v>0.29709400000000002</v>
       </c>
       <c r="AN58">
-        <v>0.183841</v>
+        <v>0.29609400000000002</v>
       </c>
       <c r="AO58">
-        <v>0.182201</v>
+        <v>0.29245100000000002</v>
       </c>
       <c r="AP58">
         <v>53.795760000000001</v>
@@ -17229,58 +17229,58 @@
         <v>26.558602</v>
       </c>
       <c r="X59">
-        <v>8.8883000000000004E-2</v>
+        <v>0.14221300000000001</v>
       </c>
       <c r="Y59">
-        <v>8.1493999999999997E-2</v>
+        <v>0.13422799999999999</v>
       </c>
       <c r="Z59">
-        <v>9.1208999999999998E-2</v>
+        <v>0.14593400000000001</v>
       </c>
       <c r="AA59">
-        <v>8.7764999999999996E-2</v>
+        <v>0.14042399999999999</v>
       </c>
       <c r="AB59">
-        <v>9.6937999999999996E-2</v>
+        <v>0.15509999999999999</v>
       </c>
       <c r="AC59">
-        <v>9.3102000000000004E-2</v>
+        <v>0.14896400000000001</v>
       </c>
       <c r="AD59">
-        <v>9.7929000000000002E-2</v>
+        <v>0.15668699999999999</v>
       </c>
       <c r="AE59">
-        <v>9.1586000000000001E-2</v>
+        <v>0.146538</v>
       </c>
       <c r="AF59">
-        <v>0.100298</v>
+        <v>0.16047600000000001</v>
       </c>
       <c r="AG59">
-        <v>0.10306700000000001</v>
+        <v>0.164907</v>
       </c>
       <c r="AH59">
-        <v>0.106264</v>
+        <v>0.17024400000000001</v>
       </c>
       <c r="AI59">
-        <v>0.101656</v>
+        <v>0.16291900000000001</v>
       </c>
       <c r="AJ59">
-        <v>0.172652</v>
+        <v>0.27624399999999999</v>
       </c>
       <c r="AK59">
-        <v>0.15545500000000001</v>
+        <v>0.248728</v>
       </c>
       <c r="AL59">
-        <v>0.176595</v>
+        <v>0.28613899999999998</v>
       </c>
       <c r="AM59">
-        <v>0.18187300000000001</v>
+        <v>0.29144900000000001</v>
       </c>
       <c r="AN59">
-        <v>0.18059</v>
+        <v>0.29109600000000002</v>
       </c>
       <c r="AO59">
-        <v>0.18326500000000001</v>
+        <v>0.29358299999999998</v>
       </c>
       <c r="AP59">
         <v>54.961114999999999</v>
@@ -17441,58 +17441,58 @@
         <v>26.248830999999999</v>
       </c>
       <c r="X60">
-        <v>8.4512000000000004E-2</v>
+        <v>0.13521900000000001</v>
       </c>
       <c r="Y60">
-        <v>6.9647000000000001E-2</v>
+        <v>0.121708</v>
       </c>
       <c r="Z60">
-        <v>8.4764000000000006E-2</v>
+        <v>0.13562199999999999</v>
       </c>
       <c r="AA60">
-        <v>8.1365000000000007E-2</v>
+        <v>0.13018399999999999</v>
       </c>
       <c r="AB60">
-        <v>9.2230000000000006E-2</v>
+        <v>0.147567</v>
       </c>
       <c r="AC60">
-        <v>9.2910999999999994E-2</v>
+        <v>0.14865999999999999</v>
       </c>
       <c r="AD60">
-        <v>9.5136999999999999E-2</v>
+        <v>0.15221899999999999</v>
       </c>
       <c r="AE60">
-        <v>8.5760000000000003E-2</v>
+        <v>0.13721700000000001</v>
       </c>
       <c r="AF60">
-        <v>9.2789999999999997E-2</v>
+        <v>0.14846400000000001</v>
       </c>
       <c r="AG60">
-        <v>9.4483999999999999E-2</v>
+        <v>0.151175</v>
       </c>
       <c r="AH60">
-        <v>0.102122</v>
+        <v>0.16431499999999999</v>
       </c>
       <c r="AI60">
-        <v>0.10266</v>
+        <v>0.16444800000000001</v>
       </c>
       <c r="AJ60">
-        <v>0.16713800000000001</v>
+        <v>0.26742100000000002</v>
       </c>
       <c r="AK60">
-        <v>0.14504500000000001</v>
+        <v>0.232072</v>
       </c>
       <c r="AL60">
-        <v>0.166736</v>
+        <v>0.275034</v>
       </c>
       <c r="AM60">
-        <v>0.17024800000000001</v>
+        <v>0.27863500000000002</v>
       </c>
       <c r="AN60">
-        <v>0.176286</v>
+        <v>0.28559499999999999</v>
       </c>
       <c r="AO60">
-        <v>0.185447</v>
+        <v>0.295649</v>
       </c>
       <c r="AP60">
         <v>55.899796000000002</v>
@@ -17653,58 +17653,58 @@
         <v>26.136261000000001</v>
       </c>
       <c r="X61">
-        <v>8.2477999999999996E-2</v>
+        <v>0.131965</v>
       </c>
       <c r="Y61">
-        <v>6.8695999999999993E-2</v>
+        <v>0.11941499999999999</v>
       </c>
       <c r="Z61">
-        <v>8.3238999999999994E-2</v>
+        <v>0.13318199999999999</v>
       </c>
       <c r="AA61">
-        <v>8.1666000000000002E-2</v>
+        <v>0.130666</v>
       </c>
       <c r="AB61">
-        <v>8.7695999999999996E-2</v>
+        <v>0.14031299999999999</v>
       </c>
       <c r="AC61">
-        <v>9.2931E-2</v>
+        <v>0.14869199999999999</v>
       </c>
       <c r="AD61">
-        <v>9.4633999999999996E-2</v>
+        <v>0.15141499999999999</v>
       </c>
       <c r="AE61">
-        <v>8.5099999999999995E-2</v>
+        <v>0.136159</v>
       </c>
       <c r="AF61">
-        <v>9.1553999999999996E-2</v>
+        <v>0.14648600000000001</v>
       </c>
       <c r="AG61">
-        <v>8.9815000000000006E-2</v>
+        <v>0.143705</v>
       </c>
       <c r="AH61">
-        <v>9.9585000000000007E-2</v>
+        <v>0.160718</v>
       </c>
       <c r="AI61">
-        <v>0.10352600000000001</v>
+        <v>0.16574700000000001</v>
       </c>
       <c r="AJ61">
-        <v>0.16321099999999999</v>
+        <v>0.26113799999999998</v>
       </c>
       <c r="AK61">
-        <v>0.142181</v>
+        <v>0.227489</v>
       </c>
       <c r="AL61">
-        <v>0.162055</v>
+        <v>0.26967400000000002</v>
       </c>
       <c r="AM61">
-        <v>0.163295</v>
+        <v>0.27099200000000001</v>
       </c>
       <c r="AN61">
-        <v>0.17293600000000001</v>
+        <v>0.28157799999999999</v>
       </c>
       <c r="AO61">
-        <v>0.18678800000000001</v>
+        <v>0.29690899999999998</v>
       </c>
       <c r="AP61">
         <v>56.787066000000003</v>
@@ -17862,58 +17862,58 @@
         <v>29.584893000000001</v>
       </c>
       <c r="X62">
-        <v>9.9266999999999994E-2</v>
+        <v>0.158828</v>
       </c>
       <c r="Y62">
-        <v>0.109815</v>
+        <v>0.172128</v>
       </c>
       <c r="Z62">
-        <v>8.9338000000000001E-2</v>
+        <v>0.14294100000000001</v>
       </c>
       <c r="AA62">
-        <v>8.7673000000000001E-2</v>
+        <v>0.14027700000000001</v>
       </c>
       <c r="AB62">
-        <v>9.5280000000000004E-2</v>
+        <v>0.152448</v>
       </c>
       <c r="AC62">
-        <v>0.103685</v>
+        <v>0.165905</v>
       </c>
       <c r="AD62">
-        <v>0.11534</v>
+        <v>0.18454400000000001</v>
       </c>
       <c r="AE62">
-        <v>0.117855</v>
+        <v>0.18856800000000001</v>
       </c>
       <c r="AF62">
-        <v>0.10136299999999999</v>
+        <v>0.16218099999999999</v>
       </c>
       <c r="AG62">
-        <v>0.105451</v>
+        <v>0.16872100000000001</v>
       </c>
       <c r="AH62">
-        <v>0.11590399999999999</v>
+        <v>0.18424499999999999</v>
       </c>
       <c r="AI62">
-        <v>0.11539000000000001</v>
+        <v>0.18326100000000001</v>
       </c>
       <c r="AJ62">
-        <v>0.182198</v>
+        <v>0.29151700000000003</v>
       </c>
       <c r="AK62">
-        <v>0.17669199999999999</v>
+        <v>0.28270800000000001</v>
       </c>
       <c r="AL62">
-        <v>0.173319</v>
+        <v>0.28205200000000002</v>
       </c>
       <c r="AM62">
-        <v>0.174646</v>
+        <v>0.28373999999999999</v>
       </c>
       <c r="AN62">
-        <v>0.18759400000000001</v>
+        <v>0.30254300000000001</v>
       </c>
       <c r="AO62">
-        <v>0.19574</v>
+        <v>0.30713600000000002</v>
       </c>
       <c r="AP62">
         <v>52.692836</v>
@@ -18071,58 +18071,58 @@
         <v>29.438814000000001</v>
       </c>
       <c r="X63">
-        <v>9.7700999999999996E-2</v>
+        <v>0.15632199999999999</v>
       </c>
       <c r="Y63">
-        <v>0.103357</v>
+        <v>0.165494</v>
       </c>
       <c r="Z63">
-        <v>9.0991000000000002E-2</v>
+        <v>0.14558599999999999</v>
       </c>
       <c r="AA63">
-        <v>9.2696000000000001E-2</v>
+        <v>0.148314</v>
       </c>
       <c r="AB63">
-        <v>9.5804E-2</v>
+        <v>0.15328700000000001</v>
       </c>
       <c r="AC63">
-        <v>0.101797</v>
+        <v>0.162883</v>
       </c>
       <c r="AD63">
-        <v>0.112968</v>
+        <v>0.18074899999999999</v>
       </c>
       <c r="AE63">
-        <v>0.114301</v>
+        <v>0.18288199999999999</v>
       </c>
       <c r="AF63">
-        <v>0.10424</v>
+        <v>0.16678499999999999</v>
       </c>
       <c r="AG63">
-        <v>0.11006199999999999</v>
+        <v>0.17609900000000001</v>
       </c>
       <c r="AH63">
-        <v>0.115981</v>
+        <v>0.184609</v>
       </c>
       <c r="AI63">
-        <v>0.113258</v>
+        <v>0.18019299999999999</v>
       </c>
       <c r="AJ63">
-        <v>0.183034</v>
+        <v>0.292854</v>
       </c>
       <c r="AK63">
-        <v>0.17458299999999999</v>
+        <v>0.279333</v>
       </c>
       <c r="AL63">
-        <v>0.17579900000000001</v>
+        <v>0.284854</v>
       </c>
       <c r="AM63">
-        <v>0.18168300000000001</v>
+        <v>0.291823</v>
       </c>
       <c r="AN63">
-        <v>0.18790699999999999</v>
+        <v>0.30385000000000001</v>
       </c>
       <c r="AO63">
-        <v>0.19308400000000001</v>
+        <v>0.30482199999999998</v>
       </c>
       <c r="AP63">
         <v>52.358317</v>
@@ -18280,58 +18280,58 @@
         <v>29.11082</v>
       </c>
       <c r="X64">
-        <v>9.5882999999999996E-2</v>
+        <v>0.15341199999999999</v>
       </c>
       <c r="Y64">
-        <v>9.8944000000000004E-2</v>
+        <v>0.15896099999999999</v>
       </c>
       <c r="Z64">
-        <v>9.5691999999999999E-2</v>
+        <v>0.15310699999999999</v>
       </c>
       <c r="AA64">
-        <v>0.105597</v>
+        <v>0.16895499999999999</v>
       </c>
       <c r="AB64">
-        <v>9.9427000000000001E-2</v>
+        <v>0.159082</v>
       </c>
       <c r="AC64">
-        <v>9.5907999999999993E-2</v>
+        <v>0.15345500000000001</v>
       </c>
       <c r="AD64">
-        <v>0.10919</v>
+        <v>0.174703</v>
       </c>
       <c r="AE64">
-        <v>0.108102</v>
+        <v>0.17296400000000001</v>
       </c>
       <c r="AF64">
-        <v>0.10718900000000001</v>
+        <v>0.17150199999999999</v>
       </c>
       <c r="AG64">
-        <v>0.11952699999999999</v>
+        <v>0.191243</v>
       </c>
       <c r="AH64">
-        <v>0.11647200000000001</v>
+        <v>0.185421</v>
       </c>
       <c r="AI64">
-        <v>0.109039</v>
+        <v>0.17411799999999999</v>
       </c>
       <c r="AJ64">
-        <v>0.184007</v>
+        <v>0.29441200000000001</v>
       </c>
       <c r="AK64">
-        <v>0.16902</v>
+        <v>0.27043099999999998</v>
       </c>
       <c r="AL64">
-        <v>0.176732</v>
+        <v>0.28667799999999999</v>
       </c>
       <c r="AM64">
-        <v>0.19527900000000001</v>
+        <v>0.30737399999999998</v>
       </c>
       <c r="AN64">
-        <v>0.19226199999999999</v>
+        <v>0.30849900000000002</v>
       </c>
       <c r="AO64">
-        <v>0.189133</v>
+        <v>0.30110799999999999</v>
       </c>
       <c r="AP64">
         <v>51.711792000000003</v>
@@ -18489,58 +18489,58 @@
         <v>28.828244999999999</v>
       </c>
       <c r="X65">
-        <v>9.5311999999999994E-2</v>
+        <v>0.15249799999999999</v>
       </c>
       <c r="Y65">
-        <v>9.6351000000000006E-2</v>
+        <v>0.154309</v>
       </c>
       <c r="Z65">
-        <v>0.104537</v>
+        <v>0.16725899999999999</v>
       </c>
       <c r="AA65">
-        <v>0.110681</v>
+        <v>0.17709</v>
       </c>
       <c r="AB65">
-        <v>0.102884</v>
+        <v>0.16461400000000001</v>
       </c>
       <c r="AC65">
-        <v>9.3568999999999999E-2</v>
+        <v>0.14971100000000001</v>
       </c>
       <c r="AD65">
-        <v>0.106033</v>
+        <v>0.169653</v>
       </c>
       <c r="AE65">
-        <v>0.103064</v>
+        <v>0.16490199999999999</v>
       </c>
       <c r="AF65">
-        <v>0.11258899999999999</v>
+        <v>0.180142</v>
       </c>
       <c r="AG65">
-        <v>0.121101</v>
+        <v>0.19376199999999999</v>
       </c>
       <c r="AH65">
-        <v>0.116782</v>
+        <v>0.18579599999999999</v>
       </c>
       <c r="AI65">
-        <v>0.10631</v>
+        <v>0.170013</v>
       </c>
       <c r="AJ65">
-        <v>0.18237900000000001</v>
+        <v>0.29180600000000001</v>
       </c>
       <c r="AK65">
-        <v>0.16528799999999999</v>
+        <v>0.26445999999999997</v>
       </c>
       <c r="AL65">
-        <v>0.185032</v>
+        <v>0.29650900000000002</v>
       </c>
       <c r="AM65">
-        <v>0.20039999999999999</v>
+        <v>0.31352799999999997</v>
       </c>
       <c r="AN65">
-        <v>0.197435</v>
+        <v>0.31326900000000002</v>
       </c>
       <c r="AO65">
-        <v>0.18738199999999999</v>
+        <v>0.29900300000000002</v>
       </c>
       <c r="AP65">
         <v>51.598053999999998</v>
@@ -18698,58 +18698,58 @@
         <v>28.410345</v>
       </c>
       <c r="X66">
-        <v>9.5134999999999997E-2</v>
+        <v>0.15221599999999999</v>
       </c>
       <c r="Y66">
-        <v>9.3608999999999998E-2</v>
+        <v>0.14969199999999999</v>
       </c>
       <c r="Z66">
-        <v>0.11208899999999999</v>
+        <v>0.179342</v>
       </c>
       <c r="AA66">
-        <v>0.11344700000000001</v>
+        <v>0.18151500000000001</v>
       </c>
       <c r="AB66">
-        <v>0.10455299999999999</v>
+        <v>0.16728599999999999</v>
       </c>
       <c r="AC66">
-        <v>9.2688999999999994E-2</v>
+        <v>0.14830099999999999</v>
       </c>
       <c r="AD66">
-        <v>0.104028</v>
+        <v>0.16644500000000001</v>
       </c>
       <c r="AE66">
-        <v>9.9194000000000004E-2</v>
+        <v>0.15870999999999999</v>
       </c>
       <c r="AF66">
-        <v>0.118008</v>
+        <v>0.18881300000000001</v>
       </c>
       <c r="AG66">
-        <v>0.119644</v>
+        <v>0.19142999999999999</v>
       </c>
       <c r="AH66">
-        <v>0.11613900000000001</v>
+        <v>0.18474499999999999</v>
       </c>
       <c r="AI66">
-        <v>0.10440099999999999</v>
+        <v>0.167049</v>
       </c>
       <c r="AJ66">
-        <v>0.18063699999999999</v>
+        <v>0.28902</v>
       </c>
       <c r="AK66">
-        <v>0.16409000000000001</v>
+        <v>0.26254499999999997</v>
       </c>
       <c r="AL66">
-        <v>0.19624800000000001</v>
+        <v>0.30921500000000002</v>
       </c>
       <c r="AM66">
-        <v>0.19921700000000001</v>
+        <v>0.31254700000000002</v>
       </c>
       <c r="AN66">
-        <v>0.19855900000000001</v>
+        <v>0.31389099999999998</v>
       </c>
       <c r="AO66">
-        <v>0.186392</v>
+        <v>0.29746</v>
       </c>
       <c r="AP66">
         <v>52.212330000000001</v>
@@ -18907,58 +18907,58 @@
         <v>28.024173000000001</v>
       </c>
       <c r="X67">
-        <v>9.2469999999999997E-2</v>
+        <v>0.147953</v>
       </c>
       <c r="Y67">
-        <v>9.0219999999999995E-2</v>
+        <v>0.14322699999999999</v>
       </c>
       <c r="Z67">
-        <v>0.10657899999999999</v>
+        <v>0.17052600000000001</v>
       </c>
       <c r="AA67">
-        <v>0.106918</v>
+        <v>0.171069</v>
       </c>
       <c r="AB67">
-        <v>0.100633</v>
+        <v>0.16101299999999999</v>
       </c>
       <c r="AC67">
-        <v>9.5376000000000002E-2</v>
+        <v>0.15260299999999999</v>
       </c>
       <c r="AD67">
-        <v>0.102131</v>
+        <v>0.163409</v>
       </c>
       <c r="AE67">
-        <v>9.6409999999999996E-2</v>
+        <v>0.15425700000000001</v>
       </c>
       <c r="AF67">
-        <v>0.113181</v>
+        <v>0.18109</v>
       </c>
       <c r="AG67">
-        <v>0.11466</v>
+        <v>0.18345600000000001</v>
       </c>
       <c r="AH67">
-        <v>0.11411499999999999</v>
+        <v>0.18170600000000001</v>
       </c>
       <c r="AI67">
-        <v>0.103079</v>
+        <v>0.164938</v>
       </c>
       <c r="AJ67">
-        <v>0.17710000000000001</v>
+        <v>0.28336</v>
       </c>
       <c r="AK67">
-        <v>0.16336899999999999</v>
+        <v>0.26139000000000001</v>
       </c>
       <c r="AL67">
-        <v>0.192109</v>
+        <v>0.30457400000000001</v>
       </c>
       <c r="AM67">
-        <v>0.193525</v>
+        <v>0.30624600000000002</v>
       </c>
       <c r="AN67">
-        <v>0.194961</v>
+        <v>0.30960700000000002</v>
       </c>
       <c r="AO67">
-        <v>0.185279</v>
+        <v>0.29582199999999997</v>
       </c>
       <c r="AP67">
         <v>53.127608000000002</v>
@@ -19116,58 +19116,58 @@
         <v>27.689267999999998</v>
       </c>
       <c r="X68">
-        <v>8.6743000000000001E-2</v>
+        <v>0.138789</v>
       </c>
       <c r="Y68">
-        <v>8.0939999999999998E-2</v>
+        <v>0.13062199999999999</v>
       </c>
       <c r="Z68">
-        <v>9.1823000000000002E-2</v>
+        <v>0.14691699999999999</v>
       </c>
       <c r="AA68">
-        <v>9.5822000000000004E-2</v>
+        <v>0.15331500000000001</v>
       </c>
       <c r="AB68">
-        <v>9.6943000000000001E-2</v>
+        <v>0.155109</v>
       </c>
       <c r="AC68">
-        <v>9.6012E-2</v>
+        <v>0.15362400000000001</v>
       </c>
       <c r="AD68">
-        <v>9.9297999999999997E-2</v>
+        <v>0.15887699999999999</v>
       </c>
       <c r="AE68">
-        <v>9.3118000000000006E-2</v>
+        <v>0.14898800000000001</v>
       </c>
       <c r="AF68">
-        <v>0.10141500000000001</v>
+        <v>0.16226399999999999</v>
       </c>
       <c r="AG68">
-        <v>0.111327</v>
+        <v>0.178124</v>
       </c>
       <c r="AH68">
-        <v>0.112288</v>
+        <v>0.17885799999999999</v>
       </c>
       <c r="AI68">
-        <v>0.10222299999999999</v>
+        <v>0.163498</v>
       </c>
       <c r="AJ68">
-        <v>0.17238400000000001</v>
+        <v>0.275814</v>
       </c>
       <c r="AK68">
-        <v>0.15737999999999999</v>
+        <v>0.25180900000000001</v>
       </c>
       <c r="AL68">
-        <v>0.17835699999999999</v>
+        <v>0.28848299999999999</v>
       </c>
       <c r="AM68">
-        <v>0.18678700000000001</v>
+        <v>0.29824400000000001</v>
       </c>
       <c r="AN68">
-        <v>0.19158600000000001</v>
+        <v>0.304703</v>
       </c>
       <c r="AO68">
-        <v>0.18337899999999999</v>
+        <v>0.29357100000000003</v>
       </c>
       <c r="AP68">
         <v>54.169590999999997</v>
@@ -19325,58 +19325,58 @@
         <v>27.049903</v>
       </c>
       <c r="X69">
-        <v>8.1592999999999999E-2</v>
+        <v>0.130548</v>
       </c>
       <c r="Y69">
-        <v>6.7908999999999997E-2</v>
+        <v>0.11550199999999999</v>
       </c>
       <c r="Z69">
-        <v>7.9582E-2</v>
+        <v>0.127331</v>
       </c>
       <c r="AA69">
-        <v>8.9688000000000004E-2</v>
+        <v>0.14349999999999999</v>
       </c>
       <c r="AB69">
-        <v>9.4404000000000002E-2</v>
+        <v>0.15104600000000001</v>
       </c>
       <c r="AC69">
-        <v>8.6817000000000005E-2</v>
+        <v>0.138904</v>
       </c>
       <c r="AD69">
-        <v>9.6361000000000002E-2</v>
+        <v>0.15417800000000001</v>
       </c>
       <c r="AE69">
-        <v>8.7416999999999995E-2</v>
+        <v>0.13986799999999999</v>
       </c>
       <c r="AF69">
-        <v>9.1538999999999995E-2</v>
+        <v>0.14646200000000001</v>
       </c>
       <c r="AG69">
-        <v>0.108478</v>
+        <v>0.173564</v>
       </c>
       <c r="AH69">
-        <v>0.10999</v>
+        <v>0.175372</v>
       </c>
       <c r="AI69">
-        <v>9.9704000000000001E-2</v>
+        <v>0.15990199999999999</v>
       </c>
       <c r="AJ69">
-        <v>0.169684</v>
+        <v>0.27149499999999999</v>
       </c>
       <c r="AK69">
-        <v>0.147818</v>
+        <v>0.236508</v>
       </c>
       <c r="AL69">
-        <v>0.16722200000000001</v>
+        <v>0.27566200000000002</v>
       </c>
       <c r="AM69">
-        <v>0.181252</v>
+        <v>0.29165200000000002</v>
       </c>
       <c r="AN69">
-        <v>0.18914600000000001</v>
+        <v>0.30025499999999999</v>
       </c>
       <c r="AO69">
-        <v>0.17988799999999999</v>
+        <v>0.29017700000000002</v>
       </c>
       <c r="AP69">
         <v>55.329680000000003</v>
@@ -19534,58 +19534,58 @@
         <v>26.698547000000001</v>
       </c>
       <c r="X70">
-        <v>7.8660999999999995E-2</v>
+        <v>0.125857</v>
       </c>
       <c r="Y70">
-        <v>6.2259000000000002E-2</v>
+        <v>0.107852</v>
       </c>
       <c r="Z70">
-        <v>7.7463000000000004E-2</v>
+        <v>0.123941</v>
       </c>
       <c r="AA70">
-        <v>9.0195999999999998E-2</v>
+        <v>0.144314</v>
       </c>
       <c r="AB70">
-        <v>9.3716999999999995E-2</v>
+        <v>0.149948</v>
       </c>
       <c r="AC70">
-        <v>8.7919999999999998E-2</v>
+        <v>0.14066999999999999</v>
       </c>
       <c r="AD70">
-        <v>9.4603999999999994E-2</v>
+        <v>0.151367</v>
       </c>
       <c r="AE70">
-        <v>8.3015000000000005E-2</v>
+        <v>0.132824</v>
       </c>
       <c r="AF70">
-        <v>9.1427999999999995E-2</v>
+        <v>0.146285</v>
       </c>
       <c r="AG70">
-        <v>0.108392</v>
+        <v>0.173427</v>
       </c>
       <c r="AH70">
-        <v>0.107172</v>
+        <v>0.17124300000000001</v>
       </c>
       <c r="AI70">
-        <v>9.9587999999999996E-2</v>
+        <v>0.159664</v>
       </c>
       <c r="AJ70">
-        <v>0.16675999999999999</v>
+        <v>0.266816</v>
       </c>
       <c r="AK70">
-        <v>0.14080799999999999</v>
+        <v>0.22529299999999999</v>
       </c>
       <c r="AL70">
-        <v>0.169624</v>
+        <v>0.27803600000000001</v>
       </c>
       <c r="AM70">
-        <v>0.181061</v>
+        <v>0.29060000000000002</v>
       </c>
       <c r="AN70">
-        <v>0.185973</v>
+        <v>0.295267</v>
       </c>
       <c r="AO70">
-        <v>0.18007100000000001</v>
+        <v>0.28997099999999998</v>
       </c>
       <c r="AP70">
         <v>56.220613</v>
@@ -19743,58 +19743,58 @@
         <v>26.675516999999999</v>
       </c>
       <c r="X71">
-        <v>7.7717999999999995E-2</v>
+        <v>0.124349</v>
       </c>
       <c r="Y71">
-        <v>6.2896999999999995E-2</v>
+        <v>0.107822</v>
       </c>
       <c r="Z71">
-        <v>7.9210000000000003E-2</v>
+        <v>0.12673599999999999</v>
       </c>
       <c r="AA71">
-        <v>9.0598999999999999E-2</v>
+        <v>0.144959</v>
       </c>
       <c r="AB71">
-        <v>9.3608999999999998E-2</v>
+        <v>0.14977499999999999</v>
       </c>
       <c r="AC71">
-        <v>8.9881000000000003E-2</v>
+        <v>0.14380899999999999</v>
       </c>
       <c r="AD71">
-        <v>9.3997999999999998E-2</v>
+        <v>0.150397</v>
       </c>
       <c r="AE71">
-        <v>8.2687999999999998E-2</v>
+        <v>0.132301</v>
       </c>
       <c r="AF71">
-        <v>9.4919000000000003E-2</v>
+        <v>0.15187</v>
       </c>
       <c r="AG71">
-        <v>0.108761</v>
+        <v>0.17401800000000001</v>
       </c>
       <c r="AH71">
-        <v>0.105297</v>
+        <v>0.16856199999999999</v>
       </c>
       <c r="AI71">
-        <v>0.100601</v>
+        <v>0.16104499999999999</v>
       </c>
       <c r="AJ71">
-        <v>0.16464999999999999</v>
+        <v>0.26343899999999998</v>
       </c>
       <c r="AK71">
-        <v>0.13994300000000001</v>
+        <v>0.223909</v>
       </c>
       <c r="AL71">
-        <v>0.17324800000000001</v>
+        <v>0.28190199999999999</v>
       </c>
       <c r="AM71">
-        <v>0.18083099999999999</v>
+        <v>0.29002299999999998</v>
       </c>
       <c r="AN71">
-        <v>0.182835</v>
+        <v>0.29115099999999999</v>
       </c>
       <c r="AO71">
-        <v>0.18113499999999999</v>
+        <v>0.29071000000000002</v>
       </c>
       <c r="AP71">
         <v>56.6477</v>
@@ -19955,58 +19955,58 @@
         <v>30.313672</v>
       </c>
       <c r="X72">
-        <v>0.101937</v>
+        <v>0.16309999999999999</v>
       </c>
       <c r="Y72">
-        <v>0.10703</v>
+        <v>0.168293</v>
       </c>
       <c r="Z72">
-        <v>9.1406000000000001E-2</v>
+        <v>0.14624999999999999</v>
       </c>
       <c r="AA72">
-        <v>9.4187000000000007E-2</v>
+        <v>0.1507</v>
       </c>
       <c r="AB72">
-        <v>0.102418</v>
+        <v>0.16386800000000001</v>
       </c>
       <c r="AC72">
-        <v>0.100492</v>
+        <v>0.16079199999999999</v>
       </c>
       <c r="AD72">
-        <v>0.115326</v>
+        <v>0.18452199999999999</v>
       </c>
       <c r="AE72">
-        <v>0.115755</v>
+        <v>0.18520800000000001</v>
       </c>
       <c r="AF72">
-        <v>0.100381</v>
+        <v>0.160609</v>
       </c>
       <c r="AG72">
-        <v>0.108866</v>
+        <v>0.17418500000000001</v>
       </c>
       <c r="AH72">
-        <v>0.120296</v>
+        <v>0.19001499999999999</v>
       </c>
       <c r="AI72">
-        <v>0.11650099999999999</v>
+        <v>0.185116</v>
       </c>
       <c r="AJ72">
-        <v>0.18390100000000001</v>
+        <v>0.29424099999999997</v>
       </c>
       <c r="AK72">
-        <v>0.17713599999999999</v>
+        <v>0.283418</v>
       </c>
       <c r="AL72">
-        <v>0.17372299999999999</v>
+        <v>0.28254000000000001</v>
       </c>
       <c r="AM72">
-        <v>0.17319100000000001</v>
+        <v>0.28099299999999999</v>
       </c>
       <c r="AN72">
-        <v>0.192885</v>
+        <v>0.30590800000000001</v>
       </c>
       <c r="AO72">
-        <v>0.19819400000000001</v>
+        <v>0.31026900000000002</v>
       </c>
       <c r="AP72">
         <v>52.027692999999999</v>
@@ -20167,58 +20167,58 @@
         <v>30.006543000000001</v>
       </c>
       <c r="X73">
-        <v>9.8637000000000002E-2</v>
+        <v>0.15781999999999999</v>
       </c>
       <c r="Y73">
-        <v>0.10366300000000001</v>
+        <v>0.16422600000000001</v>
       </c>
       <c r="Z73">
-        <v>9.3521000000000007E-2</v>
+        <v>0.14963399999999999</v>
       </c>
       <c r="AA73">
-        <v>9.8237000000000005E-2</v>
+        <v>0.15717900000000001</v>
       </c>
       <c r="AB73">
-        <v>0.101813</v>
+        <v>0.16290099999999999</v>
       </c>
       <c r="AC73">
-        <v>9.8144999999999996E-2</v>
+        <v>0.15703500000000001</v>
       </c>
       <c r="AD73">
-        <v>0.11233799999999999</v>
+        <v>0.17974100000000001</v>
       </c>
       <c r="AE73">
-        <v>0.11372</v>
+        <v>0.181952</v>
       </c>
       <c r="AF73">
-        <v>0.10628899999999999</v>
+        <v>0.17006199999999999</v>
       </c>
       <c r="AG73">
-        <v>0.11262</v>
+        <v>0.18019299999999999</v>
       </c>
       <c r="AH73">
-        <v>0.11916400000000001</v>
+        <v>0.18868199999999999</v>
       </c>
       <c r="AI73">
-        <v>0.112996</v>
+        <v>0.18018500000000001</v>
       </c>
       <c r="AJ73">
-        <v>0.182947</v>
+        <v>0.292715</v>
       </c>
       <c r="AK73">
-        <v>0.17524100000000001</v>
+        <v>0.28038600000000002</v>
       </c>
       <c r="AL73">
-        <v>0.17830499999999999</v>
+        <v>0.28736099999999998</v>
       </c>
       <c r="AM73">
-        <v>0.17955299999999999</v>
+        <v>0.28787699999999999</v>
       </c>
       <c r="AN73">
-        <v>0.19293299999999999</v>
+        <v>0.306813</v>
       </c>
       <c r="AO73">
-        <v>0.19430900000000001</v>
+        <v>0.30703599999999998</v>
       </c>
       <c r="AP73">
         <v>51.908248999999998</v>
@@ -20379,58 +20379,58 @@
         <v>29.343057999999999</v>
       </c>
       <c r="X74">
-        <v>9.4997999999999999E-2</v>
+        <v>0.15199599999999999</v>
       </c>
       <c r="Y74">
-        <v>9.9617999999999998E-2</v>
+        <v>0.15834000000000001</v>
       </c>
       <c r="Z74">
-        <v>9.2769000000000004E-2</v>
+        <v>0.14843100000000001</v>
       </c>
       <c r="AA74">
-        <v>9.8206000000000002E-2</v>
+        <v>0.15712999999999999</v>
       </c>
       <c r="AB74">
-        <v>9.7864999999999994E-2</v>
+        <v>0.156585</v>
       </c>
       <c r="AC74">
-        <v>9.2033000000000004E-2</v>
+        <v>0.14725099999999999</v>
       </c>
       <c r="AD74">
-        <v>0.109275</v>
+        <v>0.17484</v>
       </c>
       <c r="AE74">
-        <v>0.11025799999999999</v>
+        <v>0.17641299999999999</v>
       </c>
       <c r="AF74">
-        <v>0.108406</v>
+        <v>0.17344899999999999</v>
       </c>
       <c r="AG74">
-        <v>0.110097</v>
+        <v>0.17615500000000001</v>
       </c>
       <c r="AH74">
-        <v>0.116677</v>
+        <v>0.18538499999999999</v>
       </c>
       <c r="AI74">
-        <v>0.10764700000000001</v>
+        <v>0.172539</v>
       </c>
       <c r="AJ74">
-        <v>0.184749</v>
+        <v>0.29559800000000003</v>
       </c>
       <c r="AK74">
-        <v>0.17193700000000001</v>
+        <v>0.27510000000000001</v>
       </c>
       <c r="AL74">
-        <v>0.17779600000000001</v>
+        <v>0.28747400000000001</v>
       </c>
       <c r="AM74">
-        <v>0.18392900000000001</v>
+        <v>0.29386400000000001</v>
       </c>
       <c r="AN74">
-        <v>0.19334899999999999</v>
+        <v>0.30837399999999998</v>
       </c>
       <c r="AO74">
-        <v>0.188252</v>
+        <v>0.301618</v>
       </c>
       <c r="AP74">
         <v>51.891111000000002</v>
@@ -20588,58 +20588,58 @@
         <v>29.315944999999999</v>
       </c>
       <c r="X75">
-        <v>9.3182000000000001E-2</v>
+        <v>0.149091</v>
       </c>
       <c r="Y75">
-        <v>9.5120999999999997E-2</v>
+        <v>0.15182499999999999</v>
       </c>
       <c r="Z75">
-        <v>9.4198000000000004E-2</v>
+        <v>0.15071699999999999</v>
       </c>
       <c r="AA75">
-        <v>9.8656999999999995E-2</v>
+        <v>0.15785099999999999</v>
       </c>
       <c r="AB75">
-        <v>9.7736000000000003E-2</v>
+        <v>0.15637699999999999</v>
       </c>
       <c r="AC75">
-        <v>9.2521000000000006E-2</v>
+        <v>0.148034</v>
       </c>
       <c r="AD75">
-        <v>0.106712</v>
+        <v>0.170739</v>
       </c>
       <c r="AE75">
-        <v>0.105794</v>
+        <v>0.169271</v>
       </c>
       <c r="AF75">
-        <v>0.108991</v>
+        <v>0.17438500000000001</v>
       </c>
       <c r="AG75">
-        <v>0.110212</v>
+        <v>0.176339</v>
       </c>
       <c r="AH75">
-        <v>0.11548600000000001</v>
+        <v>0.18370400000000001</v>
       </c>
       <c r="AI75">
-        <v>0.106429</v>
+        <v>0.170491</v>
       </c>
       <c r="AJ75">
-        <v>0.185417</v>
+        <v>0.29666700000000001</v>
       </c>
       <c r="AK75">
-        <v>0.16949400000000001</v>
+        <v>0.27118999999999999</v>
       </c>
       <c r="AL75">
-        <v>0.179983</v>
+        <v>0.29069899999999999</v>
       </c>
       <c r="AM75">
-        <v>0.18799399999999999</v>
+        <v>0.29927399999999998</v>
       </c>
       <c r="AN75">
-        <v>0.19791900000000001</v>
+        <v>0.31306600000000001</v>
       </c>
       <c r="AO75">
-        <v>0.18743499999999999</v>
+        <v>0.30027100000000001</v>
       </c>
       <c r="AP75">
         <v>51.940389000000003</v>
@@ -20797,58 +20797,58 @@
         <v>29.618003999999999</v>
       </c>
       <c r="X76">
-        <v>9.1812000000000005E-2</v>
+        <v>0.1469</v>
       </c>
       <c r="Y76">
-        <v>9.1023000000000007E-2</v>
+        <v>0.14519899999999999</v>
       </c>
       <c r="Z76">
-        <v>9.8639000000000004E-2</v>
+        <v>0.15782199999999999</v>
       </c>
       <c r="AA76">
-        <v>0.100499</v>
+        <v>0.160799</v>
       </c>
       <c r="AB76">
-        <v>9.9484000000000003E-2</v>
+        <v>0.15917500000000001</v>
       </c>
       <c r="AC76">
-        <v>9.7911999999999999E-2</v>
+        <v>0.156664</v>
       </c>
       <c r="AD76">
-        <v>0.103925</v>
+        <v>0.16627900000000001</v>
       </c>
       <c r="AE76">
-        <v>0.10125199999999999</v>
+        <v>0.16200300000000001</v>
       </c>
       <c r="AF76">
-        <v>0.1116</v>
+        <v>0.17856</v>
       </c>
       <c r="AG76">
-        <v>0.11351799999999999</v>
+        <v>0.18163000000000001</v>
       </c>
       <c r="AH76">
-        <v>0.115115</v>
+        <v>0.18302599999999999</v>
       </c>
       <c r="AI76">
-        <v>0.107587</v>
+        <v>0.17170099999999999</v>
       </c>
       <c r="AJ76">
-        <v>0.18232400000000001</v>
+        <v>0.29171900000000001</v>
       </c>
       <c r="AK76">
-        <v>0.16581399999999999</v>
+        <v>0.26530199999999998</v>
       </c>
       <c r="AL76">
-        <v>0.18815899999999999</v>
+        <v>0.29994300000000002</v>
       </c>
       <c r="AM76">
-        <v>0.19189700000000001</v>
+        <v>0.30407600000000001</v>
       </c>
       <c r="AN76">
-        <v>0.20150899999999999</v>
+        <v>0.31623899999999999</v>
       </c>
       <c r="AO76">
-        <v>0.18984799999999999</v>
+        <v>0.30141699999999999</v>
       </c>
       <c r="AP76">
         <v>52.313025000000003</v>
@@ -21009,58 +21009,58 @@
         <v>29.526441999999999</v>
       </c>
       <c r="X77">
-        <v>8.8622999999999993E-2</v>
+        <v>0.14179700000000001</v>
       </c>
       <c r="Y77">
-        <v>8.7131E-2</v>
+        <v>0.138261</v>
       </c>
       <c r="Z77">
-        <v>9.4785999999999995E-2</v>
+        <v>0.15165699999999999</v>
       </c>
       <c r="AA77">
-        <v>9.7101000000000007E-2</v>
+        <v>0.155361</v>
       </c>
       <c r="AB77">
-        <v>9.6203999999999998E-2</v>
+        <v>0.15392700000000001</v>
       </c>
       <c r="AC77">
-        <v>9.8995E-2</v>
+        <v>0.15839600000000001</v>
       </c>
       <c r="AD77">
-        <v>0.101313</v>
+        <v>0.16209999999999999</v>
       </c>
       <c r="AE77">
-        <v>9.7785999999999998E-2</v>
+        <v>0.15645800000000001</v>
       </c>
       <c r="AF77">
-        <v>0.106334</v>
+        <v>0.17013400000000001</v>
       </c>
       <c r="AG77">
-        <v>0.11051800000000001</v>
+        <v>0.17682800000000001</v>
       </c>
       <c r="AH77">
-        <v>0.113256</v>
+        <v>0.18023400000000001</v>
       </c>
       <c r="AI77">
-        <v>0.10692</v>
+        <v>0.17043700000000001</v>
       </c>
       <c r="AJ77">
-        <v>0.17890600000000001</v>
+        <v>0.28624899999999998</v>
       </c>
       <c r="AK77">
-        <v>0.16420799999999999</v>
+        <v>0.26273299999999999</v>
       </c>
       <c r="AL77">
-        <v>0.18648500000000001</v>
+        <v>0.298317</v>
       </c>
       <c r="AM77">
-        <v>0.190723</v>
+        <v>0.303118</v>
       </c>
       <c r="AN77">
-        <v>0.198992</v>
+        <v>0.31323800000000002</v>
       </c>
       <c r="AO77">
-        <v>0.18984300000000001</v>
+        <v>0.30044999999999999</v>
       </c>
       <c r="AP77">
         <v>52.899866000000003</v>
@@ -21221,58 +21221,58 @@
         <v>28.993742000000001</v>
       </c>
       <c r="X78">
-        <v>8.3066000000000001E-2</v>
+        <v>0.132905</v>
       </c>
       <c r="Y78">
-        <v>8.0397999999999997E-2</v>
+        <v>0.128936</v>
       </c>
       <c r="Z78">
-        <v>9.0497999999999995E-2</v>
+        <v>0.14479600000000001</v>
       </c>
       <c r="AA78">
-        <v>9.8262000000000002E-2</v>
+        <v>0.15722</v>
       </c>
       <c r="AB78">
-        <v>9.2873999999999998E-2</v>
+        <v>0.14859900000000001</v>
       </c>
       <c r="AC78">
-        <v>9.3925999999999996E-2</v>
+        <v>0.150284</v>
       </c>
       <c r="AD78">
-        <v>9.7849000000000005E-2</v>
+        <v>0.156558</v>
       </c>
       <c r="AE78">
-        <v>9.4940999999999998E-2</v>
+        <v>0.15190600000000001</v>
       </c>
       <c r="AF78">
-        <v>0.103739</v>
+        <v>0.16598199999999999</v>
       </c>
       <c r="AG78">
-        <v>0.11473800000000001</v>
+        <v>0.18357999999999999</v>
       </c>
       <c r="AH78">
-        <v>0.110474</v>
+        <v>0.17611499999999999</v>
       </c>
       <c r="AI78">
-        <v>0.104268</v>
+        <v>0.166378</v>
       </c>
       <c r="AJ78">
-        <v>0.17602000000000001</v>
+        <v>0.28163300000000002</v>
       </c>
       <c r="AK78">
-        <v>0.16270699999999999</v>
+        <v>0.26033200000000001</v>
       </c>
       <c r="AL78">
-        <v>0.185386</v>
+        <v>0.29659200000000002</v>
       </c>
       <c r="AM78">
-        <v>0.194023</v>
+        <v>0.30589499999999997</v>
       </c>
       <c r="AN78">
-        <v>0.193493</v>
+        <v>0.30655900000000003</v>
       </c>
       <c r="AO78">
-        <v>0.18642500000000001</v>
+        <v>0.29639500000000002</v>
       </c>
       <c r="AP78">
         <v>53.519176999999999</v>
@@ -21433,58 +21433,58 @@
         <v>28.228515999999999</v>
       </c>
       <c r="X79">
-        <v>7.8118999999999994E-2</v>
+        <v>0.124989</v>
       </c>
       <c r="Y79">
-        <v>7.4993000000000004E-2</v>
+        <v>0.12154</v>
       </c>
       <c r="Z79">
-        <v>8.5367999999999999E-2</v>
+        <v>0.13658899999999999</v>
       </c>
       <c r="AA79">
-        <v>9.4084000000000001E-2</v>
+        <v>0.150534</v>
       </c>
       <c r="AB79">
-        <v>8.8636999999999994E-2</v>
+        <v>0.14182</v>
       </c>
       <c r="AC79">
-        <v>8.5053000000000004E-2</v>
+        <v>0.13608100000000001</v>
       </c>
       <c r="AD79">
-        <v>9.4004000000000004E-2</v>
+        <v>0.15040600000000001</v>
       </c>
       <c r="AE79">
-        <v>9.3146000000000007E-2</v>
+        <v>0.149034</v>
       </c>
       <c r="AF79">
-        <v>0.10154199999999999</v>
+        <v>0.162467</v>
       </c>
       <c r="AG79">
-        <v>0.112688</v>
+        <v>0.18030099999999999</v>
       </c>
       <c r="AH79">
-        <v>0.106686</v>
+        <v>0.17065</v>
       </c>
       <c r="AI79">
-        <v>9.9364999999999995E-2</v>
+        <v>0.15928200000000001</v>
       </c>
       <c r="AJ79">
-        <v>0.17258899999999999</v>
+        <v>0.27614300000000003</v>
       </c>
       <c r="AK79">
-        <v>0.16048399999999999</v>
+        <v>0.256774</v>
       </c>
       <c r="AL79">
-        <v>0.18107999999999999</v>
+        <v>0.29150999999999999</v>
       </c>
       <c r="AM79">
-        <v>0.18990699999999999</v>
+        <v>0.30097600000000002</v>
       </c>
       <c r="AN79">
-        <v>0.18678600000000001</v>
+        <v>0.29844500000000002</v>
       </c>
       <c r="AO79">
-        <v>0.179837</v>
+        <v>0.28976400000000002</v>
       </c>
       <c r="AP79">
         <v>53.856684999999999</v>
@@ -21645,58 +21645,58 @@
         <v>27.806160999999999</v>
       </c>
       <c r="X80">
-        <v>7.6873999999999998E-2</v>
+        <v>0.122997</v>
       </c>
       <c r="Y80">
-        <v>7.7715000000000006E-2</v>
+        <v>0.122072</v>
       </c>
       <c r="Z80">
-        <v>8.2915000000000003E-2</v>
+        <v>0.132663</v>
       </c>
       <c r="AA80">
-        <v>8.7803999999999993E-2</v>
+        <v>0.140487</v>
       </c>
       <c r="AB80">
-        <v>8.6860999999999994E-2</v>
+        <v>0.13897799999999999</v>
       </c>
       <c r="AC80">
-        <v>8.0012E-2</v>
+        <v>0.12801199999999999</v>
       </c>
       <c r="AD80">
-        <v>9.3662999999999996E-2</v>
+        <v>0.14985999999999999</v>
       </c>
       <c r="AE80">
-        <v>9.4852000000000006E-2</v>
+        <v>0.15176300000000001</v>
       </c>
       <c r="AF80">
-        <v>0.10155</v>
+        <v>0.16248000000000001</v>
       </c>
       <c r="AG80">
-        <v>0.104931</v>
+        <v>0.16788900000000001</v>
       </c>
       <c r="AH80">
-        <v>0.103934</v>
+        <v>0.16667000000000001</v>
       </c>
       <c r="AI80">
-        <v>9.5487000000000002E-2</v>
+        <v>0.15367800000000001</v>
       </c>
       <c r="AJ80">
-        <v>0.16963900000000001</v>
+        <v>0.271422</v>
       </c>
       <c r="AK80">
-        <v>0.162328</v>
+        <v>0.25972499999999998</v>
       </c>
       <c r="AL80">
-        <v>0.182836</v>
+        <v>0.29319400000000001</v>
       </c>
       <c r="AM80">
-        <v>0.18126200000000001</v>
+        <v>0.29132799999999998</v>
       </c>
       <c r="AN80">
-        <v>0.18126300000000001</v>
+        <v>0.29145399999999999</v>
       </c>
       <c r="AO80">
-        <v>0.17416000000000001</v>
+        <v>0.28412199999999999</v>
       </c>
       <c r="AP80">
         <v>53.930546</v>
@@ -21857,58 +21857,58 @@
         <v>27.735119000000001</v>
       </c>
       <c r="X81">
-        <v>7.7758999999999995E-2</v>
+        <v>0.124413</v>
       </c>
       <c r="Y81">
-        <v>8.0906000000000006E-2</v>
+        <v>0.12488100000000001</v>
       </c>
       <c r="Z81">
-        <v>8.3757999999999999E-2</v>
+        <v>0.13401199999999999</v>
       </c>
       <c r="AA81">
-        <v>8.5986999999999994E-2</v>
+        <v>0.13757900000000001</v>
       </c>
       <c r="AB81">
-        <v>8.6471000000000006E-2</v>
+        <v>0.138354</v>
       </c>
       <c r="AC81">
-        <v>7.8466999999999995E-2</v>
+        <v>0.12553900000000001</v>
       </c>
       <c r="AD81">
-        <v>9.4188999999999995E-2</v>
+        <v>0.150702</v>
       </c>
       <c r="AE81">
-        <v>9.6237000000000003E-2</v>
+        <v>0.153979</v>
       </c>
       <c r="AF81">
-        <v>0.10373599999999999</v>
+        <v>0.16597700000000001</v>
       </c>
       <c r="AG81">
-        <v>0.10255300000000001</v>
+        <v>0.16408500000000001</v>
       </c>
       <c r="AH81">
-        <v>0.10312499999999999</v>
+        <v>0.165462</v>
       </c>
       <c r="AI81">
-        <v>9.4550999999999996E-2</v>
+        <v>0.152258</v>
       </c>
       <c r="AJ81">
-        <v>0.16817099999999999</v>
+        <v>0.26907300000000001</v>
       </c>
       <c r="AK81">
-        <v>0.164273</v>
+        <v>0.26283600000000001</v>
       </c>
       <c r="AL81">
-        <v>0.18600800000000001</v>
+        <v>0.29658299999999999</v>
       </c>
       <c r="AM81">
-        <v>0.17940400000000001</v>
+        <v>0.28883199999999998</v>
       </c>
       <c r="AN81">
-        <v>0.17952199999999999</v>
+        <v>0.28837400000000002</v>
       </c>
       <c r="AO81">
-        <v>0.17249200000000001</v>
+        <v>0.28225899999999998</v>
       </c>
       <c r="AP81">
         <v>54.408943999999998</v>
@@ -22066,58 +22066,58 @@
         <v>30.175718</v>
       </c>
       <c r="X82">
-        <v>9.7638000000000003E-2</v>
+        <v>0.156222</v>
       </c>
       <c r="Y82">
-        <v>9.6430000000000002E-2</v>
+        <v>0.15576300000000001</v>
       </c>
       <c r="Z82">
-        <v>8.5314000000000001E-2</v>
+        <v>0.13650200000000001</v>
       </c>
       <c r="AA82">
-        <v>8.5817000000000004E-2</v>
+        <v>0.13730600000000001</v>
       </c>
       <c r="AB82">
-        <v>9.7739000000000006E-2</v>
+        <v>0.15638199999999999</v>
       </c>
       <c r="AC82">
-        <v>0.11047800000000001</v>
+        <v>0.17678099999999999</v>
       </c>
       <c r="AD82">
-        <v>0.109107</v>
+        <v>0.174571</v>
       </c>
       <c r="AE82">
-        <v>0.10584499999999999</v>
+        <v>0.169353</v>
       </c>
       <c r="AF82">
-        <v>9.4263E-2</v>
+        <v>0.15082100000000001</v>
       </c>
       <c r="AG82">
-        <v>9.6074000000000007E-2</v>
+        <v>0.15371799999999999</v>
       </c>
       <c r="AH82">
-        <v>0.113637</v>
+        <v>0.180534</v>
       </c>
       <c r="AI82">
-        <v>0.116007</v>
+        <v>0.184309</v>
       </c>
       <c r="AJ82">
-        <v>0.183944</v>
+        <v>0.29431000000000002</v>
       </c>
       <c r="AK82">
-        <v>0.16766500000000001</v>
+        <v>0.268264</v>
       </c>
       <c r="AL82">
-        <v>0.16950000000000001</v>
+        <v>0.277951</v>
       </c>
       <c r="AM82">
-        <v>0.16614499999999999</v>
+        <v>0.27306799999999998</v>
       </c>
       <c r="AN82">
-        <v>0.18767300000000001</v>
+        <v>0.29979699999999998</v>
       </c>
       <c r="AO82">
-        <v>0.19755800000000001</v>
+        <v>0.30973000000000001</v>
       </c>
       <c r="AP82">
         <v>51.540419</v>
@@ -22275,58 +22275,58 @@
         <v>30.132712999999999</v>
       </c>
       <c r="X83">
-        <v>9.5586000000000004E-2</v>
+        <v>0.15293799999999999</v>
       </c>
       <c r="Y83">
-        <v>9.5211000000000004E-2</v>
+        <v>0.15379399999999999</v>
       </c>
       <c r="Z83">
-        <v>8.5657999999999998E-2</v>
+        <v>0.13705300000000001</v>
       </c>
       <c r="AA83">
-        <v>8.7271000000000001E-2</v>
+        <v>0.13963400000000001</v>
       </c>
       <c r="AB83">
-        <v>9.6091999999999997E-2</v>
+        <v>0.15374699999999999</v>
       </c>
       <c r="AC83">
-        <v>0.10551099999999999</v>
+        <v>0.16883000000000001</v>
       </c>
       <c r="AD83">
-        <v>0.108422</v>
+        <v>0.17347499999999999</v>
       </c>
       <c r="AE83">
-        <v>0.10513500000000001</v>
+        <v>0.168216</v>
       </c>
       <c r="AF83">
-        <v>9.6546000000000007E-2</v>
+        <v>0.154473</v>
       </c>
       <c r="AG83">
-        <v>9.8284999999999997E-2</v>
+        <v>0.15725600000000001</v>
       </c>
       <c r="AH83">
-        <v>0.11139300000000001</v>
+        <v>0.17763799999999999</v>
       </c>
       <c r="AI83">
-        <v>0.112162</v>
+        <v>0.17890800000000001</v>
       </c>
       <c r="AJ83">
-        <v>0.18210399999999999</v>
+        <v>0.29136699999999999</v>
       </c>
       <c r="AK83">
-        <v>0.166573</v>
+        <v>0.26651599999999998</v>
       </c>
       <c r="AL83">
-        <v>0.17135</v>
+        <v>0.27977099999999999</v>
       </c>
       <c r="AM83">
-        <v>0.16797300000000001</v>
+        <v>0.27494400000000002</v>
       </c>
       <c r="AN83">
-        <v>0.18795600000000001</v>
+        <v>0.30063699999999999</v>
       </c>
       <c r="AO83">
-        <v>0.19504199999999999</v>
+        <v>0.30765300000000001</v>
       </c>
       <c r="AP83">
         <v>51.683840000000004</v>
@@ -22484,58 +22484,58 @@
         <v>29.618729999999999</v>
       </c>
       <c r="X84">
-        <v>9.3451000000000006E-2</v>
+        <v>0.14952199999999999</v>
       </c>
       <c r="Y84">
-        <v>9.5517000000000005E-2</v>
+        <v>0.15212300000000001</v>
       </c>
       <c r="Z84">
-        <v>8.4478999999999999E-2</v>
+        <v>0.13516700000000001</v>
       </c>
       <c r="AA84">
-        <v>8.0550999999999998E-2</v>
+        <v>0.128882</v>
       </c>
       <c r="AB84">
-        <v>8.8394E-2</v>
+        <v>0.14143</v>
       </c>
       <c r="AC84">
-        <v>8.8660000000000003E-2</v>
+        <v>0.14185300000000001</v>
       </c>
       <c r="AD84">
-        <v>0.107631</v>
+        <v>0.17221</v>
       </c>
       <c r="AE84">
-        <v>0.104752</v>
+        <v>0.167603</v>
       </c>
       <c r="AF84">
-        <v>9.7437999999999997E-2</v>
+        <v>0.15590100000000001</v>
       </c>
       <c r="AG84">
-        <v>9.0953999999999993E-2</v>
+        <v>0.14552699999999999</v>
       </c>
       <c r="AH84">
-        <v>0.107267</v>
+        <v>0.17205899999999999</v>
       </c>
       <c r="AI84">
-        <v>0.10599699999999999</v>
+        <v>0.170184</v>
       </c>
       <c r="AJ84">
-        <v>0.18132300000000001</v>
+        <v>0.29011700000000001</v>
       </c>
       <c r="AK84">
-        <v>0.16770199999999999</v>
+        <v>0.26832299999999998</v>
       </c>
       <c r="AL84">
-        <v>0.17069699999999999</v>
+        <v>0.279117</v>
       </c>
       <c r="AM84">
-        <v>0.16528300000000001</v>
+        <v>0.27303699999999997</v>
       </c>
       <c r="AN84">
-        <v>0.18549199999999999</v>
+        <v>0.29960799999999999</v>
       </c>
       <c r="AO84">
-        <v>0.19029199999999999</v>
+        <v>0.30342999999999998</v>
       </c>
       <c r="AP84">
         <v>51.825915999999999</v>
@@ -22693,58 +22693,58 @@
         <v>29.599433999999999</v>
       </c>
       <c r="X85">
-        <v>9.1381000000000004E-2</v>
+        <v>0.14620900000000001</v>
       </c>
       <c r="Y85">
-        <v>9.2868000000000006E-2</v>
+        <v>0.14788100000000001</v>
       </c>
       <c r="Z85">
-        <v>8.4363999999999995E-2</v>
+        <v>0.13498099999999999</v>
       </c>
       <c r="AA85">
-        <v>8.1739999999999993E-2</v>
+        <v>0.13078500000000001</v>
       </c>
       <c r="AB85">
-        <v>8.7430999999999995E-2</v>
+        <v>0.13988900000000001</v>
       </c>
       <c r="AC85">
-        <v>8.8068999999999995E-2</v>
+        <v>0.140907</v>
       </c>
       <c r="AD85">
-        <v>0.105989</v>
+        <v>0.16958200000000001</v>
       </c>
       <c r="AE85">
-        <v>0.10395</v>
+        <v>0.16632</v>
       </c>
       <c r="AF85">
-        <v>9.8077999999999999E-2</v>
+        <v>0.15692500000000001</v>
       </c>
       <c r="AG85">
-        <v>9.2855999999999994E-2</v>
+        <v>0.14857000000000001</v>
       </c>
       <c r="AH85">
-        <v>0.10661900000000001</v>
+        <v>0.1711</v>
       </c>
       <c r="AI85">
-        <v>0.10493</v>
+        <v>0.16838900000000001</v>
       </c>
       <c r="AJ85">
-        <v>0.18327499999999999</v>
+        <v>0.29324</v>
       </c>
       <c r="AK85">
-        <v>0.17104900000000001</v>
+        <v>0.27367900000000001</v>
       </c>
       <c r="AL85">
-        <v>0.171929</v>
+        <v>0.28116000000000002</v>
       </c>
       <c r="AM85">
-        <v>0.17357900000000001</v>
+        <v>0.28282499999999999</v>
       </c>
       <c r="AN85">
-        <v>0.189252</v>
+        <v>0.303456</v>
       </c>
       <c r="AO85">
-        <v>0.19017100000000001</v>
+        <v>0.30276399999999998</v>
       </c>
       <c r="AP85">
         <v>51.857469000000002</v>
@@ -22902,58 +22902,58 @@
         <v>30.249908000000001</v>
       </c>
       <c r="X86">
-        <v>8.9712E-2</v>
+        <v>0.143539</v>
       </c>
       <c r="Y86">
-        <v>8.9400999999999994E-2</v>
+        <v>0.14260300000000001</v>
       </c>
       <c r="Z86">
-        <v>9.1925000000000007E-2</v>
+        <v>0.14707999999999999</v>
       </c>
       <c r="AA86">
-        <v>9.6723000000000003E-2</v>
+        <v>0.15475700000000001</v>
       </c>
       <c r="AB86">
-        <v>9.4505000000000006E-2</v>
+        <v>0.15120700000000001</v>
       </c>
       <c r="AC86">
-        <v>0.104602</v>
+        <v>0.167375</v>
       </c>
       <c r="AD86">
-        <v>0.10348300000000001</v>
+        <v>0.165573</v>
       </c>
       <c r="AE86">
-        <v>0.10267999999999999</v>
+        <v>0.16428899999999999</v>
       </c>
       <c r="AF86">
-        <v>0.105903</v>
+        <v>0.16944500000000001</v>
       </c>
       <c r="AG86">
-        <v>0.110457</v>
+        <v>0.176731</v>
       </c>
       <c r="AH86">
-        <v>0.109697</v>
+        <v>0.175145</v>
       </c>
       <c r="AI86">
-        <v>0.107775</v>
+        <v>0.171929</v>
       </c>
       <c r="AJ86">
-        <v>0.185087</v>
+        <v>0.29614000000000001</v>
       </c>
       <c r="AK86">
-        <v>0.17308499999999999</v>
+        <v>0.27693600000000002</v>
       </c>
       <c r="AL86">
-        <v>0.18790399999999999</v>
+        <v>0.29895500000000003</v>
       </c>
       <c r="AM86">
-        <v>0.192384</v>
+        <v>0.303421</v>
       </c>
       <c r="AN86">
-        <v>0.19825699999999999</v>
+        <v>0.31102299999999999</v>
       </c>
       <c r="AO86">
-        <v>0.19336300000000001</v>
+        <v>0.30458600000000002</v>
       </c>
       <c r="AP86">
         <v>51.967883999999998</v>
@@ -23111,58 +23111,58 @@
         <v>30.327418999999999</v>
       </c>
       <c r="X87">
-        <v>8.7265999999999996E-2</v>
+        <v>0.139627</v>
       </c>
       <c r="Y87">
-        <v>8.6150000000000004E-2</v>
+        <v>0.13725699999999999</v>
       </c>
       <c r="Z87">
-        <v>9.4120999999999996E-2</v>
+        <v>0.15059400000000001</v>
       </c>
       <c r="AA87">
-        <v>9.9498000000000003E-2</v>
+        <v>0.15919700000000001</v>
       </c>
       <c r="AB87">
-        <v>9.5367999999999994E-2</v>
+        <v>0.152589</v>
       </c>
       <c r="AC87">
-        <v>0.10553899999999999</v>
+        <v>0.168876</v>
       </c>
       <c r="AD87">
-        <v>0.101745</v>
+        <v>0.16279199999999999</v>
       </c>
       <c r="AE87">
-        <v>0.10031</v>
+        <v>0.160496</v>
       </c>
       <c r="AF87">
-        <v>0.109219</v>
+        <v>0.17475099999999999</v>
       </c>
       <c r="AG87">
-        <v>0.11382299999999999</v>
+        <v>0.182116</v>
       </c>
       <c r="AH87">
-        <v>0.10964500000000001</v>
+        <v>0.174869</v>
       </c>
       <c r="AI87">
-        <v>0.10792300000000001</v>
+        <v>0.17177100000000001</v>
       </c>
       <c r="AJ87">
-        <v>0.183395</v>
+        <v>0.29343200000000003</v>
       </c>
       <c r="AK87">
-        <v>0.16950899999999999</v>
+        <v>0.27121400000000001</v>
       </c>
       <c r="AL87">
-        <v>0.192631</v>
+        <v>0.30453200000000002</v>
       </c>
       <c r="AM87">
-        <v>0.19418299999999999</v>
+        <v>0.30605700000000002</v>
       </c>
       <c r="AN87">
-        <v>0.197605</v>
+        <v>0.30966900000000003</v>
       </c>
       <c r="AO87">
-        <v>0.192939</v>
+        <v>0.30318299999999998</v>
       </c>
       <c r="AP87">
         <v>52.203873000000002</v>
@@ -23320,58 +23320,58 @@
         <v>29.806083999999998</v>
       </c>
       <c r="X88">
-        <v>8.3298999999999998E-2</v>
+        <v>0.13327800000000001</v>
       </c>
       <c r="Y88">
-        <v>8.1162999999999999E-2</v>
+        <v>0.13092000000000001</v>
       </c>
       <c r="Z88">
-        <v>9.0981000000000006E-2</v>
+        <v>0.145569</v>
       </c>
       <c r="AA88">
-        <v>9.5327999999999996E-2</v>
+        <v>0.15252399999999999</v>
       </c>
       <c r="AB88">
-        <v>9.1391E-2</v>
+        <v>0.14622499999999999</v>
       </c>
       <c r="AC88">
-        <v>9.3181E-2</v>
+        <v>0.149092</v>
       </c>
       <c r="AD88">
-        <v>0.101981</v>
+        <v>0.16316900000000001</v>
       </c>
       <c r="AE88">
-        <v>9.8375000000000004E-2</v>
+        <v>0.15739900000000001</v>
       </c>
       <c r="AF88">
-        <v>0.10879999999999999</v>
+        <v>0.17408000000000001</v>
       </c>
       <c r="AG88">
-        <v>0.113547</v>
+        <v>0.181676</v>
       </c>
       <c r="AH88">
-        <v>0.106102</v>
+        <v>0.169798</v>
       </c>
       <c r="AI88">
-        <v>0.105125</v>
+        <v>0.16750799999999999</v>
       </c>
       <c r="AJ88">
-        <v>0.18016399999999999</v>
+        <v>0.28826299999999999</v>
       </c>
       <c r="AK88">
-        <v>0.16377900000000001</v>
+        <v>0.262046</v>
       </c>
       <c r="AL88">
-        <v>0.18765799999999999</v>
+        <v>0.29943700000000001</v>
       </c>
       <c r="AM88">
-        <v>0.19350899999999999</v>
+        <v>0.30507800000000002</v>
       </c>
       <c r="AN88">
-        <v>0.18934599999999999</v>
+        <v>0.30093199999999998</v>
       </c>
       <c r="AO88">
-        <v>0.188831</v>
+        <v>0.29845300000000002</v>
       </c>
       <c r="AP88">
         <v>52.617677999999998</v>
@@ -23529,58 +23529,58 @@
         <v>28.969802000000001</v>
       </c>
       <c r="X89">
-        <v>7.9798999999999995E-2</v>
+        <v>0.12767700000000001</v>
       </c>
       <c r="Y89">
-        <v>7.8875000000000001E-2</v>
+        <v>0.12738099999999999</v>
       </c>
       <c r="Z89">
-        <v>9.0221999999999997E-2</v>
+        <v>0.14435500000000001</v>
       </c>
       <c r="AA89">
-        <v>8.9971999999999996E-2</v>
+        <v>0.143955</v>
       </c>
       <c r="AB89">
-        <v>8.6748000000000006E-2</v>
+        <v>0.138796</v>
       </c>
       <c r="AC89">
-        <v>8.5004999999999997E-2</v>
+        <v>0.13600499999999999</v>
       </c>
       <c r="AD89">
-        <v>0.10123600000000001</v>
+        <v>0.16197700000000001</v>
       </c>
       <c r="AE89">
-        <v>9.7603999999999996E-2</v>
+        <v>0.156167</v>
       </c>
       <c r="AF89">
-        <v>0.10852000000000001</v>
+        <v>0.17363300000000001</v>
       </c>
       <c r="AG89">
-        <v>0.109155</v>
+        <v>0.174647</v>
       </c>
       <c r="AH89">
-        <v>0.101628</v>
+        <v>0.16348299999999999</v>
       </c>
       <c r="AI89">
-        <v>0.100033</v>
+        <v>0.160103</v>
       </c>
       <c r="AJ89">
-        <v>0.176872</v>
+        <v>0.28299600000000003</v>
       </c>
       <c r="AK89">
-        <v>0.16165099999999999</v>
+        <v>0.25864199999999998</v>
       </c>
       <c r="AL89">
-        <v>0.185028</v>
+        <v>0.29631800000000003</v>
       </c>
       <c r="AM89">
-        <v>0.18737699999999999</v>
+        <v>0.29800900000000002</v>
       </c>
       <c r="AN89">
-        <v>0.18026600000000001</v>
+        <v>0.29093599999999997</v>
       </c>
       <c r="AO89">
-        <v>0.18163499999999999</v>
+        <v>0.29113899999999998</v>
       </c>
       <c r="AP89">
         <v>53.167715999999999</v>
@@ -23738,58 +23738,58 @@
         <v>28.026261000000002</v>
       </c>
       <c r="X90">
-        <v>7.8879000000000005E-2</v>
+        <v>0.12620600000000001</v>
       </c>
       <c r="Y90">
-        <v>7.7562999999999993E-2</v>
+        <v>0.126056</v>
       </c>
       <c r="Z90">
-        <v>8.4599999999999995E-2</v>
+        <v>0.13536100000000001</v>
       </c>
       <c r="AA90">
-        <v>7.8143000000000004E-2</v>
+        <v>0.125029</v>
       </c>
       <c r="AB90">
-        <v>7.9941999999999999E-2</v>
+        <v>0.12790699999999999</v>
       </c>
       <c r="AC90">
-        <v>7.2732000000000005E-2</v>
+        <v>0.116356</v>
       </c>
       <c r="AD90">
-        <v>0.10291</v>
+        <v>0.164656</v>
       </c>
       <c r="AE90">
-        <v>9.8101999999999995E-2</v>
+        <v>0.15696299999999999</v>
       </c>
       <c r="AF90">
-        <v>0.101969</v>
+        <v>0.16315099999999999</v>
       </c>
       <c r="AG90">
-        <v>9.3408000000000005E-2</v>
+        <v>0.149453</v>
       </c>
       <c r="AH90">
-        <v>9.8016000000000006E-2</v>
+        <v>0.15842300000000001</v>
       </c>
       <c r="AI90">
-        <v>9.3813999999999995E-2</v>
+        <v>0.151257</v>
       </c>
       <c r="AJ90">
-        <v>0.174204</v>
+        <v>0.27872599999999997</v>
       </c>
       <c r="AK90">
-        <v>0.162132</v>
+        <v>0.259411</v>
       </c>
       <c r="AL90">
-        <v>0.17200499999999999</v>
+        <v>0.28221099999999999</v>
       </c>
       <c r="AM90">
-        <v>0.166439</v>
+        <v>0.27566200000000002</v>
       </c>
       <c r="AN90">
-        <v>0.17208499999999999</v>
+        <v>0.28191699999999997</v>
       </c>
       <c r="AO90">
-        <v>0.172622</v>
+        <v>0.282551</v>
       </c>
       <c r="AP90">
         <v>53.889536</v>
@@ -23947,58 +23947,58 @@
         <v>27.777025999999999</v>
       </c>
       <c r="X91">
-        <v>8.0046000000000006E-2</v>
+        <v>0.12807399999999999</v>
       </c>
       <c r="Y91">
-        <v>7.8436000000000006E-2</v>
+        <v>0.127083</v>
       </c>
       <c r="Z91">
-        <v>8.2678000000000001E-2</v>
+        <v>0.13228500000000001</v>
       </c>
       <c r="AA91">
-        <v>7.7929999999999999E-2</v>
+        <v>0.12468899999999999</v>
       </c>
       <c r="AB91">
-        <v>7.9255000000000006E-2</v>
+        <v>0.126807</v>
       </c>
       <c r="AC91">
-        <v>7.1819999999999995E-2</v>
+        <v>0.114897</v>
       </c>
       <c r="AD91">
-        <v>0.105111</v>
+        <v>0.16817799999999999</v>
       </c>
       <c r="AE91">
-        <v>9.8738999999999993E-2</v>
+        <v>0.15798300000000001</v>
       </c>
       <c r="AF91">
-        <v>9.9578E-2</v>
+        <v>0.15932499999999999</v>
       </c>
       <c r="AG91">
-        <v>9.1425000000000006E-2</v>
+        <v>0.14627999999999999</v>
       </c>
       <c r="AH91">
-        <v>9.7882999999999998E-2</v>
+        <v>0.15820999999999999</v>
       </c>
       <c r="AI91">
-        <v>9.2079999999999995E-2</v>
+        <v>0.14872199999999999</v>
       </c>
       <c r="AJ91">
-        <v>0.17346200000000001</v>
+        <v>0.27753899999999998</v>
       </c>
       <c r="AK91">
-        <v>0.16286400000000001</v>
+        <v>0.26058199999999998</v>
       </c>
       <c r="AL91">
-        <v>0.16830100000000001</v>
+        <v>0.27804200000000001</v>
       </c>
       <c r="AM91">
-        <v>0.161911</v>
+        <v>0.27022499999999999</v>
       </c>
       <c r="AN91">
-        <v>0.171539</v>
+        <v>0.27999499999999999</v>
       </c>
       <c r="AO91">
-        <v>0.169373</v>
+        <v>0.27929399999999999</v>
       </c>
       <c r="AP91">
         <v>54.446948999999996</v>
@@ -24159,58 +24159,58 @@
         <v>28.719570000000001</v>
       </c>
       <c r="X92">
-        <v>9.4200000000000006E-2</v>
+        <v>0.15071899999999999</v>
       </c>
       <c r="Y92">
-        <v>9.5568E-2</v>
+        <v>0.15535199999999999</v>
       </c>
       <c r="Z92">
-        <v>9.5988000000000004E-2</v>
+        <v>0.153581</v>
       </c>
       <c r="AA92">
-        <v>9.4856999999999997E-2</v>
+        <v>0.15177099999999999</v>
       </c>
       <c r="AB92">
-        <v>9.5685000000000006E-2</v>
+        <v>0.15309700000000001</v>
       </c>
       <c r="AC92">
-        <v>9.2310000000000003E-2</v>
+        <v>0.14769699999999999</v>
       </c>
       <c r="AD92">
-        <v>0.10784299999999999</v>
+        <v>0.17254900000000001</v>
       </c>
       <c r="AE92">
-        <v>0.112042</v>
+        <v>0.17926700000000001</v>
       </c>
       <c r="AF92">
-        <v>0.108666</v>
+        <v>0.17386499999999999</v>
       </c>
       <c r="AG92">
-        <v>0.10902100000000001</v>
+        <v>0.174433</v>
       </c>
       <c r="AH92">
-        <v>0.108491</v>
+        <v>0.172596</v>
       </c>
       <c r="AI92">
-        <v>0.109447</v>
+        <v>0.174456</v>
       </c>
       <c r="AJ92">
-        <v>0.17444399999999999</v>
+        <v>0.27911000000000002</v>
       </c>
       <c r="AK92">
-        <v>0.16666600000000001</v>
+        <v>0.26666600000000001</v>
       </c>
       <c r="AL92">
-        <v>0.17349700000000001</v>
+        <v>0.28320200000000001</v>
       </c>
       <c r="AM92">
-        <v>0.17712800000000001</v>
+        <v>0.28691899999999998</v>
       </c>
       <c r="AN92">
-        <v>0.18517700000000001</v>
+        <v>0.29400500000000002</v>
       </c>
       <c r="AO92">
-        <v>0.19004499999999999</v>
+        <v>0.30088500000000001</v>
       </c>
       <c r="AP92">
         <v>54.458486999999998</v>
@@ -24371,58 +24371,58 @@
         <v>28.864495000000002</v>
       </c>
       <c r="X93">
-        <v>9.4891000000000003E-2</v>
+        <v>0.15182599999999999</v>
       </c>
       <c r="Y93">
-        <v>9.6877000000000005E-2</v>
+        <v>0.156248</v>
       </c>
       <c r="Z93">
-        <v>9.5849000000000004E-2</v>
+        <v>0.153359</v>
       </c>
       <c r="AA93">
-        <v>9.4356999999999996E-2</v>
+        <v>0.15097099999999999</v>
       </c>
       <c r="AB93">
-        <v>9.5528000000000002E-2</v>
+        <v>0.15284500000000001</v>
       </c>
       <c r="AC93">
-        <v>9.4492000000000007E-2</v>
+        <v>0.15118899999999999</v>
       </c>
       <c r="AD93">
-        <v>0.10872999999999999</v>
+        <v>0.17396900000000001</v>
       </c>
       <c r="AE93">
-        <v>0.113428</v>
+        <v>0.18148500000000001</v>
       </c>
       <c r="AF93">
-        <v>0.10760699999999999</v>
+        <v>0.17216999999999999</v>
       </c>
       <c r="AG93">
-        <v>0.107627</v>
+        <v>0.17220299999999999</v>
       </c>
       <c r="AH93">
-        <v>0.106434</v>
+        <v>0.169852</v>
       </c>
       <c r="AI93">
-        <v>0.109294</v>
+        <v>0.17416300000000001</v>
       </c>
       <c r="AJ93">
-        <v>0.17527000000000001</v>
+        <v>0.28043099999999999</v>
       </c>
       <c r="AK93">
-        <v>0.16922100000000001</v>
+        <v>0.27075399999999999</v>
       </c>
       <c r="AL93">
-        <v>0.17710000000000001</v>
+        <v>0.28706599999999999</v>
       </c>
       <c r="AM93">
-        <v>0.178701</v>
+        <v>0.28843200000000002</v>
       </c>
       <c r="AN93">
-        <v>0.183116</v>
+        <v>0.29182999999999998</v>
       </c>
       <c r="AO93">
-        <v>0.18959200000000001</v>
+        <v>0.30049199999999998</v>
       </c>
       <c r="AP93">
         <v>54.502653000000002</v>
@@ -24583,58 +24583,58 @@
         <v>28.795411999999999</v>
       </c>
       <c r="X94">
-        <v>9.5465999999999995E-2</v>
+        <v>0.15274599999999999</v>
       </c>
       <c r="Y94">
-        <v>9.8974000000000006E-2</v>
+        <v>0.15756100000000001</v>
       </c>
       <c r="Z94">
-        <v>9.1946E-2</v>
+        <v>0.14711299999999999</v>
       </c>
       <c r="AA94">
-        <v>8.8739999999999999E-2</v>
+        <v>0.141984</v>
       </c>
       <c r="AB94">
-        <v>9.2701000000000006E-2</v>
+        <v>0.14832200000000001</v>
       </c>
       <c r="AC94">
-        <v>9.4379000000000005E-2</v>
+        <v>0.151007</v>
       </c>
       <c r="AD94">
-        <v>0.109412</v>
+        <v>0.17505899999999999</v>
       </c>
       <c r="AE94">
-        <v>0.113798</v>
+        <v>0.18207699999999999</v>
       </c>
       <c r="AF94">
-        <v>0.10188800000000001</v>
+        <v>0.163021</v>
       </c>
       <c r="AG94">
-        <v>0.10059800000000001</v>
+        <v>0.16095699999999999</v>
       </c>
       <c r="AH94">
-        <v>0.102863</v>
+        <v>0.16497300000000001</v>
       </c>
       <c r="AI94">
-        <v>0.10799400000000001</v>
+        <v>0.17221400000000001</v>
       </c>
       <c r="AJ94">
-        <v>0.17794199999999999</v>
+        <v>0.28470699999999999</v>
       </c>
       <c r="AK94">
-        <v>0.17355100000000001</v>
+        <v>0.27768100000000001</v>
       </c>
       <c r="AL94">
-        <v>0.17771799999999999</v>
+        <v>0.287771</v>
       </c>
       <c r="AM94">
-        <v>0.17766699999999999</v>
+        <v>0.28724</v>
       </c>
       <c r="AN94">
-        <v>0.178035</v>
+        <v>0.28675299999999998</v>
       </c>
       <c r="AO94">
-        <v>0.18846299999999999</v>
+        <v>0.29936699999999999</v>
       </c>
       <c r="AP94">
         <v>54.422764999999998</v>
@@ -24795,58 +24795,58 @@
         <v>29.050439999999998</v>
       </c>
       <c r="X95">
-        <v>9.4120999999999996E-2</v>
+        <v>0.15059400000000001</v>
       </c>
       <c r="Y95">
-        <v>9.7619999999999998E-2</v>
+        <v>0.155694</v>
       </c>
       <c r="Z95">
-        <v>8.7613999999999997E-2</v>
+        <v>0.140182</v>
       </c>
       <c r="AA95">
-        <v>8.8442000000000007E-2</v>
+        <v>0.14150699999999999</v>
       </c>
       <c r="AB95">
-        <v>9.0809000000000001E-2</v>
+        <v>0.14529400000000001</v>
       </c>
       <c r="AC95">
-        <v>9.4188999999999995E-2</v>
+        <v>0.150703</v>
       </c>
       <c r="AD95">
-        <v>0.108083</v>
+        <v>0.172933</v>
       </c>
       <c r="AE95">
-        <v>0.11243</v>
+        <v>0.17988899999999999</v>
       </c>
       <c r="AF95">
-        <v>9.6102000000000007E-2</v>
+        <v>0.15376200000000001</v>
       </c>
       <c r="AG95">
-        <v>9.8038E-2</v>
+        <v>0.15686</v>
       </c>
       <c r="AH95">
-        <v>0.100059</v>
+        <v>0.16108500000000001</v>
       </c>
       <c r="AI95">
-        <v>0.106184</v>
+        <v>0.16944999999999999</v>
       </c>
       <c r="AJ95">
-        <v>0.18135299999999999</v>
+        <v>0.29016500000000001</v>
       </c>
       <c r="AK95">
-        <v>0.17566200000000001</v>
+        <v>0.281059</v>
       </c>
       <c r="AL95">
-        <v>0.17414499999999999</v>
+        <v>0.28405399999999997</v>
       </c>
       <c r="AM95">
-        <v>0.174653</v>
+        <v>0.283993</v>
       </c>
       <c r="AN95">
-        <v>0.17488699999999999</v>
+        <v>0.28299000000000002</v>
       </c>
       <c r="AO95">
-        <v>0.18799199999999999</v>
+        <v>0.29857499999999998</v>
       </c>
       <c r="AP95">
         <v>53.903680000000001</v>
@@ -25007,58 +25007,58 @@
         <v>29.411935</v>
       </c>
       <c r="X96">
-        <v>9.2834E-2</v>
+        <v>0.148533</v>
       </c>
       <c r="Y96">
-        <v>9.6394999999999995E-2</v>
+        <v>0.15318000000000001</v>
       </c>
       <c r="Z96">
-        <v>9.3761999999999998E-2</v>
+        <v>0.15001900000000001</v>
       </c>
       <c r="AA96">
-        <v>9.9612000000000006E-2</v>
+        <v>0.15937899999999999</v>
       </c>
       <c r="AB96">
-        <v>9.7064999999999999E-2</v>
+        <v>0.155303</v>
       </c>
       <c r="AC96">
-        <v>0.11014</v>
+        <v>0.17624200000000001</v>
       </c>
       <c r="AD96">
-        <v>0.105847</v>
+        <v>0.169354</v>
       </c>
       <c r="AE96">
-        <v>0.111855</v>
+        <v>0.17896899999999999</v>
       </c>
       <c r="AF96">
-        <v>0.101627</v>
+        <v>0.162602</v>
       </c>
       <c r="AG96">
-        <v>0.109737</v>
+        <v>0.17558000000000001</v>
       </c>
       <c r="AH96">
-        <v>9.9774000000000002E-2</v>
+        <v>0.160577</v>
       </c>
       <c r="AI96">
-        <v>0.105102</v>
+        <v>0.16758300000000001</v>
       </c>
       <c r="AJ96">
-        <v>0.18301999999999999</v>
+        <v>0.29283199999999998</v>
       </c>
       <c r="AK96">
-        <v>0.17735500000000001</v>
+        <v>0.28376800000000002</v>
       </c>
       <c r="AL96">
-        <v>0.18160799999999999</v>
+        <v>0.29152600000000001</v>
       </c>
       <c r="AM96">
-        <v>0.180696</v>
+        <v>0.28919899999999998</v>
       </c>
       <c r="AN96">
-        <v>0.17824999999999999</v>
+        <v>0.28425899999999998</v>
       </c>
       <c r="AO96">
-        <v>0.188197</v>
+        <v>0.29816399999999998</v>
       </c>
       <c r="AP96">
         <v>53.247973999999999</v>
@@ -25219,58 +25219,58 @@
         <v>29.036987</v>
       </c>
       <c r="X97">
-        <v>9.2408000000000004E-2</v>
+        <v>0.14785300000000001</v>
       </c>
       <c r="Y97">
-        <v>9.3085000000000001E-2</v>
+        <v>0.14934600000000001</v>
       </c>
       <c r="Z97">
-        <v>9.7650000000000001E-2</v>
+        <v>0.15623999999999999</v>
       </c>
       <c r="AA97">
-        <v>9.2848E-2</v>
+        <v>0.14855599999999999</v>
       </c>
       <c r="AB97">
-        <v>9.2753000000000002E-2</v>
+        <v>0.14840400000000001</v>
       </c>
       <c r="AC97">
-        <v>0.10342899999999999</v>
+        <v>0.16549900000000001</v>
       </c>
       <c r="AD97">
-        <v>0.104473</v>
+        <v>0.167157</v>
       </c>
       <c r="AE97">
-        <v>0.109473</v>
+        <v>0.17515600000000001</v>
       </c>
       <c r="AF97">
-        <v>0.10242</v>
+        <v>0.16387199999999999</v>
       </c>
       <c r="AG97">
-        <v>0.10485899999999999</v>
+        <v>0.16777400000000001</v>
       </c>
       <c r="AH97">
-        <v>9.6752000000000005E-2</v>
+        <v>0.156387</v>
       </c>
       <c r="AI97">
-        <v>0.100796</v>
+        <v>0.16134799999999999</v>
       </c>
       <c r="AJ97">
-        <v>0.18126800000000001</v>
+        <v>0.29003000000000001</v>
       </c>
       <c r="AK97">
-        <v>0.17408100000000001</v>
+        <v>0.27853</v>
       </c>
       <c r="AL97">
-        <v>0.18069099999999999</v>
+        <v>0.29075499999999999</v>
       </c>
       <c r="AM97">
-        <v>0.174093</v>
+        <v>0.28226299999999999</v>
       </c>
       <c r="AN97">
-        <v>0.17449899999999999</v>
+        <v>0.279916</v>
       </c>
       <c r="AO97">
-        <v>0.18457799999999999</v>
+        <v>0.29456900000000003</v>
       </c>
       <c r="AP97">
         <v>52.769148000000001</v>
@@ -25431,58 +25431,58 @@
         <v>28.113744000000001</v>
       </c>
       <c r="X98">
-        <v>9.1620999999999994E-2</v>
+        <v>0.146593</v>
       </c>
       <c r="Y98">
-        <v>9.1110999999999998E-2</v>
+        <v>0.146896</v>
       </c>
       <c r="Z98">
-        <v>9.5223000000000002E-2</v>
+        <v>0.15235699999999999</v>
       </c>
       <c r="AA98">
-        <v>8.5530999999999996E-2</v>
+        <v>0.13685</v>
       </c>
       <c r="AB98">
-        <v>8.6820999999999995E-2</v>
+        <v>0.13891300000000001</v>
       </c>
       <c r="AC98">
-        <v>8.3615999999999996E-2</v>
+        <v>0.13377900000000001</v>
       </c>
       <c r="AD98">
-        <v>0.103702</v>
+        <v>0.16592299999999999</v>
       </c>
       <c r="AE98">
-        <v>0.107142</v>
+        <v>0.171427</v>
       </c>
       <c r="AF98">
-        <v>0.10238800000000001</v>
+        <v>0.16381999999999999</v>
       </c>
       <c r="AG98">
-        <v>0.10288</v>
+        <v>0.164608</v>
       </c>
       <c r="AH98">
-        <v>9.3793000000000001E-2</v>
+        <v>0.15231600000000001</v>
       </c>
       <c r="AI98">
-        <v>9.5731999999999998E-2</v>
+        <v>0.154139</v>
       </c>
       <c r="AJ98">
-        <v>0.17961299999999999</v>
+        <v>0.28738000000000002</v>
       </c>
       <c r="AK98">
-        <v>0.17058100000000001</v>
+        <v>0.27293000000000001</v>
       </c>
       <c r="AL98">
-        <v>0.182251</v>
+        <v>0.29300199999999998</v>
       </c>
       <c r="AM98">
-        <v>0.171454</v>
+        <v>0.27958</v>
       </c>
       <c r="AN98">
-        <v>0.17032900000000001</v>
+        <v>0.27526400000000001</v>
       </c>
       <c r="AO98">
-        <v>0.180368</v>
+        <v>0.290489</v>
       </c>
       <c r="AP98">
         <v>52.996341999999999</v>
@@ -25643,58 +25643,58 @@
         <v>27.709855000000001</v>
       </c>
       <c r="X99">
-        <v>9.1110999999999998E-2</v>
+        <v>0.14577699999999999</v>
       </c>
       <c r="Y99">
-        <v>9.2057E-2</v>
+        <v>0.146125</v>
       </c>
       <c r="Z99">
-        <v>9.2954999999999996E-2</v>
+        <v>0.148727</v>
       </c>
       <c r="AA99">
-        <v>9.0176000000000006E-2</v>
+        <v>0.14428099999999999</v>
       </c>
       <c r="AB99">
-        <v>8.9584999999999998E-2</v>
+        <v>0.14333599999999999</v>
       </c>
       <c r="AC99">
-        <v>8.3283999999999997E-2</v>
+        <v>0.13324900000000001</v>
       </c>
       <c r="AD99">
-        <v>0.10316599999999999</v>
+        <v>0.16506599999999999</v>
       </c>
       <c r="AE99">
-        <v>0.104805</v>
+        <v>0.167687</v>
       </c>
       <c r="AF99">
-        <v>0.106582</v>
+        <v>0.17053099999999999</v>
       </c>
       <c r="AG99">
-        <v>0.106322</v>
+        <v>0.17011399999999999</v>
       </c>
       <c r="AH99">
-        <v>9.3803999999999998E-2</v>
+        <v>0.15235899999999999</v>
       </c>
       <c r="AI99">
-        <v>9.5018000000000005E-2</v>
+        <v>0.15293699999999999</v>
       </c>
       <c r="AJ99">
-        <v>0.178094</v>
+        <v>0.28494999999999998</v>
       </c>
       <c r="AK99">
-        <v>0.16732900000000001</v>
+        <v>0.26772600000000002</v>
       </c>
       <c r="AL99">
-        <v>0.18926699999999999</v>
+        <v>0.30079600000000001</v>
       </c>
       <c r="AM99">
-        <v>0.17704700000000001</v>
+        <v>0.28510099999999999</v>
       </c>
       <c r="AN99">
-        <v>0.17038800000000001</v>
+        <v>0.27410899999999999</v>
       </c>
       <c r="AO99">
-        <v>0.18002699999999999</v>
+        <v>0.28963899999999998</v>
       </c>
       <c r="AP99">
         <v>53.830320999999998</v>
@@ -25855,58 +25855,58 @@
         <v>27.916671000000001</v>
       </c>
       <c r="X100">
-        <v>8.9468000000000006E-2</v>
+        <v>0.143149</v>
       </c>
       <c r="Y100">
-        <v>8.6762000000000006E-2</v>
+        <v>0.14080999999999999</v>
       </c>
       <c r="Z100">
-        <v>8.9399999999999993E-2</v>
+        <v>0.14304</v>
       </c>
       <c r="AA100">
-        <v>9.0126999999999999E-2</v>
+        <v>0.144204</v>
       </c>
       <c r="AB100">
-        <v>8.8960999999999998E-2</v>
+        <v>0.14233699999999999</v>
       </c>
       <c r="AC100">
-        <v>8.6222999999999994E-2</v>
+        <v>0.13795299999999999</v>
       </c>
       <c r="AD100">
-        <v>0.103189</v>
+        <v>0.165103</v>
       </c>
       <c r="AE100">
-        <v>9.9743999999999999E-2</v>
+        <v>0.15959100000000001</v>
       </c>
       <c r="AF100">
-        <v>0.104742</v>
+        <v>0.16758700000000001</v>
       </c>
       <c r="AG100">
-        <v>0.10016700000000001</v>
+        <v>0.16026699999999999</v>
       </c>
       <c r="AH100">
-        <v>9.2937000000000006E-2</v>
+        <v>0.15134300000000001</v>
       </c>
       <c r="AI100">
-        <v>9.6673999999999996E-2</v>
+        <v>0.155115</v>
       </c>
       <c r="AJ100">
-        <v>0.17416599999999999</v>
+        <v>0.27866600000000002</v>
       </c>
       <c r="AK100">
-        <v>0.16042600000000001</v>
+        <v>0.25668200000000002</v>
       </c>
       <c r="AL100">
-        <v>0.185969</v>
+        <v>0.29769200000000001</v>
       </c>
       <c r="AM100">
-        <v>0.17147799999999999</v>
+        <v>0.27931</v>
       </c>
       <c r="AN100">
-        <v>0.16669</v>
+        <v>0.27030300000000002</v>
       </c>
       <c r="AO100">
-        <v>0.18070700000000001</v>
+        <v>0.28979899999999997</v>
       </c>
       <c r="AP100">
         <v>54.759554999999999</v>
@@ -26064,58 +26064,58 @@
         <v>27.921491</v>
       </c>
       <c r="X101">
-        <v>8.8072999999999999E-2</v>
+        <v>0.14091600000000001</v>
       </c>
       <c r="Y101">
-        <v>8.3062999999999998E-2</v>
+        <v>0.13733200000000001</v>
       </c>
       <c r="Z101">
-        <v>8.7832999999999994E-2</v>
+        <v>0.14053299999999999</v>
       </c>
       <c r="AA101">
-        <v>8.7497000000000005E-2</v>
+        <v>0.13999500000000001</v>
       </c>
       <c r="AB101">
-        <v>8.6487999999999995E-2</v>
+        <v>0.138381</v>
       </c>
       <c r="AC101">
-        <v>8.7040000000000006E-2</v>
+        <v>0.139262</v>
       </c>
       <c r="AD101">
-        <v>0.10341400000000001</v>
+        <v>0.165462</v>
       </c>
       <c r="AE101">
-        <v>9.7489000000000006E-2</v>
+        <v>0.15598200000000001</v>
       </c>
       <c r="AF101">
-        <v>0.103655</v>
+        <v>0.16584699999999999</v>
       </c>
       <c r="AG101">
-        <v>9.6914E-2</v>
+        <v>0.15506200000000001</v>
       </c>
       <c r="AH101">
-        <v>9.2161000000000007E-2</v>
+        <v>0.15051500000000001</v>
       </c>
       <c r="AI101">
-        <v>9.7550999999999999E-2</v>
+        <v>0.15632399999999999</v>
       </c>
       <c r="AJ101">
-        <v>0.17246800000000001</v>
+        <v>0.27594800000000003</v>
       </c>
       <c r="AK101">
-        <v>0.15859500000000001</v>
+        <v>0.25375199999999998</v>
       </c>
       <c r="AL101">
-        <v>0.185054</v>
+        <v>0.29675600000000002</v>
       </c>
       <c r="AM101">
-        <v>0.166739</v>
+        <v>0.27446100000000001</v>
       </c>
       <c r="AN101">
-        <v>0.163828</v>
+        <v>0.26766400000000001</v>
       </c>
       <c r="AO101">
-        <v>0.180149</v>
+        <v>0.28915299999999999</v>
       </c>
       <c r="AP101">
         <v>55.438701999999999</v>
@@ -26501,58 +26501,58 @@
         <v>23.253312999999999</v>
       </c>
       <c r="X2">
-        <v>0.103545</v>
+        <v>0.16567200000000001</v>
       </c>
       <c r="Y2">
-        <v>0.111859</v>
+        <v>0.176481</v>
       </c>
       <c r="Z2">
-        <v>0.114302</v>
+        <v>0.18288299999999999</v>
       </c>
       <c r="AA2">
-        <v>0.10620599999999999</v>
+        <v>0.16993</v>
       </c>
       <c r="AB2">
-        <v>9.3863000000000002E-2</v>
+        <v>0.15018000000000001</v>
       </c>
       <c r="AC2">
-        <v>8.9057999999999998E-2</v>
+        <v>0.14249200000000001</v>
       </c>
       <c r="AD2">
-        <v>0.11046499999999999</v>
+        <v>0.17674400000000001</v>
       </c>
       <c r="AE2">
-        <v>0.11708300000000001</v>
+        <v>0.187333</v>
       </c>
       <c r="AF2">
-        <v>0.12199400000000001</v>
+        <v>0.195191</v>
       </c>
       <c r="AG2">
-        <v>0.114038</v>
+        <v>0.18246100000000001</v>
       </c>
       <c r="AH2">
-        <v>9.8857E-2</v>
+        <v>0.15909799999999999</v>
       </c>
       <c r="AI2">
-        <v>9.8123000000000002E-2</v>
+        <v>0.157252</v>
       </c>
       <c r="AJ2">
-        <v>0.17921599999999999</v>
+        <v>0.286746</v>
       </c>
       <c r="AK2">
-        <v>0.18455099999999999</v>
+        <v>0.29528199999999999</v>
       </c>
       <c r="AL2">
-        <v>0.194108</v>
+        <v>0.30735299999999999</v>
       </c>
       <c r="AM2">
-        <v>0.18620300000000001</v>
+        <v>0.29675699999999999</v>
       </c>
       <c r="AN2">
-        <v>0.16463700000000001</v>
+        <v>0.26597599999999999</v>
       </c>
       <c r="AO2">
-        <v>0.17091999999999999</v>
+        <v>0.27681</v>
       </c>
       <c r="AP2">
         <v>57.282170000000001</v>
@@ -26713,58 +26713,58 @@
         <v>23.400338000000001</v>
       </c>
       <c r="X3">
-        <v>9.9150000000000002E-2</v>
+        <v>0.158639</v>
       </c>
       <c r="Y3">
-        <v>0.100468</v>
+        <v>0.16269600000000001</v>
       </c>
       <c r="Z3">
-        <v>0.110943</v>
+        <v>0.177509</v>
       </c>
       <c r="AA3">
-        <v>0.104167</v>
+        <v>0.16666700000000001</v>
       </c>
       <c r="AB3">
-        <v>9.3761999999999998E-2</v>
+        <v>0.15001900000000001</v>
       </c>
       <c r="AC3">
-        <v>8.8742000000000001E-2</v>
+        <v>0.141984</v>
       </c>
       <c r="AD3">
-        <v>0.109989</v>
+        <v>0.175982</v>
       </c>
       <c r="AE3">
-        <v>0.113293</v>
+        <v>0.18126800000000001</v>
       </c>
       <c r="AF3">
-        <v>0.12565799999999999</v>
+        <v>0.20105300000000001</v>
       </c>
       <c r="AG3">
-        <v>0.11666899999999999</v>
+        <v>0.18667</v>
       </c>
       <c r="AH3">
-        <v>0.103072</v>
+        <v>0.16508500000000001</v>
       </c>
       <c r="AI3">
-        <v>0.100435</v>
+        <v>0.16083</v>
       </c>
       <c r="AJ3">
-        <v>0.17479600000000001</v>
+        <v>0.279673</v>
       </c>
       <c r="AK3">
-        <v>0.17426800000000001</v>
+        <v>0.27882899999999999</v>
       </c>
       <c r="AL3">
-        <v>0.19375200000000001</v>
+        <v>0.30734499999999998</v>
       </c>
       <c r="AM3">
-        <v>0.18690399999999999</v>
+        <v>0.298037</v>
       </c>
       <c r="AN3">
-        <v>0.17081399999999999</v>
+        <v>0.27402700000000002</v>
       </c>
       <c r="AO3">
-        <v>0.171991</v>
+        <v>0.27859400000000001</v>
       </c>
       <c r="AP3">
         <v>56.163572000000002</v>
@@ -26925,58 +26925,58 @@
         <v>24.730031</v>
       </c>
       <c r="X4">
-        <v>9.9945000000000006E-2</v>
+        <v>0.159913</v>
       </c>
       <c r="Y4">
-        <v>9.9443000000000004E-2</v>
+        <v>0.160106</v>
       </c>
       <c r="Z4">
-        <v>0.11505899999999999</v>
+        <v>0.18409400000000001</v>
       </c>
       <c r="AA4">
-        <v>0.105085</v>
+        <v>0.16813500000000001</v>
       </c>
       <c r="AB4">
-        <v>9.5261999999999999E-2</v>
+        <v>0.15242</v>
       </c>
       <c r="AC4">
-        <v>9.6703999999999998E-2</v>
+        <v>0.15472900000000001</v>
       </c>
       <c r="AD4">
-        <v>0.110975</v>
+        <v>0.17756</v>
       </c>
       <c r="AE4">
-        <v>0.113402</v>
+        <v>0.18144399999999999</v>
       </c>
       <c r="AF4">
-        <v>0.12649299999999999</v>
+        <v>0.20238900000000001</v>
       </c>
       <c r="AG4">
-        <v>0.117275</v>
+        <v>0.18764</v>
       </c>
       <c r="AH4">
-        <v>0.10660500000000001</v>
+        <v>0.170346</v>
       </c>
       <c r="AI4">
-        <v>0.10301100000000001</v>
+        <v>0.164682</v>
       </c>
       <c r="AJ4">
-        <v>0.17812500000000001</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="AK4">
-        <v>0.172099</v>
+        <v>0.27535900000000002</v>
       </c>
       <c r="AL4">
-        <v>0.19592899999999999</v>
+        <v>0.309782</v>
       </c>
       <c r="AM4">
-        <v>0.19090699999999999</v>
+        <v>0.30277399999999999</v>
       </c>
       <c r="AN4">
-        <v>0.17665400000000001</v>
+        <v>0.28265800000000002</v>
       </c>
       <c r="AO4">
-        <v>0.17821600000000001</v>
+        <v>0.28547600000000001</v>
       </c>
       <c r="AP4">
         <v>54.737501999999999</v>
@@ -27137,58 +27137,58 @@
         <v>26.103929999999998</v>
       </c>
       <c r="X5">
-        <v>9.8374000000000003E-2</v>
+        <v>0.15739900000000001</v>
       </c>
       <c r="Y5">
-        <v>0.10273699999999999</v>
+        <v>0.16342999999999999</v>
       </c>
       <c r="Z5">
-        <v>0.11355999999999999</v>
+        <v>0.181696</v>
       </c>
       <c r="AA5">
-        <v>0.101497</v>
+        <v>0.16239600000000001</v>
       </c>
       <c r="AB5">
-        <v>9.4593999999999998E-2</v>
+        <v>0.15135100000000001</v>
       </c>
       <c r="AC5">
-        <v>9.1342999999999994E-2</v>
+        <v>0.146148</v>
       </c>
       <c r="AD5">
-        <v>0.10760400000000001</v>
+        <v>0.17216699999999999</v>
       </c>
       <c r="AE5">
-        <v>0.114283</v>
+        <v>0.18285299999999999</v>
       </c>
       <c r="AF5">
-        <v>0.125857</v>
+        <v>0.201372</v>
       </c>
       <c r="AG5">
-        <v>0.113009</v>
+        <v>0.180814</v>
       </c>
       <c r="AH5">
-        <v>0.10868899999999999</v>
+        <v>0.17366799999999999</v>
       </c>
       <c r="AI5">
-        <v>0.10329000000000001</v>
+        <v>0.165272</v>
       </c>
       <c r="AJ5">
-        <v>0.17482200000000001</v>
+        <v>0.27971499999999999</v>
       </c>
       <c r="AK5">
-        <v>0.17529700000000001</v>
+        <v>0.28047499999999997</v>
       </c>
       <c r="AL5">
-        <v>0.191881</v>
+        <v>0.30515700000000001</v>
       </c>
       <c r="AM5">
-        <v>0.190304</v>
+        <v>0.30219699999999999</v>
       </c>
       <c r="AN5">
-        <v>0.182784</v>
+        <v>0.29208600000000001</v>
       </c>
       <c r="AO5">
-        <v>0.182564</v>
+        <v>0.291215</v>
       </c>
       <c r="AP5">
         <v>53.776716</v>
@@ -27349,58 +27349,58 @@
         <v>26.827175</v>
       </c>
       <c r="X6">
-        <v>9.8072999999999994E-2</v>
+        <v>0.156918</v>
       </c>
       <c r="Y6">
-        <v>0.100317</v>
+        <v>0.15901899999999999</v>
       </c>
       <c r="Z6">
-        <v>0.109113</v>
+        <v>0.17458199999999999</v>
       </c>
       <c r="AA6">
-        <v>0.100385</v>
+        <v>0.16061600000000001</v>
       </c>
       <c r="AB6">
-        <v>0.10188999999999999</v>
+        <v>0.163024</v>
       </c>
       <c r="AC6">
-        <v>9.2531000000000002E-2</v>
+        <v>0.14805099999999999</v>
       </c>
       <c r="AD6">
-        <v>0.104711</v>
+        <v>0.16753799999999999</v>
       </c>
       <c r="AE6">
-        <v>0.10810599999999999</v>
+        <v>0.17297000000000001</v>
       </c>
       <c r="AF6">
-        <v>0.120841</v>
+        <v>0.19334599999999999</v>
       </c>
       <c r="AG6">
-        <v>0.11522300000000001</v>
+        <v>0.18435699999999999</v>
       </c>
       <c r="AH6">
-        <v>0.11201899999999999</v>
+        <v>0.17852699999999999</v>
       </c>
       <c r="AI6">
-        <v>0.103452</v>
+        <v>0.165548</v>
       </c>
       <c r="AJ6">
-        <v>0.173343</v>
+        <v>0.27734799999999998</v>
       </c>
       <c r="AK6">
-        <v>0.17366699999999999</v>
+        <v>0.277868</v>
       </c>
       <c r="AL6">
-        <v>0.19158500000000001</v>
+        <v>0.30413099999999998</v>
       </c>
       <c r="AM6">
-        <v>0.19000800000000001</v>
+        <v>0.30146400000000001</v>
       </c>
       <c r="AN6">
-        <v>0.189358</v>
+        <v>0.30049100000000001</v>
       </c>
       <c r="AO6">
-        <v>0.18429899999999999</v>
+        <v>0.29401500000000003</v>
       </c>
       <c r="AP6">
         <v>53.489652999999997</v>
@@ -27561,58 +27561,58 @@
         <v>27.140089</v>
       </c>
       <c r="X7">
-        <v>9.3477000000000005E-2</v>
+        <v>0.149563</v>
       </c>
       <c r="Y7">
-        <v>8.7714E-2</v>
+        <v>0.143479</v>
       </c>
       <c r="Z7">
-        <v>9.4128000000000003E-2</v>
+        <v>0.15060499999999999</v>
       </c>
       <c r="AA7">
-        <v>9.2807000000000001E-2</v>
+        <v>0.14849100000000001</v>
       </c>
       <c r="AB7">
-        <v>9.3798999999999993E-2</v>
+        <v>0.15007899999999999</v>
       </c>
       <c r="AC7">
-        <v>8.8501999999999997E-2</v>
+        <v>0.141601</v>
       </c>
       <c r="AD7">
-        <v>0.103411</v>
+        <v>0.16545699999999999</v>
       </c>
       <c r="AE7">
-        <v>9.8829E-2</v>
+        <v>0.15812699999999999</v>
       </c>
       <c r="AF7">
-        <v>0.10417</v>
+        <v>0.16667199999999999</v>
       </c>
       <c r="AG7">
-        <v>0.10491499999999999</v>
+        <v>0.16786400000000001</v>
       </c>
       <c r="AH7">
-        <v>0.11058999999999999</v>
+        <v>0.176756</v>
       </c>
       <c r="AI7">
-        <v>0.103007</v>
+        <v>0.16503599999999999</v>
       </c>
       <c r="AJ7">
-        <v>0.17568400000000001</v>
+        <v>0.28109400000000001</v>
       </c>
       <c r="AK7">
-        <v>0.160857</v>
+        <v>0.25737100000000002</v>
       </c>
       <c r="AL7">
-        <v>0.17510200000000001</v>
+        <v>0.28478100000000001</v>
       </c>
       <c r="AM7">
-        <v>0.18087500000000001</v>
+        <v>0.29128399999999999</v>
       </c>
       <c r="AN7">
-        <v>0.18735199999999999</v>
+        <v>0.30083500000000002</v>
       </c>
       <c r="AO7">
-        <v>0.184391</v>
+        <v>0.29507100000000003</v>
       </c>
       <c r="AP7">
         <v>53.404221999999997</v>
@@ -27773,58 +27773,58 @@
         <v>28.501255</v>
       </c>
       <c r="X8">
-        <v>8.9876999999999999E-2</v>
+        <v>0.14380299999999999</v>
       </c>
       <c r="Y8">
-        <v>8.813E-2</v>
+        <v>0.141461</v>
       </c>
       <c r="Z8">
-        <v>9.4708000000000001E-2</v>
+        <v>0.151533</v>
       </c>
       <c r="AA8">
-        <v>0.103196</v>
+        <v>0.16511300000000001</v>
       </c>
       <c r="AB8">
-        <v>0.10073</v>
+        <v>0.16116800000000001</v>
       </c>
       <c r="AC8">
-        <v>9.6584000000000003E-2</v>
+        <v>0.15453700000000001</v>
       </c>
       <c r="AD8">
-        <v>0.103143</v>
+        <v>0.16502800000000001</v>
       </c>
       <c r="AE8">
-        <v>9.9282999999999996E-2</v>
+        <v>0.158854</v>
       </c>
       <c r="AF8">
-        <v>0.10550900000000001</v>
+        <v>0.16881399999999999</v>
       </c>
       <c r="AG8">
-        <v>0.117324</v>
+        <v>0.187718</v>
       </c>
       <c r="AH8">
-        <v>0.11423800000000001</v>
+        <v>0.18173</v>
       </c>
       <c r="AI8">
-        <v>0.10551000000000001</v>
+        <v>0.16859499999999999</v>
       </c>
       <c r="AJ8">
-        <v>0.17761299999999999</v>
+        <v>0.28417999999999999</v>
       </c>
       <c r="AK8">
-        <v>0.161635</v>
+        <v>0.25861600000000001</v>
       </c>
       <c r="AL8">
-        <v>0.18196200000000001</v>
+        <v>0.29234100000000002</v>
       </c>
       <c r="AM8">
-        <v>0.19219900000000001</v>
+        <v>0.303705</v>
       </c>
       <c r="AN8">
-        <v>0.19331200000000001</v>
+        <v>0.30672199999999999</v>
       </c>
       <c r="AO8">
-        <v>0.186166</v>
+        <v>0.297126</v>
       </c>
       <c r="AP8">
         <v>53.515425999999998</v>
@@ -27985,58 +27985,58 @@
         <v>29.208604000000001</v>
       </c>
       <c r="X9">
-        <v>8.7931999999999996E-2</v>
+        <v>0.14069200000000001</v>
       </c>
       <c r="Y9">
-        <v>8.8367000000000001E-2</v>
+        <v>0.14114499999999999</v>
       </c>
       <c r="Z9">
-        <v>8.9464000000000002E-2</v>
+        <v>0.14314299999999999</v>
       </c>
       <c r="AA9">
-        <v>9.2491000000000004E-2</v>
+        <v>0.14798600000000001</v>
       </c>
       <c r="AB9">
-        <v>9.3031000000000003E-2</v>
+        <v>0.14884900000000001</v>
       </c>
       <c r="AC9">
-        <v>9.0410000000000004E-2</v>
+        <v>0.14465500000000001</v>
       </c>
       <c r="AD9">
-        <v>0.102936</v>
+        <v>0.16469800000000001</v>
       </c>
       <c r="AE9">
-        <v>0.10206</v>
+        <v>0.163296</v>
       </c>
       <c r="AF9">
-        <v>0.105072</v>
+        <v>0.16811599999999999</v>
       </c>
       <c r="AG9">
-        <v>0.107594</v>
+        <v>0.17215</v>
       </c>
       <c r="AH9">
-        <v>0.110802</v>
+        <v>0.17671999999999999</v>
       </c>
       <c r="AI9">
-        <v>0.104847</v>
+        <v>0.16774</v>
       </c>
       <c r="AJ9">
-        <v>0.17837500000000001</v>
+        <v>0.28539999999999999</v>
       </c>
       <c r="AK9">
-        <v>0.166907</v>
+        <v>0.26705200000000001</v>
       </c>
       <c r="AL9">
-        <v>0.181251</v>
+        <v>0.29159499999999999</v>
       </c>
       <c r="AM9">
-        <v>0.18310100000000001</v>
+        <v>0.29334700000000002</v>
       </c>
       <c r="AN9">
-        <v>0.19073200000000001</v>
+        <v>0.30368899999999999</v>
       </c>
       <c r="AO9">
-        <v>0.186252</v>
+        <v>0.297572</v>
       </c>
       <c r="AP9">
         <v>52.721324000000003</v>
@@ -28197,58 +28197,58 @@
         <v>29.605491000000001</v>
       </c>
       <c r="X10">
-        <v>8.7370000000000003E-2</v>
+        <v>0.139791</v>
       </c>
       <c r="Y10">
-        <v>8.6927000000000004E-2</v>
+        <v>0.13989499999999999</v>
       </c>
       <c r="Z10">
-        <v>8.8390999999999997E-2</v>
+        <v>0.141425</v>
       </c>
       <c r="AA10">
-        <v>8.7722999999999995E-2</v>
+        <v>0.14035600000000001</v>
       </c>
       <c r="AB10">
-        <v>8.9486999999999997E-2</v>
+        <v>0.143179</v>
       </c>
       <c r="AC10">
-        <v>9.1354000000000005E-2</v>
+        <v>0.14616599999999999</v>
       </c>
       <c r="AD10">
-        <v>0.104645</v>
+        <v>0.167431</v>
       </c>
       <c r="AE10">
-        <v>0.101311</v>
+        <v>0.16209699999999999</v>
       </c>
       <c r="AF10">
-        <v>0.10237</v>
+        <v>0.16379199999999999</v>
       </c>
       <c r="AG10">
-        <v>0.101382</v>
+        <v>0.162212</v>
       </c>
       <c r="AH10">
-        <v>0.105089</v>
+        <v>0.16855500000000001</v>
       </c>
       <c r="AI10">
-        <v>0.104355</v>
+        <v>0.166963</v>
       </c>
       <c r="AJ10">
-        <v>0.180697</v>
+        <v>0.28911500000000001</v>
       </c>
       <c r="AK10">
-        <v>0.16702800000000001</v>
+        <v>0.26724500000000001</v>
       </c>
       <c r="AL10">
-        <v>0.178233</v>
+        <v>0.28833599999999998</v>
       </c>
       <c r="AM10">
-        <v>0.178199</v>
+        <v>0.28759600000000002</v>
       </c>
       <c r="AN10">
-        <v>0.185308</v>
+        <v>0.29677500000000001</v>
       </c>
       <c r="AO10">
-        <v>0.18745600000000001</v>
+        <v>0.29851</v>
       </c>
       <c r="AP10">
         <v>52.471338000000003</v>
@@ -28409,58 +28409,58 @@
         <v>28.209334999999999</v>
       </c>
       <c r="X11">
-        <v>9.2908000000000004E-2</v>
+        <v>0.14865300000000001</v>
       </c>
       <c r="Y11">
-        <v>9.4107999999999997E-2</v>
+        <v>0.15085499999999999</v>
       </c>
       <c r="Z11">
-        <v>9.2876E-2</v>
+        <v>0.14860200000000001</v>
       </c>
       <c r="AA11">
-        <v>9.0604000000000004E-2</v>
+        <v>0.14496700000000001</v>
       </c>
       <c r="AB11">
-        <v>9.1394000000000003E-2</v>
+        <v>0.14623</v>
       </c>
       <c r="AC11">
-        <v>9.2641000000000001E-2</v>
+        <v>0.148228</v>
       </c>
       <c r="AD11">
-        <v>0.10546700000000001</v>
+        <v>0.16874700000000001</v>
       </c>
       <c r="AE11">
-        <v>0.108532</v>
+        <v>0.173651</v>
       </c>
       <c r="AF11">
-        <v>0.102613</v>
+        <v>0.16418099999999999</v>
       </c>
       <c r="AG11">
-        <v>0.10218099999999999</v>
+        <v>0.163489</v>
       </c>
       <c r="AH11">
-        <v>9.8382999999999998E-2</v>
+        <v>0.15872900000000001</v>
       </c>
       <c r="AI11">
-        <v>0.101923</v>
+        <v>0.163132</v>
       </c>
       <c r="AJ11">
-        <v>0.177677</v>
+        <v>0.28428300000000001</v>
       </c>
       <c r="AK11">
-        <v>0.16952800000000001</v>
+        <v>0.27124399999999999</v>
       </c>
       <c r="AL11">
-        <v>0.17949100000000001</v>
+        <v>0.28981699999999999</v>
       </c>
       <c r="AM11">
-        <v>0.173931</v>
+        <v>0.28240300000000002</v>
       </c>
       <c r="AN11">
-        <v>0.17423</v>
+        <v>0.28025600000000001</v>
       </c>
       <c r="AO11">
-        <v>0.18460699999999999</v>
+        <v>0.29474899999999998</v>
       </c>
       <c r="AP11">
         <v>54.206511999999996</v>

--- a/Data/2015_F013B4_CO_ISOS/2015_F013B4_CO_ISOS_SoilAnalysis.xlsx
+++ b/Data/2015_F013B4_CO_ISOS/2015_F013B4_CO_ISOS_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2015_F013B4_CO_ISOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5A46FF-5482-4CA6-A7B8-768EF08A13DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07FA35A-5B4E-4DE5-BD93-FE0577481777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-975" yWindow="-24765" windowWidth="17775" windowHeight="24285" xr2:uid="{703BA8F2-5457-4E8B-97CE-55FD3F4AE98B}"/>
+    <workbookView xWindow="-1815" yWindow="-28020" windowWidth="16335" windowHeight="23370" xr2:uid="{703BA8F2-5457-4E8B-97CE-55FD3F4AE98B}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDJH" sheetId="4" r:id="rId1"/>
@@ -380,12 +380,6 @@
     <t>Plot</t>
   </si>
   <si>
-    <t>2015d118EM38</t>
-  </si>
-  <si>
-    <t>2015d119EM38</t>
-  </si>
-  <si>
     <t>SLSND015</t>
   </si>
   <si>
@@ -1179,6 +1173,12 @@
   </si>
   <si>
     <t>2013d260EM38V</t>
+  </si>
+  <si>
+    <t>2015d118EM38V</t>
+  </si>
+  <si>
+    <t>2015d119EM38V</t>
   </si>
 </sst>
 </file>
@@ -1558,13 +1558,13 @@
         <v>101</v>
       </c>
       <c r="B1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E1" t="s">
         <v>112</v>
@@ -1575,7 +1575,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C2">
         <v>408983.429999999</v>
@@ -1592,7 +1592,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C3">
         <v>408983.89409999899</v>
@@ -1609,7 +1609,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C4">
         <v>408984.30259999901</v>
@@ -1626,7 +1626,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C5">
         <v>408984.79070000001</v>
@@ -1643,7 +1643,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C6">
         <v>408985.21360000002</v>
@@ -1660,7 +1660,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C7">
         <v>408985.649299999</v>
@@ -1677,7 +1677,7 @@
         <v>131</v>
       </c>
       <c r="B8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C8">
         <v>408992.87400000001</v>
@@ -1694,7 +1694,7 @@
         <v>132</v>
       </c>
       <c r="B9" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C9">
         <v>408992.37520000001</v>
@@ -1711,7 +1711,7 @@
         <v>133</v>
       </c>
       <c r="B10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C10">
         <v>408991.93300000002</v>
@@ -1728,7 +1728,7 @@
         <v>134</v>
       </c>
       <c r="B11" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C11">
         <v>408991.4412</v>
@@ -1745,7 +1745,7 @@
         <v>135</v>
       </c>
       <c r="B12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C12">
         <v>408990.94170000002</v>
@@ -1762,7 +1762,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C13">
         <v>408957.18540000002</v>
@@ -1779,7 +1779,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C14">
         <v>408956.76750000002</v>
@@ -1796,7 +1796,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C15">
         <v>408956.30570000003</v>
@@ -1813,7 +1813,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C16">
         <v>408955.91499999899</v>
@@ -1830,7 +1830,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C17">
         <v>408955.44280000002</v>
@@ -1847,7 +1847,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C18">
         <v>408955.01179999899</v>
@@ -1864,7 +1864,7 @@
         <v>136</v>
       </c>
       <c r="B19" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C19">
         <v>408962.41840000002</v>
@@ -1881,7 +1881,7 @@
         <v>137</v>
       </c>
       <c r="B20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C20">
         <v>408961.93680000002</v>
@@ -1898,7 +1898,7 @@
         <v>138</v>
       </c>
       <c r="B21" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C21">
         <v>408961.4645</v>
@@ -1915,7 +1915,7 @@
         <v>139</v>
       </c>
       <c r="B22" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C22">
         <v>408960.96830000001</v>
@@ -1932,7 +1932,7 @@
         <v>140</v>
       </c>
       <c r="B23" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C23">
         <v>408960.493599999</v>
@@ -1949,7 +1949,7 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C24">
         <v>408926.557299999</v>
@@ -1966,7 +1966,7 @@
         <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C25">
         <v>408926.97979999898</v>
@@ -1983,7 +1983,7 @@
         <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C26">
         <v>408927.42930000002</v>
@@ -2000,7 +2000,7 @@
         <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C27">
         <v>408927.88109999901</v>
@@ -2017,7 +2017,7 @@
         <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C28">
         <v>408928.31640000001</v>
@@ -2034,7 +2034,7 @@
         <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C29">
         <v>408928.783999999</v>
@@ -2051,7 +2051,7 @@
         <v>141</v>
       </c>
       <c r="B30" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C30">
         <v>408936.025599999</v>
@@ -2068,7 +2068,7 @@
         <v>142</v>
       </c>
       <c r="B31" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C31">
         <v>408935.529199999</v>
@@ -2085,7 +2085,7 @@
         <v>143</v>
       </c>
       <c r="B32" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C32">
         <v>408935.03840000002</v>
@@ -2102,7 +2102,7 @@
         <v>144</v>
       </c>
       <c r="B33" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C33">
         <v>408934.55099999899</v>
@@ -2119,7 +2119,7 @@
         <v>145</v>
       </c>
       <c r="B34" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C34">
         <v>408934.06530000002</v>
@@ -2136,7 +2136,7 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C35">
         <v>408901.33329999901</v>
@@ -2153,7 +2153,7 @@
         <v>26</v>
       </c>
       <c r="B36" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C36">
         <v>408900.9032</v>
@@ -2170,7 +2170,7 @@
         <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C37">
         <v>408900.44150000002</v>
@@ -2187,7 +2187,7 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C38">
         <v>408899.99949999899</v>
@@ -2204,7 +2204,7 @@
         <v>29</v>
       </c>
       <c r="B39" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C39">
         <v>408899.580599999</v>
@@ -2221,7 +2221,7 @@
         <v>30</v>
       </c>
       <c r="B40" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C40">
         <v>408899.109999999</v>
@@ -2238,7 +2238,7 @@
         <v>146</v>
       </c>
       <c r="B41" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C41">
         <v>408906.29479999898</v>
@@ -2255,7 +2255,7 @@
         <v>147</v>
       </c>
       <c r="B42" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C42">
         <v>408905.79359999899</v>
@@ -2272,7 +2272,7 @@
         <v>148</v>
       </c>
       <c r="B43" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C43">
         <v>408905.32140000002</v>
@@ -2289,7 +2289,7 @@
         <v>149</v>
       </c>
       <c r="B44" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C44">
         <v>408904.8211</v>
@@ -2306,7 +2306,7 @@
         <v>150</v>
       </c>
       <c r="B45" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C45">
         <v>408904.35749999899</v>
@@ -2323,7 +2323,7 @@
         <v>31</v>
       </c>
       <c r="B46" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C46">
         <v>408870.67979999899</v>
@@ -2340,7 +2340,7 @@
         <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C47">
         <v>408871.13660000003</v>
@@ -2357,7 +2357,7 @@
         <v>33</v>
       </c>
       <c r="B48" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C48">
         <v>408871.57900000003</v>
@@ -2374,7 +2374,7 @@
         <v>34</v>
       </c>
       <c r="B49" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C49">
         <v>408872.00809999899</v>
@@ -2391,7 +2391,7 @@
         <v>35</v>
       </c>
       <c r="B50" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C50">
         <v>408872.451899999</v>
@@ -2408,7 +2408,7 @@
         <v>36</v>
       </c>
       <c r="B51" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C51">
         <v>408872.89059999899</v>
@@ -2425,7 +2425,7 @@
         <v>151</v>
       </c>
       <c r="B52" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C52">
         <v>408879.86940000003</v>
@@ -2442,7 +2442,7 @@
         <v>152</v>
       </c>
       <c r="B53" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C53">
         <v>408879.400499999</v>
@@ -2459,7 +2459,7 @@
         <v>153</v>
       </c>
       <c r="B54" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C54">
         <v>408878.89939999901</v>
@@ -2476,7 +2476,7 @@
         <v>154</v>
       </c>
       <c r="B55" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C55">
         <v>408878.41070000001</v>
@@ -2493,7 +2493,7 @@
         <v>155</v>
       </c>
       <c r="B56" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C56">
         <v>408877.92340000003</v>
@@ -2510,7 +2510,7 @@
         <v>37</v>
       </c>
       <c r="B57" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C57">
         <v>408845.46089999902</v>
@@ -2527,7 +2527,7 @@
         <v>38</v>
       </c>
       <c r="B58" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C58">
         <v>408845.02049999899</v>
@@ -2544,7 +2544,7 @@
         <v>39</v>
       </c>
       <c r="B59" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C59">
         <v>408844.56319999899</v>
@@ -2561,7 +2561,7 @@
         <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C60">
         <v>408844.13500000001</v>
@@ -2578,7 +2578,7 @@
         <v>41</v>
       </c>
       <c r="B61" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C61">
         <v>408843.68329999998</v>
@@ -2595,7 +2595,7 @@
         <v>42</v>
       </c>
       <c r="B62" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C62">
         <v>408843.26179999899</v>
@@ -2612,7 +2612,7 @@
         <v>156</v>
       </c>
       <c r="B63" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C63">
         <v>408850.18070000003</v>
@@ -2629,7 +2629,7 @@
         <v>157</v>
       </c>
       <c r="B64" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C64">
         <v>408849.70020000002</v>
@@ -2646,7 +2646,7 @@
         <v>158</v>
       </c>
       <c r="B65" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C65">
         <v>408849.219199999</v>
@@ -2663,7 +2663,7 @@
         <v>159</v>
       </c>
       <c r="B66" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C66">
         <v>408848.73200000002</v>
@@ -2680,7 +2680,7 @@
         <v>160</v>
       </c>
       <c r="B67" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C67">
         <v>408848.231299999</v>
@@ -2697,7 +2697,7 @@
         <v>43</v>
       </c>
       <c r="B68" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C68">
         <v>408814.80080000003</v>
@@ -2714,7 +2714,7 @@
         <v>44</v>
       </c>
       <c r="B69" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C69">
         <v>408815.248499999</v>
@@ -2731,7 +2731,7 @@
         <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C70">
         <v>408815.666399999</v>
@@ -2748,7 +2748,7 @@
         <v>46</v>
       </c>
       <c r="B71" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C71">
         <v>408816.12689999898</v>
@@ -2765,7 +2765,7 @@
         <v>47</v>
       </c>
       <c r="B72" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C72">
         <v>408816.55469999899</v>
@@ -2782,7 +2782,7 @@
         <v>48</v>
       </c>
       <c r="B73" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C73">
         <v>408817.00829999999</v>
@@ -2799,7 +2799,7 @@
         <v>161</v>
       </c>
       <c r="B74" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C74">
         <v>408823.76260000002</v>
@@ -2816,7 +2816,7 @@
         <v>162</v>
       </c>
       <c r="B75" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C75">
         <v>408823.264399999</v>
@@ -2833,7 +2833,7 @@
         <v>163</v>
       </c>
       <c r="B76" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C76">
         <v>408822.77899999899</v>
@@ -2850,7 +2850,7 @@
         <v>164</v>
       </c>
       <c r="B77" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C77">
         <v>408822.312299999</v>
@@ -2867,7 +2867,7 @@
         <v>165</v>
       </c>
       <c r="B78" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C78">
         <v>408821.829399999</v>
@@ -2884,7 +2884,7 @@
         <v>49</v>
       </c>
       <c r="B79" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C79">
         <v>408788.581799999</v>
@@ -2901,7 +2901,7 @@
         <v>50</v>
       </c>
       <c r="B80" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C80">
         <v>408788.11670000001</v>
@@ -2918,7 +2918,7 @@
         <v>51</v>
       </c>
       <c r="B81" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C81">
         <v>408787.67560000002</v>
@@ -2935,7 +2935,7 @@
         <v>52</v>
       </c>
       <c r="B82" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C82">
         <v>408787.222799999</v>
@@ -2952,7 +2952,7 @@
         <v>53</v>
       </c>
       <c r="B83" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C83">
         <v>408786.80749999901</v>
@@ -2969,7 +2969,7 @@
         <v>54</v>
       </c>
       <c r="B84" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C84">
         <v>408786.36930000002</v>
@@ -2986,7 +2986,7 @@
         <v>166</v>
       </c>
       <c r="B85" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C85">
         <v>408793.35800000001</v>
@@ -3003,7 +3003,7 @@
         <v>167</v>
       </c>
       <c r="B86" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C86">
         <v>408792.866099999</v>
@@ -3020,7 +3020,7 @@
         <v>168</v>
       </c>
       <c r="B87" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C87">
         <v>408792.38530000002</v>
@@ -3037,7 +3037,7 @@
         <v>169</v>
       </c>
       <c r="B88" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C88">
         <v>408791.8947</v>
@@ -3054,7 +3054,7 @@
         <v>170</v>
       </c>
       <c r="B89" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C89">
         <v>408791.43050000002</v>
@@ -3071,7 +3071,7 @@
         <v>55</v>
       </c>
       <c r="B90" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C90">
         <v>408757.90980000002</v>
@@ -3088,7 +3088,7 @@
         <v>56</v>
       </c>
       <c r="B91" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C91">
         <v>408758.367499999</v>
@@ -3105,7 +3105,7 @@
         <v>57</v>
       </c>
       <c r="B92" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C92">
         <v>408758.807399999</v>
@@ -3122,7 +3122,7 @@
         <v>58</v>
       </c>
       <c r="B93" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C93">
         <v>408759.24219999899</v>
@@ -3139,7 +3139,7 @@
         <v>59</v>
       </c>
       <c r="B94" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C94">
         <v>408759.692099999</v>
@@ -3156,7 +3156,7 @@
         <v>60</v>
       </c>
       <c r="B95" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C95">
         <v>408760.11839999899</v>
@@ -3173,7 +3173,7 @@
         <v>171</v>
       </c>
       <c r="B96" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C96">
         <v>408766.92910000001</v>
@@ -3190,7 +3190,7 @@
         <v>172</v>
       </c>
       <c r="B97" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C97">
         <v>408766.46409999899</v>
@@ -3207,7 +3207,7 @@
         <v>173</v>
       </c>
       <c r="B98" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C98">
         <v>408765.99229999899</v>
@@ -3224,7 +3224,7 @@
         <v>174</v>
       </c>
       <c r="B99" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C99">
         <v>408765.47999999899</v>
@@ -3241,7 +3241,7 @@
         <v>175</v>
       </c>
       <c r="B100" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C100">
         <v>408765.01639999897</v>
@@ -3258,7 +3258,7 @@
         <v>61</v>
       </c>
       <c r="B101" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C101">
         <v>408674.80969999899</v>
@@ -3275,7 +3275,7 @@
         <v>62</v>
       </c>
       <c r="B102" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C102">
         <v>408674.3175</v>
@@ -3292,7 +3292,7 @@
         <v>63</v>
       </c>
       <c r="B103" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C103">
         <v>408673.885899999</v>
@@ -3309,7 +3309,7 @@
         <v>64</v>
       </c>
       <c r="B104" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C104">
         <v>408673.42570000002</v>
@@ -3326,7 +3326,7 @@
         <v>65</v>
       </c>
       <c r="B105" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C105">
         <v>408673.00859999901</v>
@@ -3343,7 +3343,7 @@
         <v>66</v>
       </c>
       <c r="B106" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C106">
         <v>408672.59139999899</v>
@@ -3360,7 +3360,7 @@
         <v>176</v>
       </c>
       <c r="B107" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C107">
         <v>408680.68900000001</v>
@@ -3377,7 +3377,7 @@
         <v>177</v>
       </c>
       <c r="B108" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C108">
         <v>408680.20289999899</v>
@@ -3394,7 +3394,7 @@
         <v>178</v>
       </c>
       <c r="B109" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C109">
         <v>408679.7047</v>
@@ -3411,7 +3411,7 @@
         <v>179</v>
       </c>
       <c r="B110" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C110">
         <v>408679.21340000001</v>
@@ -3428,7 +3428,7 @@
         <v>180</v>
       </c>
       <c r="B111" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C111">
         <v>408678.73639999999</v>
@@ -3455,13 +3455,13 @@
         <v>101</v>
       </c>
       <c r="B1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E1" t="s">
         <v>112</v>
@@ -3472,7 +3472,7 @@
         <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C2">
         <v>409000.4903</v>
@@ -3489,7 +3489,7 @@
         <v>71</v>
       </c>
       <c r="B3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C3">
         <v>408997.63040000002</v>
@@ -3506,7 +3506,7 @@
         <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C4">
         <v>408987.19380000001</v>
@@ -3523,7 +3523,7 @@
         <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C5">
         <v>408982.38959999901</v>
@@ -3540,7 +3540,7 @@
         <v>146</v>
       </c>
       <c r="B6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C6">
         <v>408985.71999999898</v>
@@ -3557,7 +3557,7 @@
         <v>147</v>
       </c>
       <c r="B7" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C7">
         <v>408984.80999999901</v>
@@ -3574,7 +3574,7 @@
         <v>148</v>
       </c>
       <c r="B8" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C8">
         <v>408983.89</v>
@@ -3591,7 +3591,7 @@
         <v>149</v>
       </c>
       <c r="B9" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C9">
         <v>409002.11999999901</v>
@@ -3608,7 +3608,7 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C10">
         <v>408957.29330000002</v>
@@ -3625,7 +3625,7 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C11">
         <v>408956.69130000001</v>
@@ -3642,7 +3642,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C12">
         <v>408956.084399999</v>
@@ -3659,7 +3659,7 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C13">
         <v>408955.49589999899</v>
@@ -3676,7 +3676,7 @@
         <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C14">
         <v>408973.7121</v>
@@ -3693,7 +3693,7 @@
         <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C15">
         <v>408968.074599999</v>
@@ -3710,7 +3710,7 @@
         <v>144</v>
       </c>
       <c r="B16" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C16">
         <v>408961.76</v>
@@ -3727,7 +3727,7 @@
         <v>145</v>
       </c>
       <c r="B17" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C17">
         <v>408963.02</v>
@@ -3744,7 +3744,7 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C18">
         <v>408943.05879999901</v>
@@ -3761,7 +3761,7 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C19">
         <v>408942.48519999901</v>
@@ -3778,7 +3778,7 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C20">
         <v>408941.846599999</v>
@@ -3795,7 +3795,7 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C21">
         <v>408941.274299999</v>
@@ -3812,7 +3812,7 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C22">
         <v>408928.85560000001</v>
@@ -3829,7 +3829,7 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C23">
         <v>408928.25300000003</v>
@@ -3846,7 +3846,7 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C24">
         <v>408927.64370000002</v>
@@ -3863,7 +3863,7 @@
         <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C25">
         <v>408927.035299999</v>
@@ -3880,7 +3880,7 @@
         <v>140</v>
       </c>
       <c r="B26" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C26">
         <v>408933.33</v>
@@ -3897,7 +3897,7 @@
         <v>141</v>
       </c>
       <c r="B27" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C27">
         <v>408934.59</v>
@@ -3914,7 +3914,7 @@
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C28">
         <v>408914.35340000002</v>
@@ -3931,7 +3931,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C29">
         <v>408913.7599</v>
@@ -3948,7 +3948,7 @@
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C30">
         <v>408913.14380000002</v>
@@ -3965,7 +3965,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C31">
         <v>408912.52870000002</v>
@@ -3982,7 +3982,7 @@
         <v>139</v>
       </c>
       <c r="B32" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C32">
         <v>408905.239999999</v>
@@ -3999,7 +3999,7 @@
         <v>153</v>
       </c>
       <c r="B33" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C33">
         <v>408900.20380000002</v>
@@ -4016,7 +4016,7 @@
         <v>154</v>
       </c>
       <c r="B34" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C34">
         <v>408899.61949999898</v>
@@ -4033,7 +4033,7 @@
         <v>155</v>
       </c>
       <c r="B35" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C35">
         <v>408899.00260000001</v>
@@ -4050,7 +4050,7 @@
         <v>156</v>
       </c>
       <c r="B36" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C36">
         <v>408898.37829999899</v>
@@ -4067,7 +4067,7 @@
         <v>135</v>
       </c>
       <c r="B37" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C37">
         <v>408877.859999999</v>
@@ -4084,7 +4084,7 @@
         <v>157</v>
       </c>
       <c r="B38" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C38">
         <v>408885.99040000001</v>
@@ -4101,7 +4101,7 @@
         <v>158</v>
       </c>
       <c r="B39" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C39">
         <v>408885.37439999898</v>
@@ -4118,7 +4118,7 @@
         <v>159</v>
       </c>
       <c r="B40" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C40">
         <v>408884.80279999902</v>
@@ -4135,7 +4135,7 @@
         <v>160</v>
       </c>
       <c r="B41" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C41">
         <v>408884.17149999901</v>
@@ -4152,7 +4152,7 @@
         <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C42">
         <v>408859.25290000002</v>
@@ -4169,7 +4169,7 @@
         <v>18</v>
       </c>
       <c r="B43" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C43">
         <v>408858.64659999899</v>
@@ -4186,7 +4186,7 @@
         <v>19</v>
       </c>
       <c r="B44" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C44">
         <v>408858.0344</v>
@@ -4203,7 +4203,7 @@
         <v>20</v>
       </c>
       <c r="B45" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C45">
         <v>408857.44079999899</v>
@@ -4220,7 +4220,7 @@
         <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C46">
         <v>408845.03460000001</v>
@@ -4237,7 +4237,7 @@
         <v>22</v>
       </c>
       <c r="B47" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C47">
         <v>408844.4375</v>
@@ -4254,7 +4254,7 @@
         <v>23</v>
       </c>
       <c r="B48" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C48">
         <v>408843.829399999</v>
@@ -4271,7 +4271,7 @@
         <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C49">
         <v>408843.20490000001</v>
@@ -4288,7 +4288,7 @@
         <v>132</v>
       </c>
       <c r="B50" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C50">
         <v>408849.489999999</v>
@@ -4305,7 +4305,7 @@
         <v>133</v>
       </c>
       <c r="B51" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C51">
         <v>408850.72999999899</v>
@@ -4322,7 +4322,7 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C52">
         <v>408830.81489999901</v>
@@ -4339,7 +4339,7 @@
         <v>26</v>
       </c>
       <c r="B53" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C53">
         <v>408830.206899999</v>
@@ -4356,7 +4356,7 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C54">
         <v>408829.59519999899</v>
@@ -4373,7 +4373,7 @@
         <v>28</v>
       </c>
       <c r="B55" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C55">
         <v>408828.99920000002</v>
@@ -4390,7 +4390,7 @@
         <v>29</v>
       </c>
       <c r="B56" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C56">
         <v>408816.59179999901</v>
@@ -4407,7 +4407,7 @@
         <v>30</v>
       </c>
       <c r="B57" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C57">
         <v>408815.986199999</v>
@@ -4424,7 +4424,7 @@
         <v>31</v>
       </c>
       <c r="B58" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C58">
         <v>408815.39</v>
@@ -4441,7 +4441,7 @@
         <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C59">
         <v>408814.777</v>
@@ -4458,7 +4458,7 @@
         <v>128</v>
       </c>
       <c r="B60" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C60">
         <v>408821.109999999</v>
@@ -4475,7 +4475,7 @@
         <v>129</v>
       </c>
       <c r="B61" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C61">
         <v>408822.35</v>
@@ -4492,7 +4492,7 @@
         <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C62">
         <v>408802.449499999</v>
@@ -4509,7 +4509,7 @@
         <v>34</v>
       </c>
       <c r="B63" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C63">
         <v>408801.83819999901</v>
@@ -4526,7 +4526,7 @@
         <v>35</v>
       </c>
       <c r="B64" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C64">
         <v>408801.21379999898</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="B65" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C65">
         <v>408800.62819999899</v>
@@ -4560,7 +4560,7 @@
         <v>37</v>
       </c>
       <c r="B66" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C66">
         <v>408788.22350000002</v>
@@ -4577,7 +4577,7 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C67">
         <v>408787.60700000002</v>
@@ -4594,7 +4594,7 @@
         <v>39</v>
       </c>
       <c r="B68" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C68">
         <v>408787.00040000002</v>
@@ -4611,7 +4611,7 @@
         <v>40</v>
       </c>
       <c r="B69" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C69">
         <v>408786.40159999899</v>
@@ -4628,7 +4628,7 @@
         <v>126</v>
       </c>
       <c r="B70" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C70">
         <v>408794.59</v>
@@ -4645,7 +4645,7 @@
         <v>127</v>
       </c>
       <c r="B71" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C71">
         <v>408793.34999999899</v>
@@ -4662,7 +4662,7 @@
         <v>41</v>
       </c>
       <c r="B72" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C72">
         <v>408773.99790000002</v>
@@ -4679,7 +4679,7 @@
         <v>42</v>
       </c>
       <c r="B73" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C73">
         <v>408773.39649999898</v>
@@ -4696,7 +4696,7 @@
         <v>43</v>
       </c>
       <c r="B74" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C74">
         <v>408772.784099999</v>
@@ -4713,7 +4713,7 @@
         <v>44</v>
       </c>
       <c r="B75" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C75">
         <v>408772.17050000001</v>
@@ -4730,7 +4730,7 @@
         <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C76">
         <v>408759.7758</v>
@@ -4747,7 +4747,7 @@
         <v>46</v>
       </c>
       <c r="B77" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C77">
         <v>408759.1692</v>
@@ -4764,7 +4764,7 @@
         <v>47</v>
       </c>
       <c r="B78" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C78">
         <v>408758.57179999899</v>
@@ -4781,7 +4781,7 @@
         <v>48</v>
       </c>
       <c r="B79" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C79">
         <v>408757.959299999</v>
@@ -4798,7 +4798,7 @@
         <v>123</v>
       </c>
       <c r="B80" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C80">
         <v>408764.84999999899</v>
@@ -4815,7 +4815,7 @@
         <v>67</v>
       </c>
       <c r="B81" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C81">
         <v>408685.49530000001</v>
@@ -4832,7 +4832,7 @@
         <v>68</v>
       </c>
       <c r="B82" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C82">
         <v>408676.1875</v>
@@ -4849,7 +4849,7 @@
         <v>70</v>
       </c>
       <c r="B83" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C83">
         <v>408673.02689999901</v>
@@ -4866,7 +4866,7 @@
         <v>113</v>
       </c>
       <c r="B84" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C84">
         <v>408680.549999999</v>
@@ -4883,7 +4883,7 @@
         <v>114</v>
       </c>
       <c r="B85" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C85">
         <v>408679.679999999</v>
@@ -4900,7 +4900,7 @@
         <v>115</v>
       </c>
       <c r="B86" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C86">
         <v>408678.72999999899</v>
@@ -4930,211 +4930,211 @@
         <v>100</v>
       </c>
       <c r="C1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E1" t="s">
         <v>379</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>113</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>114</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>115</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>116</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>117</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>118</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>119</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>120</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>121</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>122</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>123</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>124</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>125</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>126</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>127</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>128</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>129</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>130</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>131</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>132</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>133</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>134</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>135</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>136</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>137</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>138</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>139</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>140</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>141</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>142</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>143</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>144</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>145</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>146</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>147</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>148</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>149</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>150</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>151</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>152</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>153</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>154</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>155</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>156</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>157</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>158</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>159</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>160</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>161</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>162</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>163</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>164</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>165</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>166</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>167</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>168</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>169</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BK1" t="s">
         <v>170</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>171</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>172</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>173</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>174</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>175</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>176</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>177</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>178</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>179</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
@@ -26226,211 +26226,211 @@
         <v>112</v>
       </c>
       <c r="C1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E1" t="s">
         <v>379</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>113</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>114</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>115</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>116</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>117</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>118</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>119</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>120</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>121</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>122</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>123</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>124</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>125</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>126</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>127</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>128</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>129</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>130</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>131</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>132</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>133</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>134</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>135</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>136</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>137</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>138</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>139</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>140</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>141</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>142</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>143</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>144</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>145</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>146</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>147</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>148</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>149</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>150</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>151</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>152</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>153</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>154</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>155</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>156</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>157</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>158</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>159</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>160</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>161</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>162</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>163</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>164</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>165</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>166</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>167</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>168</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>169</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BK1" t="s">
         <v>170</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>171</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>172</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>173</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>174</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>175</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>176</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>177</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>178</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>179</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
